--- a/research/traditional_assets/database/data/mexico/mexico_entertainment.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_entertainment.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.179</v>
+        <v>-0.214</v>
       </c>
       <c r="G2">
-        <v>-0.4167585446527012</v>
+        <v>0.1629090909090909</v>
       </c>
       <c r="H2">
-        <v>-0.4167585446527012</v>
+        <v>0.1629090909090909</v>
       </c>
       <c r="I2">
-        <v>-0.3202866593164278</v>
+        <v>0.4094545454545455</v>
       </c>
       <c r="J2">
-        <v>-0.3202866593164278</v>
+        <v>0.2465958132045089</v>
       </c>
       <c r="K2">
-        <v>-54.7</v>
+        <v>333.3</v>
       </c>
       <c r="L2">
-        <v>-0.3015435501653804</v>
+        <v>2.424</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +624,76 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>165</v>
+        <v>120.7</v>
       </c>
       <c r="V2">
-        <v>0.6718241042345277</v>
+        <v>0.3118057349522087</v>
       </c>
       <c r="W2">
-        <v>-0.7803138373751785</v>
+        <v>13.54878048780488</v>
       </c>
       <c r="X2">
-        <v>0.1138025881669136</v>
+        <v>0.1419879803440663</v>
       </c>
       <c r="Y2">
-        <v>-0.8941164255420921</v>
+        <v>13.40679250746081</v>
       </c>
       <c r="Z2">
-        <v>1.438540840602697</v>
+        <v>1.98699421965318</v>
       </c>
       <c r="AA2">
-        <v>-0.4607454401268836</v>
+        <v>0.4899844554280343</v>
       </c>
       <c r="AB2">
-        <v>0.0747940110384222</v>
+        <v>0.1400516781815918</v>
       </c>
       <c r="AC2">
-        <v>-0.5355394511653058</v>
+        <v>0.3499327772464425</v>
       </c>
       <c r="AD2">
-        <v>209.6</v>
+        <v>8.27</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>209.6</v>
+        <v>8.27</v>
       </c>
       <c r="AG2">
-        <v>44.59999999999999</v>
+        <v>-112.43</v>
       </c>
       <c r="AH2">
-        <v>0.4604569420035149</v>
+        <v>0.02091711561322306</v>
       </c>
       <c r="AI2">
-        <v>0.894579598804951</v>
+        <v>0.02359015317910831</v>
       </c>
       <c r="AJ2">
-        <v>0.1536871123363198</v>
+        <v>-0.4093275567044089</v>
       </c>
       <c r="AK2">
-        <v>0.6435786435786435</v>
+        <v>-0.4891025362161222</v>
       </c>
       <c r="AL2">
-        <v>18.7</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>14.44</v>
+        <v>-6.98</v>
       </c>
       <c r="AN2">
-        <v>-6.894736842105264</v>
-      </c>
-      <c r="AO2">
-        <v>-3.106951871657754</v>
+        <v>0.1759574468085106</v>
       </c>
       <c r="AP2">
-        <v>-1.467105263157895</v>
+        <v>-2.392127659574468</v>
       </c>
       <c r="AQ2">
-        <v>-4.023545706371191</v>
+        <v>-8.06590257879656</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +713,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.179</v>
+        <v>-0.214</v>
       </c>
       <c r="G3">
-        <v>-0.4167585446527012</v>
+        <v>0.1629090909090909</v>
       </c>
       <c r="H3">
-        <v>-0.4167585446527012</v>
+        <v>0.1629090909090909</v>
       </c>
       <c r="I3">
-        <v>-0.3202866593164278</v>
+        <v>0.4094545454545455</v>
       </c>
       <c r="J3">
-        <v>-0.3202866593164278</v>
+        <v>0.2465958132045089</v>
       </c>
       <c r="K3">
-        <v>-54.7</v>
+        <v>333.3</v>
       </c>
       <c r="L3">
-        <v>-0.3015435501653804</v>
+        <v>2.424</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +740,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +749,76 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>165</v>
+        <v>120.7</v>
       </c>
       <c r="V3">
-        <v>0.6718241042345277</v>
+        <v>0.3118057349522087</v>
       </c>
       <c r="W3">
-        <v>-0.7803138373751785</v>
+        <v>13.54878048780488</v>
       </c>
       <c r="X3">
-        <v>0.1138025881669136</v>
+        <v>0.1419879803440663</v>
       </c>
       <c r="Y3">
-        <v>-0.8941164255420921</v>
+        <v>13.40679250746081</v>
       </c>
       <c r="Z3">
-        <v>1.438540840602697</v>
+        <v>1.98699421965318</v>
       </c>
       <c r="AA3">
-        <v>-0.4607454401268836</v>
+        <v>0.4899844554280343</v>
       </c>
       <c r="AB3">
-        <v>0.0747940110384222</v>
+        <v>0.1400516781815918</v>
       </c>
       <c r="AC3">
-        <v>-0.5355394511653058</v>
+        <v>0.3499327772464425</v>
       </c>
       <c r="AD3">
-        <v>209.6</v>
+        <v>8.27</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>209.6</v>
+        <v>8.27</v>
       </c>
       <c r="AG3">
-        <v>44.59999999999999</v>
+        <v>-112.43</v>
       </c>
       <c r="AH3">
-        <v>0.4604569420035149</v>
+        <v>0.02091711561322306</v>
       </c>
       <c r="AI3">
-        <v>0.894579598804951</v>
+        <v>0.02359015317910831</v>
       </c>
       <c r="AJ3">
-        <v>0.1536871123363198</v>
+        <v>-0.4093275567044089</v>
       </c>
       <c r="AK3">
-        <v>0.6435786435786435</v>
+        <v>-0.4891025362161222</v>
       </c>
       <c r="AL3">
-        <v>18.7</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>14.44</v>
+        <v>-6.98</v>
       </c>
       <c r="AN3">
-        <v>-6.894736842105264</v>
-      </c>
-      <c r="AO3">
-        <v>-3.106951871657754</v>
+        <v>0.1759574468085106</v>
       </c>
       <c r="AP3">
-        <v>-1.467105263157895</v>
+        <v>-2.392127659574468</v>
       </c>
       <c r="AQ3">
-        <v>-4.023545706371191</v>
+        <v>-8.06590257879656</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/mexico/mexico_entertainment.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_entertainment.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bmv_cie_b" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,112 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.214</v>
+        <v>-0.187</v>
+      </c>
+      <c r="E2">
+        <v>0.414</v>
       </c>
       <c r="G2">
-        <v>0.1629090909090909</v>
+        <v>0.1578479324144064</v>
       </c>
       <c r="H2">
-        <v>0.1629090909090909</v>
+        <v>0.1578479324144064</v>
       </c>
       <c r="I2">
-        <v>0.4094545454545455</v>
+        <v>0.223654957759004</v>
       </c>
       <c r="J2">
-        <v>0.2465958132045089</v>
+        <v>0.2032655298829823</v>
       </c>
       <c r="K2">
-        <v>333.3</v>
+        <v>70.3</v>
       </c>
       <c r="L2">
-        <v>2.424</v>
+        <v>0.3125833703868386</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>176.7704</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.2332986670186089</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>2.51451493598862</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>176.7704</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.2332986670186089</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.51451493598862</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>120.7</v>
+        <v>103.4</v>
       </c>
       <c r="V2">
-        <v>0.3118057349522087</v>
+        <v>0.1364656196383793</v>
       </c>
       <c r="W2">
-        <v>13.54878048780488</v>
+        <v>0.1959855032060217</v>
       </c>
       <c r="X2">
-        <v>0.1419879803440663</v>
+        <v>0.1208468273414744</v>
       </c>
       <c r="Y2">
-        <v>13.40679250746081</v>
+        <v>0.07513867586454737</v>
       </c>
       <c r="Z2">
-        <v>1.98699421965318</v>
+        <v>0.9132253218012751</v>
       </c>
       <c r="AA2">
-        <v>0.4899844554280343</v>
+        <v>0.1856272289384932</v>
       </c>
       <c r="AB2">
-        <v>0.1400516781815918</v>
+        <v>0.1121647835823337</v>
       </c>
       <c r="AC2">
-        <v>0.3499327772464425</v>
+        <v>0.07346244535615951</v>
       </c>
       <c r="AD2">
-        <v>8.27</v>
+        <v>99.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>8.27</v>
+        <v>99.5</v>
       </c>
       <c r="AG2">
-        <v>-112.43</v>
+        <v>-3.900000000000006</v>
       </c>
       <c r="AH2">
-        <v>0.02091711561322306</v>
+        <v>0.116075594960336</v>
       </c>
       <c r="AI2">
-        <v>0.02359015317910831</v>
+        <v>0.2535031847133758</v>
       </c>
       <c r="AJ2">
-        <v>-0.4093275567044089</v>
+        <v>-0.005173786150172467</v>
       </c>
       <c r="AK2">
-        <v>-0.4891025362161222</v>
+        <v>-0.01349014181943966</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="AM2">
-        <v>-6.98</v>
+        <v>-2.299999999999999</v>
       </c>
       <c r="AN2">
-        <v>0.1759574468085106</v>
+        <v>1.839186691312384</v>
+      </c>
+      <c r="AO2">
+        <v>4.883495145631067</v>
       </c>
       <c r="AP2">
-        <v>-2.392127659574468</v>
+        <v>-0.07208872458410362</v>
       </c>
       <c r="AQ2">
-        <v>-8.06590257879656</v>
+        <v>-21.86956521739131</v>
       </c>
     </row>
     <row r="3">
@@ -713,112 +724,8893 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.214</v>
+        <v>-0.187</v>
+      </c>
+      <c r="E3">
+        <v>0.414</v>
       </c>
       <c r="G3">
-        <v>0.1629090909090909</v>
+        <v>0.1578479324144064</v>
       </c>
       <c r="H3">
-        <v>0.1629090909090909</v>
+        <v>0.1578479324144064</v>
       </c>
       <c r="I3">
-        <v>0.4094545454545455</v>
+        <v>0.223654957759004</v>
       </c>
       <c r="J3">
-        <v>0.2465958132045089</v>
+        <v>0.2032655298829823</v>
       </c>
       <c r="K3">
-        <v>333.3</v>
+        <v>70.3</v>
       </c>
       <c r="L3">
-        <v>2.424</v>
+        <v>0.3125833703868386</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>176.7704</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.2332986670186089</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>2.51451493598862</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>176.7704</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.2332986670186089</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>2.51451493598862</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>120.7</v>
+        <v>103.4</v>
       </c>
       <c r="V3">
-        <v>0.3118057349522087</v>
+        <v>0.1364656196383793</v>
       </c>
       <c r="W3">
-        <v>13.54878048780488</v>
+        <v>0.1959855032060217</v>
       </c>
       <c r="X3">
-        <v>0.1419879803440663</v>
+        <v>0.1208468273414744</v>
       </c>
       <c r="Y3">
-        <v>13.40679250746081</v>
+        <v>0.07513867586454737</v>
       </c>
       <c r="Z3">
-        <v>1.98699421965318</v>
+        <v>0.9132253218012751</v>
       </c>
       <c r="AA3">
-        <v>0.4899844554280343</v>
+        <v>0.1856272289384932</v>
       </c>
       <c r="AB3">
-        <v>0.1400516781815918</v>
+        <v>0.1121647835823337</v>
       </c>
       <c r="AC3">
-        <v>0.3499327772464425</v>
+        <v>0.07346244535615951</v>
       </c>
       <c r="AD3">
-        <v>8.27</v>
+        <v>99.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>8.27</v>
+        <v>99.5</v>
       </c>
       <c r="AG3">
-        <v>-112.43</v>
+        <v>-3.900000000000006</v>
       </c>
       <c r="AH3">
-        <v>0.02091711561322306</v>
+        <v>0.116075594960336</v>
       </c>
       <c r="AI3">
-        <v>0.02359015317910831</v>
+        <v>0.2535031847133758</v>
       </c>
       <c r="AJ3">
-        <v>-0.4093275567044089</v>
+        <v>-0.005173786150172467</v>
       </c>
       <c r="AK3">
-        <v>-0.4891025362161222</v>
+        <v>-0.01349014181943966</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="AM3">
-        <v>-6.98</v>
+        <v>-2.299999999999999</v>
       </c>
       <c r="AN3">
-        <v>0.1759574468085106</v>
+        <v>1.839186691312384</v>
+      </c>
+      <c r="AO3">
+        <v>4.883495145631067</v>
       </c>
       <c r="AP3">
-        <v>-2.392127659574468</v>
+        <v>-0.07208872458410362</v>
       </c>
       <c r="AQ3">
-        <v>-8.06590257879656</v>
+        <v>-21.86956521739131</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Corporación Interamericana de Entretenimiento, S.A.B. de C.V. (BMV:CIE B)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BMV:CIE B</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>4.88349514563107</v>
+      </c>
+      <c r="F2">
+        <v>4.0031662712091</v>
+      </c>
+      <c r="G2">
+        <v>1.83918669131238</v>
+      </c>
+      <c r="H2">
+        <v>4.43652495378928</v>
+      </c>
+      <c r="I2">
+        <v>0.116075594960336</v>
+      </c>
+      <c r="J2">
+        <v>0.28</v>
+      </c>
+      <c r="K2">
+        <v>757.7</v>
+      </c>
+      <c r="L2">
+        <v>671.307403996851</v>
+      </c>
+      <c r="M2">
+        <v>753.8</v>
+      </c>
+      <c r="N2">
+        <v>807.923403996851</v>
+      </c>
+      <c r="O2">
+        <v>99.5</v>
+      </c>
+      <c r="P2">
+        <v>240.016</v>
+      </c>
+      <c r="Q2">
+        <v>0.112164783582334</v>
+      </c>
+      <c r="R2">
+        <v>0.107250020869279</v>
+      </c>
+      <c r="S2">
+        <v>0.0460503659310687</v>
+      </c>
+      <c r="T2">
+        <v>0.03745</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.120846827341474</v>
+      </c>
+      <c r="X2">
+        <v>0.134394473429554</v>
+      </c>
+      <c r="Y2">
+        <v>1.11104493842696</v>
+      </c>
+      <c r="Z2">
+        <v>1.29450168016195</v>
+      </c>
+      <c r="AA2">
+        <v>99.5</v>
+      </c>
+      <c r="AB2">
+        <v>0.06578623704438383</v>
+      </c>
+      <c r="AC2">
+        <v>4.883495145631067</v>
+      </c>
+      <c r="AD2">
+        <v>99.5</v>
+      </c>
+      <c r="AE2">
+        <v>10.3</v>
+      </c>
+      <c r="AF2">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="AG2">
+        <v>54.1</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>757.7</v>
+      </c>
+      <c r="AK2">
+        <v>0.07384654256887045</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.3</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>16</v>
+      </c>
+      <c r="AR2">
+        <v>10.3</v>
+      </c>
+      <c r="AS2">
+        <v>99.5</v>
+      </c>
+      <c r="AT2">
+        <v>103.4</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1139397607743218</v>
+      </c>
+      <c r="C2">
+        <v>839.3934779465278</v>
+      </c>
+      <c r="D2">
+        <v>735.9934779465278</v>
+      </c>
+      <c r="E2">
+        <v>-99.5</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>103.4</v>
+      </c>
+      <c r="H2">
+        <v>757.7</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K2">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L2">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="O2">
+        <v>15.42122448979592</v>
+      </c>
+      <c r="P2">
+        <v>35.98285714285714</v>
+      </c>
+      <c r="Q2">
+        <v>39.78285714285715</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1139397607743218</v>
+      </c>
+      <c r="T2">
+        <v>1.017512237681883</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.3</v>
+      </c>
+      <c r="W2">
+        <v>0.03129</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1136392414919988</v>
+      </c>
+      <c r="C3">
+        <v>833.7768824559457</v>
+      </c>
+      <c r="D3">
+        <v>738.9488824559457</v>
+      </c>
+      <c r="E3">
+        <v>-90.928</v>
+      </c>
+      <c r="F3">
+        <v>8.572000000000001</v>
+      </c>
+      <c r="G3">
+        <v>103.4</v>
+      </c>
+      <c r="H3">
+        <v>757.7</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K3">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L3">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M3">
+        <v>0.3831684000000001</v>
+      </c>
+      <c r="N3">
+        <v>51.02091323265306</v>
+      </c>
+      <c r="O3">
+        <v>15.30627396979592</v>
+      </c>
+      <c r="P3">
+        <v>35.71463926285714</v>
+      </c>
+      <c r="Q3">
+        <v>39.51463926285714</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.11447105201212</v>
+      </c>
+      <c r="T3">
+        <v>1.024706768655391</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.3</v>
+      </c>
+      <c r="W3">
+        <v>0.03129</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>134.1553260463364</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1133387222096758</v>
+      </c>
+      <c r="C4">
+        <v>828.1841176943008</v>
+      </c>
+      <c r="D4">
+        <v>741.9281176943008</v>
+      </c>
+      <c r="E4">
+        <v>-82.35599999999999</v>
+      </c>
+      <c r="F4">
+        <v>17.144</v>
+      </c>
+      <c r="G4">
+        <v>103.4</v>
+      </c>
+      <c r="H4">
+        <v>757.7</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K4">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L4">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M4">
+        <v>0.7663368000000002</v>
+      </c>
+      <c r="N4">
+        <v>50.63774483265306</v>
+      </c>
+      <c r="O4">
+        <v>15.19132344979592</v>
+      </c>
+      <c r="P4">
+        <v>35.44642138285715</v>
+      </c>
+      <c r="Q4">
+        <v>39.24642138285715</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1150131859282407</v>
+      </c>
+      <c r="T4">
+        <v>1.032048126791624</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.3</v>
+      </c>
+      <c r="W4">
+        <v>0.03129</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>67.07766302316821</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1130382029273529</v>
+      </c>
+      <c r="C5">
+        <v>822.6154730648896</v>
+      </c>
+      <c r="D5">
+        <v>744.9314730648896</v>
+      </c>
+      <c r="E5">
+        <v>-73.78399999999999</v>
+      </c>
+      <c r="F5">
+        <v>25.716</v>
+      </c>
+      <c r="G5">
+        <v>103.4</v>
+      </c>
+      <c r="H5">
+        <v>757.7</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K5">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L5">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M5">
+        <v>1.1495052</v>
+      </c>
+      <c r="N5">
+        <v>50.25457643265306</v>
+      </c>
+      <c r="O5">
+        <v>15.07637292979592</v>
+      </c>
+      <c r="P5">
+        <v>35.17820350285714</v>
+      </c>
+      <c r="Q5">
+        <v>38.97820350285715</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1155664978632504</v>
+      </c>
+      <c r="T5">
+        <v>1.039540853136851</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.3</v>
+      </c>
+      <c r="W5">
+        <v>0.03129</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>44.71844201544548</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1127376836450299</v>
+      </c>
+      <c r="C6">
+        <v>817.0712426761208</v>
+      </c>
+      <c r="D6">
+        <v>747.9592426761209</v>
+      </c>
+      <c r="E6">
+        <v>-65.21199999999999</v>
+      </c>
+      <c r="F6">
+        <v>34.288</v>
+      </c>
+      <c r="G6">
+        <v>103.4</v>
+      </c>
+      <c r="H6">
+        <v>757.7</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K6">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L6">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M6">
+        <v>1.5326736</v>
+      </c>
+      <c r="N6">
+        <v>49.87140803265306</v>
+      </c>
+      <c r="O6">
+        <v>14.96142240979592</v>
+      </c>
+      <c r="P6">
+        <v>34.90998562285714</v>
+      </c>
+      <c r="Q6">
+        <v>38.70998562285715</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1161313371302395</v>
+      </c>
+      <c r="T6">
+        <v>1.047189677947604</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.3</v>
+      </c>
+      <c r="W6">
+        <v>0.03129</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>33.5388315115841</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1124371643627069</v>
+      </c>
+      <c r="C7">
+        <v>811.5517254375252</v>
+      </c>
+      <c r="D7">
+        <v>751.0117254375252</v>
+      </c>
+      <c r="E7">
+        <v>-56.63999999999999</v>
+      </c>
+      <c r="F7">
+        <v>42.86000000000001</v>
+      </c>
+      <c r="G7">
+        <v>103.4</v>
+      </c>
+      <c r="H7">
+        <v>757.7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K7">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L7">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M7">
+        <v>1.915842</v>
+      </c>
+      <c r="N7">
+        <v>49.48823963265306</v>
+      </c>
+      <c r="O7">
+        <v>14.84647188979592</v>
+      </c>
+      <c r="P7">
+        <v>34.64176774285714</v>
+      </c>
+      <c r="Q7">
+        <v>38.44176774285715</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1167080677502178</v>
+      </c>
+      <c r="T7">
+        <v>1.05499953064911</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.3</v>
+      </c>
+      <c r="W7">
+        <v>0.03129</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>26.83106520926728</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.112136645080384</v>
+      </c>
+      <c r="C8">
+        <v>806.057225158125</v>
+      </c>
+      <c r="D8">
+        <v>754.089225158125</v>
+      </c>
+      <c r="E8">
+        <v>-48.068</v>
+      </c>
+      <c r="F8">
+        <v>51.432</v>
+      </c>
+      <c r="G8">
+        <v>103.4</v>
+      </c>
+      <c r="H8">
+        <v>757.7</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K8">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L8">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M8">
+        <v>2.2990104</v>
+      </c>
+      <c r="N8">
+        <v>49.10507123265306</v>
+      </c>
+      <c r="O8">
+        <v>14.73152136979592</v>
+      </c>
+      <c r="P8">
+        <v>34.37354986285715</v>
+      </c>
+      <c r="Q8">
+        <v>38.17354986285715</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.117297069234451</v>
+      </c>
+      <c r="T8">
+        <v>1.062975550429371</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.3</v>
+      </c>
+      <c r="W8">
+        <v>0.03129</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>22.35922100772274</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.111836125798061</v>
+      </c>
+      <c r="C9">
+        <v>800.588050647234</v>
+      </c>
+      <c r="D9">
+        <v>757.1920506472341</v>
+      </c>
+      <c r="E9">
+        <v>-39.49599999999999</v>
+      </c>
+      <c r="F9">
+        <v>60.00400000000001</v>
+      </c>
+      <c r="G9">
+        <v>103.4</v>
+      </c>
+      <c r="H9">
+        <v>757.7</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K9">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L9">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M9">
+        <v>2.682178800000001</v>
+      </c>
+      <c r="N9">
+        <v>48.72190283265306</v>
+      </c>
+      <c r="O9">
+        <v>14.61657084979592</v>
+      </c>
+      <c r="P9">
+        <v>34.10533198285714</v>
+      </c>
+      <c r="Q9">
+        <v>37.90533198285714</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1178987374172699</v>
+      </c>
+      <c r="T9">
+        <v>1.071123097516735</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.3</v>
+      </c>
+      <c r="W9">
+        <v>0.03129</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>19.16504657804806</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.111535606515738</v>
+      </c>
+      <c r="C10">
+        <v>795.1445158177543</v>
+      </c>
+      <c r="D10">
+        <v>760.3205158177543</v>
+      </c>
+      <c r="E10">
+        <v>-30.92399999999999</v>
+      </c>
+      <c r="F10">
+        <v>68.57600000000001</v>
+      </c>
+      <c r="G10">
+        <v>103.4</v>
+      </c>
+      <c r="H10">
+        <v>757.7</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K10">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L10">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M10">
+        <v>3.065347200000001</v>
+      </c>
+      <c r="N10">
+        <v>48.33873443265306</v>
+      </c>
+      <c r="O10">
+        <v>14.50162032979592</v>
+      </c>
+      <c r="P10">
+        <v>33.83711410285714</v>
+      </c>
+      <c r="Q10">
+        <v>37.63711410285715</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1185134853431935</v>
+      </c>
+      <c r="T10">
+        <v>1.079447765192954</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.3</v>
+      </c>
+      <c r="W10">
+        <v>0.03129</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>16.76941575579205</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1112350872334151</v>
+      </c>
+      <c r="C11">
+        <v>789.7269397920458</v>
+      </c>
+      <c r="D11">
+        <v>763.4749397920458</v>
+      </c>
+      <c r="E11">
+        <v>-22.352</v>
+      </c>
+      <c r="F11">
+        <v>77.148</v>
+      </c>
+      <c r="G11">
+        <v>103.4</v>
+      </c>
+      <c r="H11">
+        <v>757.7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K11">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L11">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M11">
+        <v>3.4485156</v>
+      </c>
+      <c r="N11">
+        <v>47.95556603265306</v>
+      </c>
+      <c r="O11">
+        <v>14.38666980979592</v>
+      </c>
+      <c r="P11">
+        <v>33.56889622285714</v>
+      </c>
+      <c r="Q11">
+        <v>37.36889622285715</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.119141744212544</v>
+      </c>
+      <c r="T11">
+        <v>1.087955392598321</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.3</v>
+      </c>
+      <c r="W11">
+        <v>0.03129</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>14.90614733848183</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1109345679510921</v>
+      </c>
+      <c r="C12">
+        <v>784.3356470104414</v>
+      </c>
+      <c r="D12">
+        <v>766.6556470104415</v>
+      </c>
+      <c r="E12">
+        <v>-13.77999999999999</v>
+      </c>
+      <c r="F12">
+        <v>85.72000000000001</v>
+      </c>
+      <c r="G12">
+        <v>103.4</v>
+      </c>
+      <c r="H12">
+        <v>757.7</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K12">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L12">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M12">
+        <v>3.831684000000001</v>
+      </c>
+      <c r="N12">
+        <v>47.57239763265306</v>
+      </c>
+      <c r="O12">
+        <v>14.27171928979592</v>
+      </c>
+      <c r="P12">
+        <v>33.30067834285714</v>
+      </c>
+      <c r="Q12">
+        <v>37.10067834285714</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1197839643901023</v>
+      </c>
+      <c r="T12">
+        <v>1.096652078390473</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.3</v>
+      </c>
+      <c r="W12">
+        <v>0.03129</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>13.41553260463364</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1107187486687692</v>
+      </c>
+      <c r="C13">
+        <v>778.0642859201735</v>
+      </c>
+      <c r="D13">
+        <v>768.9562859201735</v>
+      </c>
+      <c r="E13">
+        <v>-5.207999999999998</v>
+      </c>
+      <c r="F13">
+        <v>94.292</v>
+      </c>
+      <c r="G13">
+        <v>103.4</v>
+      </c>
+      <c r="H13">
+        <v>757.7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K13">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L13">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M13">
+        <v>4.3185736</v>
+      </c>
+      <c r="N13">
+        <v>47.08550803265306</v>
+      </c>
+      <c r="O13">
+        <v>14.12565240979592</v>
+      </c>
+      <c r="P13">
+        <v>32.95985562285714</v>
+      </c>
+      <c r="Q13">
+        <v>36.75985562285715</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1204406164817631</v>
+      </c>
+      <c r="T13">
+        <v>1.105544195324023</v>
+      </c>
+      <c r="U13">
+        <v>0.0458</v>
+      </c>
+      <c r="V13">
+        <v>0.3</v>
+      </c>
+      <c r="W13">
+        <v>0.03206</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>11.903023172432</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1104259293864462</v>
+      </c>
+      <c r="C14">
+        <v>772.6359132309766</v>
+      </c>
+      <c r="D14">
+        <v>772.0999132309767</v>
+      </c>
+      <c r="E14">
+        <v>3.364000000000004</v>
+      </c>
+      <c r="F14">
+        <v>102.864</v>
+      </c>
+      <c r="G14">
+        <v>103.4</v>
+      </c>
+      <c r="H14">
+        <v>757.7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K14">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L14">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M14">
+        <v>4.7111712</v>
+      </c>
+      <c r="N14">
+        <v>46.69291043265306</v>
+      </c>
+      <c r="O14">
+        <v>14.00787312979592</v>
+      </c>
+      <c r="P14">
+        <v>32.68503730285714</v>
+      </c>
+      <c r="Q14">
+        <v>36.48503730285714</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.121112192484598</v>
+      </c>
+      <c r="T14">
+        <v>1.114638405824244</v>
+      </c>
+      <c r="U14">
+        <v>0.0458</v>
+      </c>
+      <c r="V14">
+        <v>0.3</v>
+      </c>
+      <c r="W14">
+        <v>0.03206</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>10.91110457472933</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1101331101041232</v>
+      </c>
+      <c r="C15">
+        <v>767.233349445715</v>
+      </c>
+      <c r="D15">
+        <v>775.2693494457151</v>
+      </c>
+      <c r="E15">
+        <v>11.93600000000001</v>
+      </c>
+      <c r="F15">
+        <v>111.436</v>
+      </c>
+      <c r="G15">
+        <v>103.4</v>
+      </c>
+      <c r="H15">
+        <v>757.7</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K15">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L15">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M15">
+        <v>5.1037688</v>
+      </c>
+      <c r="N15">
+        <v>46.30031283265306</v>
+      </c>
+      <c r="O15">
+        <v>13.89009384979592</v>
+      </c>
+      <c r="P15">
+        <v>32.41021898285715</v>
+      </c>
+      <c r="Q15">
+        <v>36.21021898285715</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1217992070162336</v>
+      </c>
+      <c r="T15">
+        <v>1.123941678634815</v>
+      </c>
+      <c r="U15">
+        <v>0.0458</v>
+      </c>
+      <c r="V15">
+        <v>0.3</v>
+      </c>
+      <c r="W15">
+        <v>0.03206</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>10.07178883821169</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1100558908218003</v>
+      </c>
+      <c r="C16">
+        <v>759.5015009346761</v>
+      </c>
+      <c r="D16">
+        <v>776.1095009346761</v>
+      </c>
+      <c r="E16">
+        <v>20.50800000000002</v>
+      </c>
+      <c r="F16">
+        <v>120.008</v>
+      </c>
+      <c r="G16">
+        <v>103.4</v>
+      </c>
+      <c r="H16">
+        <v>757.7</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K16">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L16">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M16">
+        <v>5.760384000000001</v>
+      </c>
+      <c r="N16">
+        <v>45.64369763265306</v>
+      </c>
+      <c r="O16">
+        <v>13.69310928979592</v>
+      </c>
+      <c r="P16">
+        <v>31.95058834285714</v>
+      </c>
+      <c r="Q16">
+        <v>35.75058834285714</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1225021986300003</v>
+      </c>
+      <c r="T16">
+        <v>1.133461306627027</v>
+      </c>
+      <c r="U16">
+        <v>0.048</v>
+      </c>
+      <c r="V16">
+        <v>0.3</v>
+      </c>
+      <c r="W16">
+        <v>0.0336</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>8.923724812903629</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1097784715394773</v>
+      </c>
+      <c r="C17">
+        <v>753.9629241133306</v>
+      </c>
+      <c r="D17">
+        <v>779.1429241133307</v>
+      </c>
+      <c r="E17">
+        <v>29.08000000000001</v>
+      </c>
+      <c r="F17">
+        <v>128.58</v>
+      </c>
+      <c r="G17">
+        <v>103.4</v>
+      </c>
+      <c r="H17">
+        <v>757.7</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K17">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L17">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M17">
+        <v>6.17184</v>
+      </c>
+      <c r="N17">
+        <v>45.23224163265306</v>
+      </c>
+      <c r="O17">
+        <v>13.56967248979592</v>
+      </c>
+      <c r="P17">
+        <v>31.66256914285714</v>
+      </c>
+      <c r="Q17">
+        <v>35.46256914285715</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1232217312229145</v>
+      </c>
+      <c r="T17">
+        <v>1.143204925866115</v>
+      </c>
+      <c r="U17">
+        <v>0.048</v>
+      </c>
+      <c r="V17">
+        <v>0.3</v>
+      </c>
+      <c r="W17">
+        <v>0.0336</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>8.32880982537672</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1095010522571543</v>
+      </c>
+      <c r="C18">
+        <v>748.4481525976871</v>
+      </c>
+      <c r="D18">
+        <v>782.2001525976872</v>
+      </c>
+      <c r="E18">
+        <v>37.65200000000002</v>
+      </c>
+      <c r="F18">
+        <v>137.152</v>
+      </c>
+      <c r="G18">
+        <v>103.4</v>
+      </c>
+      <c r="H18">
+        <v>757.7</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K18">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L18">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M18">
+        <v>6.583296000000001</v>
+      </c>
+      <c r="N18">
+        <v>44.82078563265306</v>
+      </c>
+      <c r="O18">
+        <v>13.44623568979592</v>
+      </c>
+      <c r="P18">
+        <v>31.37454994285714</v>
+      </c>
+      <c r="Q18">
+        <v>35.17454994285714</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1239583955442313</v>
+      </c>
+      <c r="T18">
+        <v>1.153180536039467</v>
+      </c>
+      <c r="U18">
+        <v>0.048</v>
+      </c>
+      <c r="V18">
+        <v>0.3</v>
+      </c>
+      <c r="W18">
+        <v>0.0336</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>7.808259211290674</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1094021329748314</v>
+      </c>
+      <c r="C19">
+        <v>740.9720780955111</v>
+      </c>
+      <c r="D19">
+        <v>783.2960780955111</v>
+      </c>
+      <c r="E19">
+        <v>46.22400000000002</v>
+      </c>
+      <c r="F19">
+        <v>145.724</v>
+      </c>
+      <c r="G19">
+        <v>103.4</v>
+      </c>
+      <c r="H19">
+        <v>757.7</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K19">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L19">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M19">
+        <v>7.213338000000001</v>
+      </c>
+      <c r="N19">
+        <v>44.19074363265306</v>
+      </c>
+      <c r="O19">
+        <v>13.25722308979592</v>
+      </c>
+      <c r="P19">
+        <v>30.93352054285714</v>
+      </c>
+      <c r="Q19">
+        <v>34.73352054285715</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1247128108130498</v>
+      </c>
+      <c r="T19">
+        <v>1.163396522361574</v>
+      </c>
+      <c r="U19">
+        <v>0.0495</v>
+      </c>
+      <c r="V19">
+        <v>0.3</v>
+      </c>
+      <c r="W19">
+        <v>0.03465</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>7.126254396044252</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1091352136925084</v>
+      </c>
+      <c r="C20">
+        <v>735.3726549319972</v>
+      </c>
+      <c r="D20">
+        <v>786.2686549319972</v>
+      </c>
+      <c r="E20">
+        <v>54.79599999999999</v>
+      </c>
+      <c r="F20">
+        <v>154.296</v>
+      </c>
+      <c r="G20">
+        <v>103.4</v>
+      </c>
+      <c r="H20">
+        <v>757.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K20">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L20">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M20">
+        <v>7.637652</v>
+      </c>
+      <c r="N20">
+        <v>43.76642963265306</v>
+      </c>
+      <c r="O20">
+        <v>13.12992888979592</v>
+      </c>
+      <c r="P20">
+        <v>30.63650074285714</v>
+      </c>
+      <c r="Q20">
+        <v>34.43650074285715</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1254856264542785</v>
+      </c>
+      <c r="T20">
+        <v>1.173861679081782</v>
+      </c>
+      <c r="U20">
+        <v>0.0495</v>
+      </c>
+      <c r="V20">
+        <v>0.3</v>
+      </c>
+      <c r="W20">
+        <v>0.03465</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>6.730351374041794</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1088682944101854</v>
+      </c>
+      <c r="C21">
+        <v>729.7958793320504</v>
+      </c>
+      <c r="D21">
+        <v>789.2638793320505</v>
+      </c>
+      <c r="E21">
+        <v>63.36800000000002</v>
+      </c>
+      <c r="F21">
+        <v>162.868</v>
+      </c>
+      <c r="G21">
+        <v>103.4</v>
+      </c>
+      <c r="H21">
+        <v>757.7</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K21">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L21">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M21">
+        <v>8.061966000000002</v>
+      </c>
+      <c r="N21">
+        <v>43.34211563265306</v>
+      </c>
+      <c r="O21">
+        <v>13.00263468979592</v>
+      </c>
+      <c r="P21">
+        <v>30.33948094285714</v>
+      </c>
+      <c r="Q21">
+        <v>34.13948094285715</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1262775239631919</v>
+      </c>
+      <c r="T21">
+        <v>1.184585234733352</v>
+      </c>
+      <c r="U21">
+        <v>0.0495</v>
+      </c>
+      <c r="V21">
+        <v>0.3</v>
+      </c>
+      <c r="W21">
+        <v>0.03465</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>6.376122354355384</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1087973751278625</v>
+      </c>
+      <c r="C22">
+        <v>722.0235382875957</v>
+      </c>
+      <c r="D22">
+        <v>790.0635382875957</v>
+      </c>
+      <c r="E22">
+        <v>71.94000000000003</v>
+      </c>
+      <c r="F22">
+        <v>171.44</v>
+      </c>
+      <c r="G22">
+        <v>103.4</v>
+      </c>
+      <c r="H22">
+        <v>757.7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K22">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L22">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M22">
+        <v>8.726296000000001</v>
+      </c>
+      <c r="N22">
+        <v>42.67778563265306</v>
+      </c>
+      <c r="O22">
+        <v>12.80333568979592</v>
+      </c>
+      <c r="P22">
+        <v>29.87444994285714</v>
+      </c>
+      <c r="Q22">
+        <v>33.67444994285714</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1270892189098281</v>
+      </c>
+      <c r="T22">
+        <v>1.195576879276212</v>
+      </c>
+      <c r="U22">
+        <v>0.0509</v>
+      </c>
+      <c r="V22">
+        <v>0.3</v>
+      </c>
+      <c r="W22">
+        <v>0.03563</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>5.890710289068013</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1085402558455395</v>
+      </c>
+      <c r="C23">
+        <v>716.3643548164591</v>
+      </c>
+      <c r="D23">
+        <v>792.9763548164592</v>
+      </c>
+      <c r="E23">
+        <v>80.512</v>
+      </c>
+      <c r="F23">
+        <v>180.012</v>
+      </c>
+      <c r="G23">
+        <v>103.4</v>
+      </c>
+      <c r="H23">
+        <v>757.7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K23">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L23">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M23">
+        <v>9.1626108</v>
+      </c>
+      <c r="N23">
+        <v>42.24147083265306</v>
+      </c>
+      <c r="O23">
+        <v>12.67244124979592</v>
+      </c>
+      <c r="P23">
+        <v>29.56902958285715</v>
+      </c>
+      <c r="Q23">
+        <v>33.36902958285715</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1279214630956196</v>
+      </c>
+      <c r="T23">
+        <v>1.20684679330117</v>
+      </c>
+      <c r="U23">
+        <v>0.0509</v>
+      </c>
+      <c r="V23">
+        <v>0.3</v>
+      </c>
+      <c r="W23">
+        <v>0.03563</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>5.610200275302872</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1082831365632165</v>
+      </c>
+      <c r="C24">
+        <v>710.726728843515</v>
+      </c>
+      <c r="D24">
+        <v>795.9107288435151</v>
+      </c>
+      <c r="E24">
+        <v>89.084</v>
+      </c>
+      <c r="F24">
+        <v>188.584</v>
+      </c>
+      <c r="G24">
+        <v>103.4</v>
+      </c>
+      <c r="H24">
+        <v>757.7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K24">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L24">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M24">
+        <v>9.598925600000001</v>
+      </c>
+      <c r="N24">
+        <v>41.80515603265306</v>
+      </c>
+      <c r="O24">
+        <v>12.54154680979592</v>
+      </c>
+      <c r="P24">
+        <v>29.26360922285714</v>
+      </c>
+      <c r="Q24">
+        <v>33.06360922285715</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1287750468759186</v>
+      </c>
+      <c r="T24">
+        <v>1.218405679480613</v>
+      </c>
+      <c r="U24">
+        <v>0.0509</v>
+      </c>
+      <c r="V24">
+        <v>0.3</v>
+      </c>
+      <c r="W24">
+        <v>0.03563</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>5.355191171880013</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1080260172808936</v>
+      </c>
+      <c r="C25">
+        <v>705.1109005753515</v>
+      </c>
+      <c r="D25">
+        <v>798.8669005753516</v>
+      </c>
+      <c r="E25">
+        <v>97.65600000000001</v>
+      </c>
+      <c r="F25">
+        <v>197.156</v>
+      </c>
+      <c r="G25">
+        <v>103.4</v>
+      </c>
+      <c r="H25">
+        <v>757.7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K25">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L25">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M25">
+        <v>10.0352404</v>
+      </c>
+      <c r="N25">
+        <v>41.36884123265306</v>
+      </c>
+      <c r="O25">
+        <v>12.41065236979592</v>
+      </c>
+      <c r="P25">
+        <v>28.95818886285714</v>
+      </c>
+      <c r="Q25">
+        <v>32.75818886285715</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1296508016634981</v>
+      </c>
+      <c r="T25">
+        <v>1.230264796469912</v>
+      </c>
+      <c r="U25">
+        <v>0.0509</v>
+      </c>
+      <c r="V25">
+        <v>0.3</v>
+      </c>
+      <c r="W25">
+        <v>0.03563</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>5.122356773102621</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1077688979985706</v>
+      </c>
+      <c r="C26">
+        <v>699.5171138005617</v>
+      </c>
+      <c r="D26">
+        <v>801.8451138005616</v>
+      </c>
+      <c r="E26">
+        <v>106.228</v>
+      </c>
+      <c r="F26">
+        <v>205.728</v>
+      </c>
+      <c r="G26">
+        <v>103.4</v>
+      </c>
+      <c r="H26">
+        <v>757.7</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K26">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L26">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M26">
+        <v>10.4715552</v>
+      </c>
+      <c r="N26">
+        <v>40.93252643265306</v>
+      </c>
+      <c r="O26">
+        <v>12.27975792979592</v>
+      </c>
+      <c r="P26">
+        <v>28.65276850285714</v>
+      </c>
+      <c r="Q26">
+        <v>32.45276850285715</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1305496026296982</v>
+      </c>
+      <c r="T26">
+        <v>1.242435995485246</v>
+      </c>
+      <c r="U26">
+        <v>0.0509</v>
+      </c>
+      <c r="V26">
+        <v>0.3</v>
+      </c>
+      <c r="W26">
+        <v>0.03563</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>4.908925240890012</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1075117787162476</v>
+      </c>
+      <c r="C27">
+        <v>693.9456159567635</v>
+      </c>
+      <c r="D27">
+        <v>804.8456159567635</v>
+      </c>
+      <c r="E27">
+        <v>114.8</v>
+      </c>
+      <c r="F27">
+        <v>214.3</v>
+      </c>
+      <c r="G27">
+        <v>103.4</v>
+      </c>
+      <c r="H27">
+        <v>757.7</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K27">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L27">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M27">
+        <v>10.90787</v>
+      </c>
+      <c r="N27">
+        <v>40.49621163265306</v>
+      </c>
+      <c r="O27">
+        <v>12.14886348979592</v>
+      </c>
+      <c r="P27">
+        <v>28.34734814285714</v>
+      </c>
+      <c r="Q27">
+        <v>32.14734814285715</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1314723716216635</v>
+      </c>
+      <c r="T27">
+        <v>1.254931759807655</v>
+      </c>
+      <c r="U27">
+        <v>0.0509</v>
+      </c>
+      <c r="V27">
+        <v>0.3</v>
+      </c>
+      <c r="W27">
+        <v>0.03563</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>4.712568231254411</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1072546594339247</v>
+      </c>
+      <c r="C28">
+        <v>688.3966581991303</v>
+      </c>
+      <c r="D28">
+        <v>807.8686581991304</v>
+      </c>
+      <c r="E28">
+        <v>123.372</v>
+      </c>
+      <c r="F28">
+        <v>222.872</v>
+      </c>
+      <c r="G28">
+        <v>103.4</v>
+      </c>
+      <c r="H28">
+        <v>757.7</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K28">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L28">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M28">
+        <v>11.3441848</v>
+      </c>
+      <c r="N28">
+        <v>40.05989683265306</v>
+      </c>
+      <c r="O28">
+        <v>12.01796904979592</v>
+      </c>
+      <c r="P28">
+        <v>28.04192778285714</v>
+      </c>
+      <c r="Q28">
+        <v>31.84192778285715</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1324200803161144</v>
+      </c>
+      <c r="T28">
+        <v>1.267765247490129</v>
+      </c>
+      <c r="U28">
+        <v>0.0509</v>
+      </c>
+      <c r="V28">
+        <v>0.3</v>
+      </c>
+      <c r="W28">
+        <v>0.03563</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>4.531315606975395</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1074889401516017</v>
+      </c>
+      <c r="C29">
+        <v>677.0692211722385</v>
+      </c>
+      <c r="D29">
+        <v>805.1132211722386</v>
+      </c>
+      <c r="E29">
+        <v>131.944</v>
+      </c>
+      <c r="F29">
+        <v>231.444</v>
+      </c>
+      <c r="G29">
+        <v>103.4</v>
+      </c>
+      <c r="H29">
+        <v>757.7</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K29">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L29">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M29">
+        <v>12.382254</v>
+      </c>
+      <c r="N29">
+        <v>39.02182763265306</v>
+      </c>
+      <c r="O29">
+        <v>11.70654828979592</v>
+      </c>
+      <c r="P29">
+        <v>27.31527934285714</v>
+      </c>
+      <c r="Q29">
+        <v>31.11527934285714</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1333937536323311</v>
+      </c>
+      <c r="T29">
+        <v>1.280950337574863</v>
+      </c>
+      <c r="U29">
+        <v>0.0535</v>
+      </c>
+      <c r="V29">
+        <v>0.3</v>
+      </c>
+      <c r="W29">
+        <v>0.03745</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>4.151431688661294</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1072500208692787</v>
+      </c>
+      <c r="C30">
+        <v>671.3074039968511</v>
+      </c>
+      <c r="D30">
+        <v>807.9234039968512</v>
+      </c>
+      <c r="E30">
+        <v>140.516</v>
+      </c>
+      <c r="F30">
+        <v>240.016</v>
+      </c>
+      <c r="G30">
+        <v>103.4</v>
+      </c>
+      <c r="H30">
+        <v>757.7</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K30">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L30">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M30">
+        <v>12.840856</v>
+      </c>
+      <c r="N30">
+        <v>38.56322563265306</v>
+      </c>
+      <c r="O30">
+        <v>11.56896768979592</v>
+      </c>
+      <c r="P30">
+        <v>26.99425794285714</v>
+      </c>
+      <c r="Q30">
+        <v>30.79425794285714</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1343944734295538</v>
+      </c>
+      <c r="T30">
+        <v>1.29450168016195</v>
+      </c>
+      <c r="U30">
+        <v>0.0535</v>
+      </c>
+      <c r="V30">
+        <v>0.3</v>
+      </c>
+      <c r="W30">
+        <v>0.03745</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>4.003166271209104</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1075592015869558</v>
+      </c>
+      <c r="C31">
+        <v>659.1025180396177</v>
+      </c>
+      <c r="D31">
+        <v>804.2905180396177</v>
+      </c>
+      <c r="E31">
+        <v>149.088</v>
+      </c>
+      <c r="F31">
+        <v>248.588</v>
+      </c>
+      <c r="G31">
+        <v>103.4</v>
+      </c>
+      <c r="H31">
+        <v>757.7</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K31">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L31">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M31">
+        <v>13.9706456</v>
+      </c>
+      <c r="N31">
+        <v>37.43343603265306</v>
+      </c>
+      <c r="O31">
+        <v>11.23003080979592</v>
+      </c>
+      <c r="P31">
+        <v>26.20340522285714</v>
+      </c>
+      <c r="Q31">
+        <v>30.00340522285715</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1354233825168391</v>
+      </c>
+      <c r="T31">
+        <v>1.308434750709238</v>
+      </c>
+      <c r="U31">
+        <v>0.0562</v>
+      </c>
+      <c r="V31">
+        <v>0.3</v>
+      </c>
+      <c r="W31">
+        <v>0.03934</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>3.679434945558498</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1073391823046328</v>
+      </c>
+      <c r="C32">
+        <v>653.1123904315546</v>
+      </c>
+      <c r="D32">
+        <v>806.8723904315545</v>
+      </c>
+      <c r="E32">
+        <v>157.66</v>
+      </c>
+      <c r="F32">
+        <v>257.16</v>
+      </c>
+      <c r="G32">
+        <v>103.4</v>
+      </c>
+      <c r="H32">
+        <v>757.7</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K32">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L32">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M32">
+        <v>14.452392</v>
+      </c>
+      <c r="N32">
+        <v>36.95168963265306</v>
+      </c>
+      <c r="O32">
+        <v>11.08550688979592</v>
+      </c>
+      <c r="P32">
+        <v>25.86618274285714</v>
+      </c>
+      <c r="Q32">
+        <v>29.66618274285715</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1364816890066183</v>
+      </c>
+      <c r="T32">
+        <v>1.322765908986447</v>
+      </c>
+      <c r="U32">
+        <v>0.0562</v>
+      </c>
+      <c r="V32">
+        <v>0.3</v>
+      </c>
+      <c r="W32">
+        <v>0.03934</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>3.55678711403988</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1081390630223098</v>
+      </c>
+      <c r="C33">
+        <v>635.2324817491929</v>
+      </c>
+      <c r="D33">
+        <v>797.564481749193</v>
+      </c>
+      <c r="E33">
+        <v>166.232</v>
+      </c>
+      <c r="F33">
+        <v>265.732</v>
+      </c>
+      <c r="G33">
+        <v>103.4</v>
+      </c>
+      <c r="H33">
+        <v>757.7</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K33">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L33">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M33">
+        <v>16.1830788</v>
+      </c>
+      <c r="N33">
+        <v>35.22100283265306</v>
+      </c>
+      <c r="O33">
+        <v>10.56630084979592</v>
+      </c>
+      <c r="P33">
+        <v>24.65470198285714</v>
+      </c>
+      <c r="Q33">
+        <v>28.45470198285715</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1375706710468259</v>
+      </c>
+      <c r="T33">
+        <v>1.33751246315575</v>
+      </c>
+      <c r="U33">
+        <v>0.0609</v>
+      </c>
+      <c r="V33">
+        <v>0.3</v>
+      </c>
+      <c r="W33">
+        <v>0.04263</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>3.176409277118088</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1079519437399869</v>
+      </c>
+      <c r="C34">
+        <v>628.8186234493357</v>
+      </c>
+      <c r="D34">
+        <v>799.7226234493357</v>
+      </c>
+      <c r="E34">
+        <v>174.804</v>
+      </c>
+      <c r="F34">
+        <v>274.304</v>
+      </c>
+      <c r="G34">
+        <v>103.4</v>
+      </c>
+      <c r="H34">
+        <v>757.7</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K34">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L34">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M34">
+        <v>16.7051136</v>
+      </c>
+      <c r="N34">
+        <v>34.69896803265306</v>
+      </c>
+      <c r="O34">
+        <v>10.40969040979592</v>
+      </c>
+      <c r="P34">
+        <v>24.28927762285714</v>
+      </c>
+      <c r="Q34">
+        <v>28.08927762285715</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1386916819705689</v>
+      </c>
+      <c r="T34">
+        <v>1.352692739506503</v>
+      </c>
+      <c r="U34">
+        <v>0.0609</v>
+      </c>
+      <c r="V34">
+        <v>0.3</v>
+      </c>
+      <c r="W34">
+        <v>0.04263</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>3.077146487208147</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1099131244576639</v>
+      </c>
+      <c r="C35">
+        <v>598.1916146087008</v>
+      </c>
+      <c r="D35">
+        <v>777.6676146087009</v>
+      </c>
+      <c r="E35">
+        <v>183.376</v>
+      </c>
+      <c r="F35">
+        <v>282.876</v>
+      </c>
+      <c r="G35">
+        <v>103.4</v>
+      </c>
+      <c r="H35">
+        <v>757.7</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K35">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L35">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M35">
+        <v>19.8578952</v>
+      </c>
+      <c r="N35">
+        <v>31.54618643265306</v>
+      </c>
+      <c r="O35">
+        <v>9.463855929795917</v>
+      </c>
+      <c r="P35">
+        <v>22.08233050285714</v>
+      </c>
+      <c r="Q35">
+        <v>25.88233050285714</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1398461559069611</v>
+      </c>
+      <c r="T35">
+        <v>1.36832615843489</v>
+      </c>
+      <c r="U35">
+        <v>0.0702</v>
+      </c>
+      <c r="V35">
+        <v>0.3</v>
+      </c>
+      <c r="W35">
+        <v>0.04914</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>2.588596682323767</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1097911051753409</v>
+      </c>
+      <c r="C36">
+        <v>590.9562671933593</v>
+      </c>
+      <c r="D36">
+        <v>779.0042671933594</v>
+      </c>
+      <c r="E36">
+        <v>191.948</v>
+      </c>
+      <c r="F36">
+        <v>291.448</v>
+      </c>
+      <c r="G36">
+        <v>103.4</v>
+      </c>
+      <c r="H36">
+        <v>757.7</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K36">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L36">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M36">
+        <v>20.4596496</v>
+      </c>
+      <c r="N36">
+        <v>30.94443203265306</v>
+      </c>
+      <c r="O36">
+        <v>9.283329609795917</v>
+      </c>
+      <c r="P36">
+        <v>21.66110242285714</v>
+      </c>
+      <c r="Q36">
+        <v>25.46110242285715</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1410356139020317</v>
+      </c>
+      <c r="T36">
+        <v>1.384433317330804</v>
+      </c>
+      <c r="U36">
+        <v>0.0702</v>
+      </c>
+      <c r="V36">
+        <v>0.3</v>
+      </c>
+      <c r="W36">
+        <v>0.04914</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>2.512461485784832</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.110820585893018</v>
+      </c>
+      <c r="C37">
+        <v>571.2489804955399</v>
+      </c>
+      <c r="D37">
+        <v>767.8689804955399</v>
+      </c>
+      <c r="E37">
+        <v>200.52</v>
+      </c>
+      <c r="F37">
+        <v>300.02</v>
+      </c>
+      <c r="G37">
+        <v>103.4</v>
+      </c>
+      <c r="H37">
+        <v>757.7</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K37">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L37">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M37">
+        <v>22.471498</v>
+      </c>
+      <c r="N37">
+        <v>28.93258363265306</v>
+      </c>
+      <c r="O37">
+        <v>8.679775089795918</v>
+      </c>
+      <c r="P37">
+        <v>20.25280854285714</v>
+      </c>
+      <c r="Q37">
+        <v>24.05280854285715</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1422616706046431</v>
+      </c>
+      <c r="T37">
+        <v>1.401036081115823</v>
+      </c>
+      <c r="U37">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V37">
+        <v>0.3</v>
+      </c>
+      <c r="W37">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>2.28752358354806</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.110731466610695</v>
+      </c>
+      <c r="C38">
+        <v>563.6283295460211</v>
+      </c>
+      <c r="D38">
+        <v>768.8203295460211</v>
+      </c>
+      <c r="E38">
+        <v>209.092</v>
+      </c>
+      <c r="F38">
+        <v>308.592</v>
+      </c>
+      <c r="G38">
+        <v>103.4</v>
+      </c>
+      <c r="H38">
+        <v>757.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K38">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L38">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M38">
+        <v>23.1135408</v>
+      </c>
+      <c r="N38">
+        <v>28.29054083265306</v>
+      </c>
+      <c r="O38">
+        <v>8.487162249795919</v>
+      </c>
+      <c r="P38">
+        <v>19.80337858285715</v>
+      </c>
+      <c r="Q38">
+        <v>23.60337858285715</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.143526041579211</v>
+      </c>
+      <c r="T38">
+        <v>1.418157681269124</v>
+      </c>
+      <c r="U38">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V38">
+        <v>0.3</v>
+      </c>
+      <c r="W38">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>2.223981261782837</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1106423473283721</v>
+      </c>
+      <c r="C39">
+        <v>556.0100388630523</v>
+      </c>
+      <c r="D39">
+        <v>769.7740388630523</v>
+      </c>
+      <c r="E39">
+        <v>217.664</v>
+      </c>
+      <c r="F39">
+        <v>317.164</v>
+      </c>
+      <c r="G39">
+        <v>103.4</v>
+      </c>
+      <c r="H39">
+        <v>757.7</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K39">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L39">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M39">
+        <v>23.7555836</v>
+      </c>
+      <c r="N39">
+        <v>27.64849803265306</v>
+      </c>
+      <c r="O39">
+        <v>8.294549409795918</v>
+      </c>
+      <c r="P39">
+        <v>19.35394862285715</v>
+      </c>
+      <c r="Q39">
+        <v>23.15394862285715</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1448305513148763</v>
+      </c>
+      <c r="T39">
+        <v>1.435822824284434</v>
+      </c>
+      <c r="U39">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V39">
+        <v>0.3</v>
+      </c>
+      <c r="W39">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>2.16387366011303</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1105532280460491</v>
+      </c>
+      <c r="C40">
+        <v>548.394117241161</v>
+      </c>
+      <c r="D40">
+        <v>770.730117241161</v>
+      </c>
+      <c r="E40">
+        <v>226.236</v>
+      </c>
+      <c r="F40">
+        <v>325.736</v>
+      </c>
+      <c r="G40">
+        <v>103.4</v>
+      </c>
+      <c r="H40">
+        <v>757.7</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K40">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L40">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M40">
+        <v>24.3976264</v>
+      </c>
+      <c r="N40">
+        <v>27.00645523265306</v>
+      </c>
+      <c r="O40">
+        <v>8.101936569795917</v>
+      </c>
+      <c r="P40">
+        <v>18.90451866285714</v>
+      </c>
+      <c r="Q40">
+        <v>22.70451866285715</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1461771420097566</v>
+      </c>
+      <c r="T40">
+        <v>1.454057810622819</v>
+      </c>
+      <c r="U40">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V40">
+        <v>0.3</v>
+      </c>
+      <c r="W40">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>2.106929616425845</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1104641087637261</v>
+      </c>
+      <c r="C41">
+        <v>540.7805735186216</v>
+      </c>
+      <c r="D41">
+        <v>771.6885735186218</v>
+      </c>
+      <c r="E41">
+        <v>234.808</v>
+      </c>
+      <c r="F41">
+        <v>334.308</v>
+      </c>
+      <c r="G41">
+        <v>103.4</v>
+      </c>
+      <c r="H41">
+        <v>757.7</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K41">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L41">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M41">
+        <v>25.0396692</v>
+      </c>
+      <c r="N41">
+        <v>26.36441243265306</v>
+      </c>
+      <c r="O41">
+        <v>7.909323729795917</v>
+      </c>
+      <c r="P41">
+        <v>18.45508870285714</v>
+      </c>
+      <c r="Q41">
+        <v>22.25508870285714</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1475678832192232</v>
+      </c>
+      <c r="T41">
+        <v>1.472890665365741</v>
+      </c>
+      <c r="U41">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V41">
+        <v>0.3</v>
+      </c>
+      <c r="W41">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>2.052905780107233</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1103749894814032</v>
+      </c>
+      <c r="C42">
+        <v>533.1694165777278</v>
+      </c>
+      <c r="D42">
+        <v>772.6494165777279</v>
+      </c>
+      <c r="E42">
+        <v>243.3800000000001</v>
+      </c>
+      <c r="F42">
+        <v>342.8800000000001</v>
+      </c>
+      <c r="G42">
+        <v>103.4</v>
+      </c>
+      <c r="H42">
+        <v>757.7</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K42">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L42">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M42">
+        <v>25.681712</v>
+      </c>
+      <c r="N42">
+        <v>25.72236963265306</v>
+      </c>
+      <c r="O42">
+        <v>7.716710889795918</v>
+      </c>
+      <c r="P42">
+        <v>18.00565874285714</v>
+      </c>
+      <c r="Q42">
+        <v>21.80565874285715</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1490049824690053</v>
+      </c>
+      <c r="T42">
+        <v>1.492351281933428</v>
+      </c>
+      <c r="U42">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V42">
+        <v>0.3</v>
+      </c>
+      <c r="W42">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>2.001583135604553</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1149639701990802</v>
+      </c>
+      <c r="C43">
+        <v>478.0442594230813</v>
+      </c>
+      <c r="D43">
+        <v>726.0962594230814</v>
+      </c>
+      <c r="E43">
+        <v>251.9520000000001</v>
+      </c>
+      <c r="F43">
+        <v>351.4520000000001</v>
+      </c>
+      <c r="G43">
+        <v>103.4</v>
+      </c>
+      <c r="H43">
+        <v>757.7</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K43">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L43">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M43">
+        <v>32.0524224</v>
+      </c>
+      <c r="N43">
+        <v>19.35165923265306</v>
+      </c>
+      <c r="O43">
+        <v>5.805497769795917</v>
+      </c>
+      <c r="P43">
+        <v>13.54616146285714</v>
+      </c>
+      <c r="Q43">
+        <v>17.34616146285714</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1504907969475935</v>
+      </c>
+      <c r="T43">
+        <v>1.512471580418663</v>
+      </c>
+      <c r="U43">
+        <v>0.0912</v>
+      </c>
+      <c r="V43">
+        <v>0.3</v>
+      </c>
+      <c r="W43">
+        <v>0.06383999999999999</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>1.603750287299754</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1149889509167572</v>
+      </c>
+      <c r="C44">
+        <v>469.2341880827524</v>
+      </c>
+      <c r="D44">
+        <v>725.8581880827525</v>
+      </c>
+      <c r="E44">
+        <v>260.524</v>
+      </c>
+      <c r="F44">
+        <v>360.024</v>
+      </c>
+      <c r="G44">
+        <v>103.4</v>
+      </c>
+      <c r="H44">
+        <v>757.7</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K44">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L44">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M44">
+        <v>32.8341888</v>
+      </c>
+      <c r="N44">
+        <v>18.56989283265306</v>
+      </c>
+      <c r="O44">
+        <v>5.570967849795918</v>
+      </c>
+      <c r="P44">
+        <v>12.99892498285714</v>
+      </c>
+      <c r="Q44">
+        <v>16.79892498285715</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1520278464082021</v>
+      </c>
+      <c r="T44">
+        <v>1.53328568229994</v>
+      </c>
+      <c r="U44">
+        <v>0.0912</v>
+      </c>
+      <c r="V44">
+        <v>0.3</v>
+      </c>
+      <c r="W44">
+        <v>0.06383999999999999</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>1.56556575664976</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1150139316344343</v>
+      </c>
+      <c r="C45">
+        <v>460.424272808193</v>
+      </c>
+      <c r="D45">
+        <v>725.620272808193</v>
+      </c>
+      <c r="E45">
+        <v>269.096</v>
+      </c>
+      <c r="F45">
+        <v>368.596</v>
+      </c>
+      <c r="G45">
+        <v>103.4</v>
+      </c>
+      <c r="H45">
+        <v>757.7</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K45">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L45">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M45">
+        <v>33.6159552</v>
+      </c>
+      <c r="N45">
+        <v>17.78812643265306</v>
+      </c>
+      <c r="O45">
+        <v>5.336437929795918</v>
+      </c>
+      <c r="P45">
+        <v>12.45168850285714</v>
+      </c>
+      <c r="Q45">
+        <v>16.25168850285715</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.153618827428832</v>
+      </c>
+      <c r="T45">
+        <v>1.554830103545473</v>
+      </c>
+      <c r="U45">
+        <v>0.0912</v>
+      </c>
+      <c r="V45">
+        <v>0.3</v>
+      </c>
+      <c r="W45">
+        <v>0.06383999999999999</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>1.52915725068116</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1391494656506305</v>
+      </c>
+      <c r="C46">
+        <v>277.3298409880125</v>
+      </c>
+      <c r="D46">
+        <v>551.0978409880125</v>
+      </c>
+      <c r="E46">
+        <v>277.668</v>
+      </c>
+      <c r="F46">
+        <v>377.168</v>
+      </c>
+      <c r="G46">
+        <v>103.4</v>
+      </c>
+      <c r="H46">
+        <v>757.7</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K46">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L46">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M46">
+        <v>59.06450880000001</v>
+      </c>
+      <c r="N46">
+        <v>-7.660427167346946</v>
+      </c>
+      <c r="O46">
+        <v>-2.298128150204084</v>
+      </c>
+      <c r="P46">
+        <v>-5.362299017142862</v>
+      </c>
+      <c r="Q46">
+        <v>-1.562299017142857</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.157563740845436</v>
+      </c>
+      <c r="T46">
+        <v>1.608250524859374</v>
+      </c>
+      <c r="U46">
+        <v>0.1566</v>
+      </c>
+      <c r="V46">
+        <v>0.2610912170964489</v>
+      </c>
+      <c r="W46">
+        <v>0.1157131154026961</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.870304056988163</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1403274656506305</v>
+      </c>
+      <c r="C47">
+        <v>262.3635785830212</v>
+      </c>
+      <c r="D47">
+        <v>544.7035785830212</v>
+      </c>
+      <c r="E47">
+        <v>286.24</v>
+      </c>
+      <c r="F47">
+        <v>385.74</v>
+      </c>
+      <c r="G47">
+        <v>103.4</v>
+      </c>
+      <c r="H47">
+        <v>757.7</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K47">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L47">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M47">
+        <v>60.40688400000001</v>
+      </c>
+      <c r="N47">
+        <v>-9.002802367346945</v>
+      </c>
+      <c r="O47">
+        <v>-2.700840710204083</v>
+      </c>
+      <c r="P47">
+        <v>-6.301961657142861</v>
+      </c>
+      <c r="Q47">
+        <v>-2.501961657142857</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1597230815880803</v>
+      </c>
+      <c r="T47">
+        <v>1.63749144349318</v>
+      </c>
+      <c r="U47">
+        <v>0.1566</v>
+      </c>
+      <c r="V47">
+        <v>0.2552891900498611</v>
+      </c>
+      <c r="W47">
+        <v>0.1166217128381918</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.8509639668328706</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1415054656506304</v>
+      </c>
+      <c r="C48">
+        <v>247.5439966115465</v>
+      </c>
+      <c r="D48">
+        <v>538.4559966115465</v>
+      </c>
+      <c r="E48">
+        <v>294.812</v>
+      </c>
+      <c r="F48">
+        <v>394.312</v>
+      </c>
+      <c r="G48">
+        <v>103.4</v>
+      </c>
+      <c r="H48">
+        <v>757.7</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K48">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L48">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M48">
+        <v>61.74925920000001</v>
+      </c>
+      <c r="N48">
+        <v>-10.34517756734695</v>
+      </c>
+      <c r="O48">
+        <v>-3.103553270204085</v>
+      </c>
+      <c r="P48">
+        <v>-7.241624297142867</v>
+      </c>
+      <c r="Q48">
+        <v>-3.441624297142862</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1619623979137855</v>
+      </c>
+      <c r="T48">
+        <v>1.667815359113425</v>
+      </c>
+      <c r="U48">
+        <v>0.1566</v>
+      </c>
+      <c r="V48">
+        <v>0.2497394250487772</v>
+      </c>
+      <c r="W48">
+        <v>0.1174908060373615</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.8324647501625906</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1426834656506304</v>
+      </c>
+      <c r="C49">
+        <v>232.8661051683247</v>
+      </c>
+      <c r="D49">
+        <v>532.3501051683248</v>
+      </c>
+      <c r="E49">
+        <v>303.3840000000001</v>
+      </c>
+      <c r="F49">
+        <v>402.8840000000001</v>
+      </c>
+      <c r="G49">
+        <v>103.4</v>
+      </c>
+      <c r="H49">
+        <v>757.7</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K49">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L49">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M49">
+        <v>63.09163440000002</v>
+      </c>
+      <c r="N49">
+        <v>-11.68755276734696</v>
+      </c>
+      <c r="O49">
+        <v>-3.506265830204087</v>
+      </c>
+      <c r="P49">
+        <v>-8.18128693714287</v>
+      </c>
+      <c r="Q49">
+        <v>-4.381286937142866</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1642862167423474</v>
+      </c>
+      <c r="T49">
+        <v>1.699283573436319</v>
+      </c>
+      <c r="U49">
+        <v>0.1566</v>
+      </c>
+      <c r="V49">
+        <v>0.2444258202605053</v>
+      </c>
+      <c r="W49">
+        <v>0.1183229165472049</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.8147527342016844</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1710754821258499</v>
+      </c>
+      <c r="C50">
+        <v>110.0288406339373</v>
+      </c>
+      <c r="D50">
+        <v>418.0848406339373</v>
+      </c>
+      <c r="E50">
+        <v>311.956</v>
+      </c>
+      <c r="F50">
+        <v>411.456</v>
+      </c>
+      <c r="G50">
+        <v>103.4</v>
+      </c>
+      <c r="H50">
+        <v>757.7</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K50">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L50">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M50">
+        <v>85.91201280000001</v>
+      </c>
+      <c r="N50">
+        <v>-34.50793116734695</v>
+      </c>
+      <c r="O50">
+        <v>-10.35237935020409</v>
+      </c>
+      <c r="P50">
+        <v>-24.15555181714287</v>
+      </c>
+      <c r="Q50">
+        <v>-20.35555181714286</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1708494449012761</v>
+      </c>
+      <c r="T50">
+        <v>1.78816015357963</v>
+      </c>
+      <c r="U50">
+        <v>0.2088</v>
+      </c>
+      <c r="V50">
+        <v>0.1795002117538086</v>
+      </c>
+      <c r="W50">
+        <v>0.1713203557858048</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.598334039179362</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1727754821258499</v>
+      </c>
+      <c r="C51">
+        <v>96.15180856538268</v>
+      </c>
+      <c r="D51">
+        <v>412.7798085653827</v>
+      </c>
+      <c r="E51">
+        <v>320.528</v>
+      </c>
+      <c r="F51">
+        <v>420.028</v>
+      </c>
+      <c r="G51">
+        <v>103.4</v>
+      </c>
+      <c r="H51">
+        <v>757.7</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K51">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L51">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M51">
+        <v>87.70184640000001</v>
+      </c>
+      <c r="N51">
+        <v>-36.29776476734695</v>
+      </c>
+      <c r="O51">
+        <v>-10.88932943020408</v>
+      </c>
+      <c r="P51">
+        <v>-25.40843533714286</v>
+      </c>
+      <c r="Q51">
+        <v>-21.60843533714286</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1734386497032619</v>
+      </c>
+      <c r="T51">
+        <v>1.823222117375309</v>
+      </c>
+      <c r="U51">
+        <v>0.2088</v>
+      </c>
+      <c r="V51">
+        <v>0.1758369421261799</v>
+      </c>
+      <c r="W51">
+        <v>0.1720852464840537</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.5861231404205995</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1744754821258498</v>
+      </c>
+      <c r="C52">
+        <v>82.40771952198259</v>
+      </c>
+      <c r="D52">
+        <v>407.6077195219826</v>
+      </c>
+      <c r="E52">
+        <v>329.1</v>
+      </c>
+      <c r="F52">
+        <v>428.6</v>
+      </c>
+      <c r="G52">
+        <v>103.4</v>
+      </c>
+      <c r="H52">
+        <v>757.7</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K52">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L52">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M52">
+        <v>89.49168000000002</v>
+      </c>
+      <c r="N52">
+        <v>-38.08759836734696</v>
+      </c>
+      <c r="O52">
+        <v>-11.42627951020409</v>
+      </c>
+      <c r="P52">
+        <v>-26.66131885714287</v>
+      </c>
+      <c r="Q52">
+        <v>-22.86131885714287</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1761314226973271</v>
+      </c>
+      <c r="T52">
+        <v>1.859686559722815</v>
+      </c>
+      <c r="U52">
+        <v>0.2088</v>
+      </c>
+      <c r="V52">
+        <v>0.1723202032836562</v>
+      </c>
+      <c r="W52">
+        <v>0.1728195415543726</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.5744006776121875</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1761754821258498</v>
+      </c>
+      <c r="C53">
+        <v>68.79163805661187</v>
+      </c>
+      <c r="D53">
+        <v>402.5636380566119</v>
+      </c>
+      <c r="E53">
+        <v>337.672</v>
+      </c>
+      <c r="F53">
+        <v>437.172</v>
+      </c>
+      <c r="G53">
+        <v>103.4</v>
+      </c>
+      <c r="H53">
+        <v>757.7</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K53">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L53">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M53">
+        <v>91.28151360000001</v>
+      </c>
+      <c r="N53">
+        <v>-39.87743196734695</v>
+      </c>
+      <c r="O53">
+        <v>-11.96322959020408</v>
+      </c>
+      <c r="P53">
+        <v>-27.91420237714286</v>
+      </c>
+      <c r="Q53">
+        <v>-24.11420237714286</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1789341047931909</v>
+      </c>
+      <c r="T53">
+        <v>1.897639346655934</v>
+      </c>
+      <c r="U53">
+        <v>0.2088</v>
+      </c>
+      <c r="V53">
+        <v>0.1689413757682905</v>
+      </c>
+      <c r="W53">
+        <v>0.1735250407395809</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.5631379192276349</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1778754821258499</v>
+      </c>
+      <c r="C54">
+        <v>55.2988700374367</v>
+      </c>
+      <c r="D54">
+        <v>397.6428700374368</v>
+      </c>
+      <c r="E54">
+        <v>346.244</v>
+      </c>
+      <c r="F54">
+        <v>445.744</v>
+      </c>
+      <c r="G54">
+        <v>103.4</v>
+      </c>
+      <c r="H54">
+        <v>757.7</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K54">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L54">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M54">
+        <v>93.07134720000001</v>
+      </c>
+      <c r="N54">
+        <v>-41.66726556734694</v>
+      </c>
+      <c r="O54">
+        <v>-12.50017967020408</v>
+      </c>
+      <c r="P54">
+        <v>-29.16708589714286</v>
+      </c>
+      <c r="Q54">
+        <v>-25.36708589714286</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1818535653097157</v>
+      </c>
+      <c r="T54">
+        <v>1.937173499711266</v>
+      </c>
+      <c r="U54">
+        <v>0.2088</v>
+      </c>
+      <c r="V54">
+        <v>0.1656925031573618</v>
+      </c>
+      <c r="W54">
+        <v>0.1742034053407429</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.5523083438578726</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1795754821258499</v>
+      </c>
+      <c r="C55">
+        <v>41.92494807733772</v>
+      </c>
+      <c r="D55">
+        <v>392.8409480773378</v>
+      </c>
+      <c r="E55">
+        <v>354.816</v>
+      </c>
+      <c r="F55">
+        <v>454.316</v>
+      </c>
+      <c r="G55">
+        <v>103.4</v>
+      </c>
+      <c r="H55">
+        <v>757.7</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K55">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L55">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M55">
+        <v>94.86118080000001</v>
+      </c>
+      <c r="N55">
+        <v>-43.45709916734695</v>
+      </c>
+      <c r="O55">
+        <v>-13.03712975020409</v>
+      </c>
+      <c r="P55">
+        <v>-30.41996941714287</v>
+      </c>
+      <c r="Q55">
+        <v>-26.61996941714286</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1848972581886459</v>
+      </c>
+      <c r="T55">
+        <v>1.978389957151931</v>
+      </c>
+      <c r="U55">
+        <v>0.2088</v>
+      </c>
+      <c r="V55">
+        <v>0.1625662295128833</v>
+      </c>
+      <c r="W55">
+        <v>0.17485617127771</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.541887431709611</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1812754821258498</v>
+      </c>
+      <c r="C56">
+        <v>28.66561800645877</v>
+      </c>
+      <c r="D56">
+        <v>388.1536180064588</v>
+      </c>
+      <c r="E56">
+        <v>363.388</v>
+      </c>
+      <c r="F56">
+        <v>462.888</v>
+      </c>
+      <c r="G56">
+        <v>103.4</v>
+      </c>
+      <c r="H56">
+        <v>757.7</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K56">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L56">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M56">
+        <v>96.65101440000001</v>
+      </c>
+      <c r="N56">
+        <v>-45.24693276734695</v>
+      </c>
+      <c r="O56">
+        <v>-13.57407983020408</v>
+      </c>
+      <c r="P56">
+        <v>-31.67285293714286</v>
+      </c>
+      <c r="Q56">
+        <v>-27.87285293714286</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.188073285540573</v>
+      </c>
+      <c r="T56">
+        <v>2.021398434481321</v>
+      </c>
+      <c r="U56">
+        <v>0.2088</v>
+      </c>
+      <c r="V56">
+        <v>0.1595557437811632</v>
+      </c>
+      <c r="W56">
+        <v>0.1754847606984931</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.5318524792705441</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1829754821258499</v>
+      </c>
+      <c r="C57">
+        <v>15.5168263017847</v>
+      </c>
+      <c r="D57">
+        <v>383.5768263017847</v>
+      </c>
+      <c r="E57">
+        <v>371.96</v>
+      </c>
+      <c r="F57">
+        <v>471.46</v>
+      </c>
+      <c r="G57">
+        <v>103.4</v>
+      </c>
+      <c r="H57">
+        <v>757.7</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K57">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L57">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M57">
+        <v>98.44084800000002</v>
+      </c>
+      <c r="N57">
+        <v>-47.03676636734696</v>
+      </c>
+      <c r="O57">
+        <v>-14.11102991020409</v>
+      </c>
+      <c r="P57">
+        <v>-32.92573645714287</v>
+      </c>
+      <c r="Q57">
+        <v>-29.12573645714286</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1913904696636968</v>
+      </c>
+      <c r="T57">
+        <v>2.066318399692017</v>
+      </c>
+      <c r="U57">
+        <v>0.2088</v>
+      </c>
+      <c r="V57">
+        <v>0.1566547302578693</v>
+      </c>
+      <c r="W57">
+        <v>0.1760904923221569</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.5221824341928978</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1846754821258499</v>
+      </c>
+      <c r="C58">
+        <v>2.474708395675577</v>
+      </c>
+      <c r="D58">
+        <v>379.1067083956757</v>
+      </c>
+      <c r="E58">
+        <v>380.5320000000001</v>
+      </c>
+      <c r="F58">
+        <v>480.0320000000001</v>
+      </c>
+      <c r="G58">
+        <v>103.4</v>
+      </c>
+      <c r="H58">
+        <v>757.7</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K58">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L58">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M58">
+        <v>100.2306816</v>
+      </c>
+      <c r="N58">
+        <v>-48.82659996734697</v>
+      </c>
+      <c r="O58">
+        <v>-14.64797999020409</v>
+      </c>
+      <c r="P58">
+        <v>-34.17861997714287</v>
+      </c>
+      <c r="Q58">
+        <v>-30.37861997714287</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1948584348833263</v>
+      </c>
+      <c r="T58">
+        <v>2.113280181503199</v>
+      </c>
+      <c r="U58">
+        <v>0.2088</v>
+      </c>
+      <c r="V58">
+        <v>0.1538573243604074</v>
+      </c>
+      <c r="W58">
+        <v>0.176674590673547</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.5128577478680245</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1863754821258499</v>
+      </c>
+      <c r="C59">
+        <v>-10.46442220751663</v>
+      </c>
+      <c r="D59">
+        <v>374.7395777924835</v>
+      </c>
+      <c r="E59">
+        <v>389.1040000000001</v>
+      </c>
+      <c r="F59">
+        <v>488.6040000000001</v>
+      </c>
+      <c r="G59">
+        <v>103.4</v>
+      </c>
+      <c r="H59">
+        <v>757.7</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K59">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L59">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M59">
+        <v>102.0205152</v>
+      </c>
+      <c r="N59">
+        <v>-50.61643356734697</v>
+      </c>
+      <c r="O59">
+        <v>-15.18493007020409</v>
+      </c>
+      <c r="P59">
+        <v>-35.43150349714288</v>
+      </c>
+      <c r="Q59">
+        <v>-31.63150349714288</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1984877008108455</v>
+      </c>
+      <c r="T59">
+        <v>2.162426232235832</v>
+      </c>
+      <c r="U59">
+        <v>0.2088</v>
+      </c>
+      <c r="V59">
+        <v>0.1511580730558388</v>
+      </c>
+      <c r="W59">
+        <v>0.1772381943459409</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.5038602435194627</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.206288804918018</v>
+      </c>
+      <c r="C60">
+        <v>-63.59050556392441</v>
+      </c>
+      <c r="D60">
+        <v>330.1854944360756</v>
+      </c>
+      <c r="E60">
+        <v>397.676</v>
+      </c>
+      <c r="F60">
+        <v>497.176</v>
+      </c>
+      <c r="G60">
+        <v>103.4</v>
+      </c>
+      <c r="H60">
+        <v>757.7</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K60">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L60">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M60">
+        <v>118.7256288</v>
+      </c>
+      <c r="N60">
+        <v>-67.32154716734695</v>
+      </c>
+      <c r="O60">
+        <v>-20.19646415020408</v>
+      </c>
+      <c r="P60">
+        <v>-47.12508301714287</v>
+      </c>
+      <c r="Q60">
+        <v>-43.32508301714287</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2042262717638849</v>
+      </c>
+      <c r="T60">
+        <v>2.240135638166212</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.1298896004650675</v>
+      </c>
+      <c r="W60">
+        <v>0.2077823634089419</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.4329653348835585</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2082888049180179</v>
+      </c>
+      <c r="C61">
+        <v>-76.0587569369373</v>
+      </c>
+      <c r="D61">
+        <v>326.2892430630627</v>
+      </c>
+      <c r="E61">
+        <v>406.248</v>
+      </c>
+      <c r="F61">
+        <v>505.748</v>
+      </c>
+      <c r="G61">
+        <v>103.4</v>
+      </c>
+      <c r="H61">
+        <v>757.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K61">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L61">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M61">
+        <v>120.7726224</v>
+      </c>
+      <c r="N61">
+        <v>-69.36854076734694</v>
+      </c>
+      <c r="O61">
+        <v>-20.81056223020408</v>
+      </c>
+      <c r="P61">
+        <v>-48.55797853714286</v>
+      </c>
+      <c r="Q61">
+        <v>-44.75797853714285</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2082610588800772</v>
+      </c>
+      <c r="T61">
+        <v>2.294773092755631</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.1276880818131172</v>
+      </c>
+      <c r="W61">
+        <v>0.2083080860630276</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.4256269393770575</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2102888049180179</v>
+      </c>
+      <c r="C62">
+        <v>-88.43612770990478</v>
+      </c>
+      <c r="D62">
+        <v>322.4838722900953</v>
+      </c>
+      <c r="E62">
+        <v>414.8200000000001</v>
+      </c>
+      <c r="F62">
+        <v>514.3200000000001</v>
+      </c>
+      <c r="G62">
+        <v>103.4</v>
+      </c>
+      <c r="H62">
+        <v>757.7</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K62">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L62">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M62">
+        <v>122.819616</v>
+      </c>
+      <c r="N62">
+        <v>-71.41553436734696</v>
+      </c>
+      <c r="O62">
+        <v>-21.42466031020409</v>
+      </c>
+      <c r="P62">
+        <v>-49.99087405714288</v>
+      </c>
+      <c r="Q62">
+        <v>-46.19087405714287</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2124975853520792</v>
+      </c>
+      <c r="T62">
+        <v>2.352142420074522</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.1255599471162319</v>
+      </c>
+      <c r="W62">
+        <v>0.2088162846286438</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.4185331570541065</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.212288804918018</v>
+      </c>
+      <c r="C63">
+        <v>-100.72576093059</v>
+      </c>
+      <c r="D63">
+        <v>318.7662390694101</v>
+      </c>
+      <c r="E63">
+        <v>423.3920000000001</v>
+      </c>
+      <c r="F63">
+        <v>522.8920000000001</v>
+      </c>
+      <c r="G63">
+        <v>103.4</v>
+      </c>
+      <c r="H63">
+        <v>757.7</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K63">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L63">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M63">
+        <v>124.8666096</v>
+      </c>
+      <c r="N63">
+        <v>-73.46252796734696</v>
+      </c>
+      <c r="O63">
+        <v>-22.03875839020409</v>
+      </c>
+      <c r="P63">
+        <v>-51.42376957714287</v>
+      </c>
+      <c r="Q63">
+        <v>-47.62376957714287</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2169513695918761</v>
+      </c>
+      <c r="T63">
+        <v>2.412453764178998</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.1235015873274413</v>
+      </c>
+      <c r="W63">
+        <v>0.2093078209462071</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.4116719577581376</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.214288804918018</v>
+      </c>
+      <c r="C64">
+        <v>-112.9306563647839</v>
+      </c>
+      <c r="D64">
+        <v>315.1333436352161</v>
+      </c>
+      <c r="E64">
+        <v>431.9640000000001</v>
+      </c>
+      <c r="F64">
+        <v>531.4640000000001</v>
+      </c>
+      <c r="G64">
+        <v>103.4</v>
+      </c>
+      <c r="H64">
+        <v>757.7</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K64">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L64">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M64">
+        <v>126.9136032</v>
+      </c>
+      <c r="N64">
+        <v>-75.50952156734697</v>
+      </c>
+      <c r="O64">
+        <v>-22.65285647020409</v>
+      </c>
+      <c r="P64">
+        <v>-52.85666509714288</v>
+      </c>
+      <c r="Q64">
+        <v>-49.05666509714288</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2216395635285044</v>
+      </c>
+      <c r="T64">
+        <v>2.475939389552129</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.1215096262415148</v>
+      </c>
+      <c r="W64">
+        <v>0.2097835012535263</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.4050320874717159</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2162888049180179</v>
+      </c>
+      <c r="C65">
+        <v>-125.0536785690381</v>
+      </c>
+      <c r="D65">
+        <v>311.5823214309619</v>
+      </c>
+      <c r="E65">
+        <v>440.5360000000001</v>
+      </c>
+      <c r="F65">
+        <v>540.0360000000001</v>
+      </c>
+      <c r="G65">
+        <v>103.4</v>
+      </c>
+      <c r="H65">
+        <v>757.7</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K65">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L65">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M65">
+        <v>128.9605968</v>
+      </c>
+      <c r="N65">
+        <v>-77.55651516734696</v>
+      </c>
+      <c r="O65">
+        <v>-23.26695455020409</v>
+      </c>
+      <c r="P65">
+        <v>-54.28956061714287</v>
+      </c>
+      <c r="Q65">
+        <v>-50.48956061714286</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2265811733535991</v>
+      </c>
+      <c r="T65">
+        <v>2.542856670350835</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.119580902015459</v>
+      </c>
+      <c r="W65">
+        <v>0.2102440805987084</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.3986030067181967</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2182888049180179</v>
+      </c>
+      <c r="C66">
+        <v>-137.0975644236827</v>
+      </c>
+      <c r="D66">
+        <v>308.1104355763174</v>
+      </c>
+      <c r="E66">
+        <v>449.1080000000001</v>
+      </c>
+      <c r="F66">
+        <v>548.6080000000001</v>
+      </c>
+      <c r="G66">
+        <v>103.4</v>
+      </c>
+      <c r="H66">
+        <v>757.7</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K66">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L66">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M66">
+        <v>131.0075904</v>
+      </c>
+      <c r="N66">
+        <v>-79.60350876734697</v>
+      </c>
+      <c r="O66">
+        <v>-23.88105263020409</v>
+      </c>
+      <c r="P66">
+        <v>-55.72245613714288</v>
+      </c>
+      <c r="Q66">
+        <v>-51.92245613714287</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2317973170578658</v>
+      </c>
+      <c r="T66">
+        <v>2.613491577860581</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.1177124504214674</v>
+      </c>
+      <c r="W66">
+        <v>0.2106902668393536</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.3923748347382249</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.220288804918018</v>
+      </c>
+      <c r="C67">
+        <v>-149.0649301677627</v>
+      </c>
+      <c r="D67">
+        <v>304.7150698322374</v>
+      </c>
+      <c r="E67">
+        <v>457.6800000000001</v>
+      </c>
+      <c r="F67">
+        <v>557.1800000000001</v>
+      </c>
+      <c r="G67">
+        <v>103.4</v>
+      </c>
+      <c r="H67">
+        <v>757.7</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K67">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L67">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M67">
+        <v>133.054584</v>
+      </c>
+      <c r="N67">
+        <v>-81.65050236734697</v>
+      </c>
+      <c r="O67">
+        <v>-24.49515071020409</v>
+      </c>
+      <c r="P67">
+        <v>-57.15535165714289</v>
+      </c>
+      <c r="Q67">
+        <v>-53.35535165714288</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.237311526116662</v>
+      </c>
+      <c r="T67">
+        <v>2.688162765799455</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.1159014896457526</v>
+      </c>
+      <c r="W67">
+        <v>0.2111227242725943</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.3863382988191753</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2222888049180179</v>
+      </c>
+      <c r="C68">
+        <v>-160.9582779738959</v>
+      </c>
+      <c r="D68">
+        <v>301.3937220261042</v>
+      </c>
+      <c r="E68">
+        <v>466.2520000000001</v>
+      </c>
+      <c r="F68">
+        <v>565.7520000000001</v>
+      </c>
+      <c r="G68">
+        <v>103.4</v>
+      </c>
+      <c r="H68">
+        <v>757.7</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K68">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L68">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M68">
+        <v>135.1015776</v>
+      </c>
+      <c r="N68">
+        <v>-83.69749596734695</v>
+      </c>
+      <c r="O68">
+        <v>-25.10924879020408</v>
+      </c>
+      <c r="P68">
+        <v>-58.58824717714287</v>
+      </c>
+      <c r="Q68">
+        <v>-54.78824717714286</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2431501004142108</v>
+      </c>
+      <c r="T68">
+        <v>2.767226376558262</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.1141454064693018</v>
+      </c>
+      <c r="W68">
+        <v>0.2115420769351307</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.3804846882310059</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.224288804918018</v>
+      </c>
+      <c r="C69">
+        <v>-172.7800020977784</v>
+      </c>
+      <c r="D69">
+        <v>298.1439979022217</v>
+      </c>
+      <c r="E69">
+        <v>474.8240000000001</v>
+      </c>
+      <c r="F69">
+        <v>574.3240000000001</v>
+      </c>
+      <c r="G69">
+        <v>103.4</v>
+      </c>
+      <c r="H69">
+        <v>757.7</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K69">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L69">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M69">
+        <v>137.1485712</v>
+      </c>
+      <c r="N69">
+        <v>-85.74448956734696</v>
+      </c>
+      <c r="O69">
+        <v>-25.72334687020409</v>
+      </c>
+      <c r="P69">
+        <v>-60.02114269714288</v>
+      </c>
+      <c r="Q69">
+        <v>-56.22114269714287</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.24934252769949</v>
+      </c>
+      <c r="T69">
+        <v>2.851081721302452</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.1124417436861779</v>
+      </c>
+      <c r="W69">
+        <v>0.2119489116077407</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.3748058122872595</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2262888049180179</v>
+      </c>
+      <c r="C70">
+        <v>-184.5323946340962</v>
+      </c>
+      <c r="D70">
+        <v>294.9636053659038</v>
+      </c>
+      <c r="E70">
+        <v>483.3960000000001</v>
+      </c>
+      <c r="F70">
+        <v>582.8960000000001</v>
+      </c>
+      <c r="G70">
+        <v>103.4</v>
+      </c>
+      <c r="H70">
+        <v>757.7</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K70">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L70">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M70">
+        <v>139.1955648</v>
+      </c>
+      <c r="N70">
+        <v>-87.79148316734697</v>
+      </c>
+      <c r="O70">
+        <v>-26.33744495020409</v>
+      </c>
+      <c r="P70">
+        <v>-61.45403821714288</v>
+      </c>
+      <c r="Q70">
+        <v>-57.65403821714288</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.255921981690099</v>
+      </c>
+      <c r="T70">
+        <v>2.940178025093153</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.1107881886319694</v>
+      </c>
+      <c r="W70">
+        <v>0.2123437805546857</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.3692939621065645</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.228288804918018</v>
+      </c>
+      <c r="C71">
+        <v>-196.2176509079276</v>
+      </c>
+      <c r="D71">
+        <v>291.8503490920725</v>
+      </c>
+      <c r="E71">
+        <v>491.9680000000001</v>
+      </c>
+      <c r="F71">
+        <v>591.4680000000001</v>
+      </c>
+      <c r="G71">
+        <v>103.4</v>
+      </c>
+      <c r="H71">
+        <v>757.7</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K71">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L71">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M71">
+        <v>141.2425584</v>
+      </c>
+      <c r="N71">
+        <v>-89.83847676734698</v>
+      </c>
+      <c r="O71">
+        <v>-26.95154303020409</v>
+      </c>
+      <c r="P71">
+        <v>-62.88693373714288</v>
+      </c>
+      <c r="Q71">
+        <v>-59.08693373714288</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.262925916583328</v>
+      </c>
+      <c r="T71">
+        <v>3.035022477515513</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.1091825627097669</v>
+      </c>
+      <c r="W71">
+        <v>0.2127272040249077</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.363941875699223</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.230288804918018</v>
+      </c>
+      <c r="C72">
+        <v>-207.8378745282799</v>
+      </c>
+      <c r="D72">
+        <v>288.8021254717201</v>
+      </c>
+      <c r="E72">
+        <v>500.5400000000001</v>
+      </c>
+      <c r="F72">
+        <v>600.0400000000001</v>
+      </c>
+      <c r="G72">
+        <v>103.4</v>
+      </c>
+      <c r="H72">
+        <v>757.7</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K72">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L72">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M72">
+        <v>143.289552</v>
+      </c>
+      <c r="N72">
+        <v>-91.88547036734695</v>
+      </c>
+      <c r="O72">
+        <v>-27.56564111020409</v>
+      </c>
+      <c r="P72">
+        <v>-64.31982925714287</v>
+      </c>
+      <c r="Q72">
+        <v>-60.51982925714287</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.270396780469439</v>
+      </c>
+      <c r="T72">
+        <v>3.136189893432697</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.1076228118139131</v>
+      </c>
+      <c r="W72">
+        <v>0.2130996725388376</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.358742706046377</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.232288804918018</v>
+      </c>
+      <c r="C73">
+        <v>-219.395082128214</v>
+      </c>
+      <c r="D73">
+        <v>285.816917871786</v>
+      </c>
+      <c r="E73">
+        <v>509.112</v>
+      </c>
+      <c r="F73">
+        <v>608.612</v>
+      </c>
+      <c r="G73">
+        <v>103.4</v>
+      </c>
+      <c r="H73">
+        <v>757.7</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K73">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L73">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M73">
+        <v>145.3365456</v>
+      </c>
+      <c r="N73">
+        <v>-93.93246396734693</v>
+      </c>
+      <c r="O73">
+        <v>-28.17973919020408</v>
+      </c>
+      <c r="P73">
+        <v>-65.75272477714286</v>
+      </c>
+      <c r="Q73">
+        <v>-61.95272477714285</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2783828763476954</v>
+      </c>
+      <c r="T73">
+        <v>3.244334372516582</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.1061069975630129</v>
+      </c>
+      <c r="W73">
+        <v>0.2134616489819525</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.3536899918767098</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.234288804918018</v>
+      </c>
+      <c r="C74">
+        <v>-230.8912078139957</v>
+      </c>
+      <c r="D74">
+        <v>282.8927921860042</v>
+      </c>
+      <c r="E74">
+        <v>517.684</v>
+      </c>
+      <c r="F74">
+        <v>617.184</v>
+      </c>
+      <c r="G74">
+        <v>103.4</v>
+      </c>
+      <c r="H74">
+        <v>757.7</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K74">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L74">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M74">
+        <v>147.3835392</v>
+      </c>
+      <c r="N74">
+        <v>-95.97945756734694</v>
+      </c>
+      <c r="O74">
+        <v>-28.79383727020408</v>
+      </c>
+      <c r="P74">
+        <v>-67.18562029714286</v>
+      </c>
+      <c r="Q74">
+        <v>-63.38562029714286</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2869394076458274</v>
+      </c>
+      <c r="T74">
+        <v>3.360203457249318</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.1046332892635266</v>
+      </c>
+      <c r="W74">
+        <v>0.2138135705238698</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3487776308784222</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.236288804918018</v>
+      </c>
+      <c r="C75">
+        <v>-242.3281073439053</v>
+      </c>
+      <c r="D75">
+        <v>280.0278926560947</v>
+      </c>
+      <c r="E75">
+        <v>526.256</v>
+      </c>
+      <c r="F75">
+        <v>625.756</v>
+      </c>
+      <c r="G75">
+        <v>103.4</v>
+      </c>
+      <c r="H75">
+        <v>757.7</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K75">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L75">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M75">
+        <v>149.4305328</v>
+      </c>
+      <c r="N75">
+        <v>-98.02645116734695</v>
+      </c>
+      <c r="O75">
+        <v>-29.40793535020408</v>
+      </c>
+      <c r="P75">
+        <v>-68.61851581714286</v>
+      </c>
+      <c r="Q75">
+        <v>-64.81851581714287</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2961297560771544</v>
+      </c>
+      <c r="T75">
+        <v>3.484655437147441</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.1031999565338893</v>
+      </c>
+      <c r="W75">
+        <v>0.2141558503797072</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.3439998551129643</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.238288804918018</v>
+      </c>
+      <c r="C76">
+        <v>-253.7075620556739</v>
+      </c>
+      <c r="D76">
+        <v>277.2204379443261</v>
+      </c>
+      <c r="E76">
+        <v>534.828</v>
+      </c>
+      <c r="F76">
+        <v>634.328</v>
+      </c>
+      <c r="G76">
+        <v>103.4</v>
+      </c>
+      <c r="H76">
+        <v>757.7</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K76">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L76">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M76">
+        <v>151.4775264</v>
+      </c>
+      <c r="N76">
+        <v>-100.0734447673469</v>
+      </c>
+      <c r="O76">
+        <v>-30.02203343020408</v>
+      </c>
+      <c r="P76">
+        <v>-70.05141133714285</v>
+      </c>
+      <c r="Q76">
+        <v>-66.25141133714286</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3060270543878141</v>
+      </c>
+      <c r="T76">
+        <v>3.618680646268496</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.1018053625266746</v>
+      </c>
+      <c r="W76">
+        <v>0.2144888794286301</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.3393512084222486</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.240288804918018</v>
+      </c>
+      <c r="C77">
+        <v>-265.0312825600179</v>
+      </c>
+      <c r="D77">
+        <v>274.4687174399822</v>
+      </c>
+      <c r="E77">
+        <v>543.4000000000001</v>
+      </c>
+      <c r="F77">
+        <v>642.9000000000001</v>
+      </c>
+      <c r="G77">
+        <v>103.4</v>
+      </c>
+      <c r="H77">
+        <v>757.7</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K77">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L77">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M77">
+        <v>153.52452</v>
+      </c>
+      <c r="N77">
+        <v>-102.120438367347</v>
+      </c>
+      <c r="O77">
+        <v>-30.63613151020409</v>
+      </c>
+      <c r="P77">
+        <v>-71.48430685714288</v>
+      </c>
+      <c r="Q77">
+        <v>-67.68430685714287</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3167161365633267</v>
+      </c>
+      <c r="T77">
+        <v>3.763427872119236</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.1004479576929855</v>
+      </c>
+      <c r="W77">
+        <v>0.2148130277029151</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3348265256432852</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.242288804918018</v>
+      </c>
+      <c r="C78">
+        <v>-276.3009122163576</v>
+      </c>
+      <c r="D78">
+        <v>271.7710877836425</v>
+      </c>
+      <c r="E78">
+        <v>551.9720000000001</v>
+      </c>
+      <c r="F78">
+        <v>651.4720000000001</v>
+      </c>
+      <c r="G78">
+        <v>103.4</v>
+      </c>
+      <c r="H78">
+        <v>757.7</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K78">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L78">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M78">
+        <v>155.5715136</v>
+      </c>
+      <c r="N78">
+        <v>-104.167431967347</v>
+      </c>
+      <c r="O78">
+        <v>-31.25022959020409</v>
+      </c>
+      <c r="P78">
+        <v>-72.91720237714289</v>
+      </c>
+      <c r="Q78">
+        <v>-69.11720237714289</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3282959755867987</v>
+      </c>
+      <c r="T78">
+        <v>3.920237366790871</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.09912627403913048</v>
+      </c>
+      <c r="W78">
+        <v>0.2151286457594557</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3304209134637682</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.244288804918018</v>
+      </c>
+      <c r="C79">
+        <v>-287.5180304055657</v>
+      </c>
+      <c r="D79">
+        <v>269.1259695944344</v>
+      </c>
+      <c r="E79">
+        <v>560.5440000000001</v>
+      </c>
+      <c r="F79">
+        <v>660.0440000000001</v>
+      </c>
+      <c r="G79">
+        <v>103.4</v>
+      </c>
+      <c r="H79">
+        <v>757.7</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K79">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L79">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M79">
+        <v>157.6185072</v>
+      </c>
+      <c r="N79">
+        <v>-106.214425567347</v>
+      </c>
+      <c r="O79">
+        <v>-31.86432767020409</v>
+      </c>
+      <c r="P79">
+        <v>-74.35009789714289</v>
+      </c>
+      <c r="Q79">
+        <v>-70.55009789714288</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3408827571340508</v>
+      </c>
+      <c r="T79">
+        <v>4.090682469694822</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.09783891983083008</v>
+      </c>
+      <c r="W79">
+        <v>0.2154360659443978</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3261297327694336</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.246288804918018</v>
+      </c>
+      <c r="C80">
+        <v>-298.6841556134367</v>
+      </c>
+      <c r="D80">
+        <v>266.5318443865634</v>
+      </c>
+      <c r="E80">
+        <v>569.1160000000001</v>
+      </c>
+      <c r="F80">
+        <v>668.6160000000001</v>
+      </c>
+      <c r="G80">
+        <v>103.4</v>
+      </c>
+      <c r="H80">
+        <v>757.7</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K80">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L80">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M80">
+        <v>159.6655008</v>
+      </c>
+      <c r="N80">
+        <v>-108.261419167347</v>
+      </c>
+      <c r="O80">
+        <v>-32.47842575020409</v>
+      </c>
+      <c r="P80">
+        <v>-75.78299341714288</v>
+      </c>
+      <c r="Q80">
+        <v>-71.98299341714286</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3546137915492349</v>
+      </c>
+      <c r="T80">
+        <v>4.276622581953678</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.09658457470479381</v>
+      </c>
+      <c r="W80">
+        <v>0.2157356035604953</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3219485823493127</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.248288804918018</v>
+      </c>
+      <c r="C81">
+        <v>-309.8007483375287</v>
+      </c>
+      <c r="D81">
+        <v>263.9872516624714</v>
+      </c>
+      <c r="E81">
+        <v>577.6880000000001</v>
+      </c>
+      <c r="F81">
+        <v>677.1880000000001</v>
+      </c>
+      <c r="G81">
+        <v>103.4</v>
+      </c>
+      <c r="H81">
+        <v>757.7</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K81">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L81">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M81">
+        <v>161.7124944</v>
+      </c>
+      <c r="N81">
+        <v>-110.308412767347</v>
+      </c>
+      <c r="O81">
+        <v>-33.09252383020409</v>
+      </c>
+      <c r="P81">
+        <v>-77.21588893714288</v>
+      </c>
+      <c r="Q81">
+        <v>-73.41588893714288</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3696525435277699</v>
+      </c>
+      <c r="T81">
+        <v>4.480271276332425</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.09536198515156856</v>
+      </c>
+      <c r="W81">
+        <v>0.2160275579458054</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3178732838385619</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.250288804918018</v>
+      </c>
+      <c r="C82">
+        <v>-320.8692138290692</v>
+      </c>
+      <c r="D82">
+        <v>261.490786170931</v>
+      </c>
+      <c r="E82">
+        <v>586.2600000000001</v>
+      </c>
+      <c r="F82">
+        <v>685.7600000000001</v>
+      </c>
+      <c r="G82">
+        <v>103.4</v>
+      </c>
+      <c r="H82">
+        <v>757.7</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K82">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L82">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M82">
+        <v>163.759488</v>
+      </c>
+      <c r="N82">
+        <v>-112.355406367347</v>
+      </c>
+      <c r="O82">
+        <v>-33.70662191020409</v>
+      </c>
+      <c r="P82">
+        <v>-78.64878445714288</v>
+      </c>
+      <c r="Q82">
+        <v>-74.84878445714287</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3861951707041584</v>
+      </c>
+      <c r="T82">
+        <v>4.704284840149046</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.09416996033717397</v>
+      </c>
+      <c r="W82">
+        <v>0.2163122134714829</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3138998677905799</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.252288804918018</v>
+      </c>
+      <c r="C83">
+        <v>-331.8909046807403</v>
+      </c>
+      <c r="D83">
+        <v>259.0410953192599</v>
+      </c>
+      <c r="E83">
+        <v>594.8320000000001</v>
+      </c>
+      <c r="F83">
+        <v>694.3320000000001</v>
+      </c>
+      <c r="G83">
+        <v>103.4</v>
+      </c>
+      <c r="H83">
+        <v>757.7</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K83">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L83">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M83">
+        <v>165.8064816</v>
+      </c>
+      <c r="N83">
+        <v>-114.402399967347</v>
+      </c>
+      <c r="O83">
+        <v>-34.32071999020409</v>
+      </c>
+      <c r="P83">
+        <v>-80.0816799771429</v>
+      </c>
+      <c r="Q83">
+        <v>-76.28167997714289</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.404479127057009</v>
+      </c>
+      <c r="T83">
+        <v>4.95187877910426</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.09300736823424587</v>
+      </c>
+      <c r="W83">
+        <v>0.2165898404656621</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3100245607808196</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.254288804918018</v>
+      </c>
+      <c r="C84">
+        <v>-342.8671232703585</v>
+      </c>
+      <c r="D84">
+        <v>256.6368767296416</v>
+      </c>
+      <c r="E84">
+        <v>603.4040000000001</v>
+      </c>
+      <c r="F84">
+        <v>702.9040000000001</v>
+      </c>
+      <c r="G84">
+        <v>103.4</v>
+      </c>
+      <c r="H84">
+        <v>757.7</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K84">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L84">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M84">
+        <v>167.8534752</v>
+      </c>
+      <c r="N84">
+        <v>-116.449393567347</v>
+      </c>
+      <c r="O84">
+        <v>-34.93481807020409</v>
+      </c>
+      <c r="P84">
+        <v>-81.51457549714289</v>
+      </c>
+      <c r="Q84">
+        <v>-77.71457549714287</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4247946341157317</v>
+      </c>
+      <c r="T84">
+        <v>5.226983155721163</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.09187313203626726</v>
+      </c>
+      <c r="W84">
+        <v>0.2168606960697394</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3062437734542243</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.256288804918018</v>
+      </c>
+      <c r="C85">
+        <v>-353.7991240697227</v>
+      </c>
+      <c r="D85">
+        <v>254.2768759302774</v>
+      </c>
+      <c r="E85">
+        <v>611.9760000000001</v>
+      </c>
+      <c r="F85">
+        <v>711.4760000000001</v>
+      </c>
+      <c r="G85">
+        <v>103.4</v>
+      </c>
+      <c r="H85">
+        <v>757.7</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K85">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L85">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M85">
+        <v>169.9004688</v>
+      </c>
+      <c r="N85">
+        <v>-118.496387167347</v>
+      </c>
+      <c r="O85">
+        <v>-35.54891615020409</v>
+      </c>
+      <c r="P85">
+        <v>-82.94747101714287</v>
+      </c>
+      <c r="Q85">
+        <v>-79.14747101714286</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4475002008284218</v>
+      </c>
+      <c r="T85">
+        <v>5.534452753116526</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.09076622683101104</v>
+      </c>
+      <c r="W85">
+        <v>0.2171250250327546</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.3025540894367035</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.258288804918018</v>
+      </c>
+      <c r="C86">
+        <v>-364.6881158272316</v>
+      </c>
+      <c r="D86">
+        <v>251.9598841727684</v>
+      </c>
+      <c r="E86">
+        <v>620.548</v>
+      </c>
+      <c r="F86">
+        <v>720.048</v>
+      </c>
+      <c r="G86">
+        <v>103.4</v>
+      </c>
+      <c r="H86">
+        <v>757.7</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K86">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L86">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M86">
+        <v>171.9474624</v>
+      </c>
+      <c r="N86">
+        <v>-120.5433807673469</v>
+      </c>
+      <c r="O86">
+        <v>-36.16301423020408</v>
+      </c>
+      <c r="P86">
+        <v>-84.38036653714286</v>
+      </c>
+      <c r="Q86">
+        <v>-80.58036653714285</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4730439633801979</v>
+      </c>
+      <c r="T86">
+        <v>5.880356050186305</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.08968567651159426</v>
+      </c>
+      <c r="W86">
+        <v>0.2173830604490313</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2989522550386475</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.260288804918018</v>
+      </c>
+      <c r="C87">
+        <v>-375.5352636322507</v>
+      </c>
+      <c r="D87">
+        <v>249.6847363677493</v>
+      </c>
+      <c r="E87">
+        <v>629.12</v>
+      </c>
+      <c r="F87">
+        <v>728.62</v>
+      </c>
+      <c r="G87">
+        <v>103.4</v>
+      </c>
+      <c r="H87">
+        <v>757.7</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K87">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L87">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M87">
+        <v>173.994456</v>
+      </c>
+      <c r="N87">
+        <v>-122.590374367347</v>
+      </c>
+      <c r="O87">
+        <v>-36.77711231020408</v>
+      </c>
+      <c r="P87">
+        <v>-85.81326205714288</v>
+      </c>
+      <c r="Q87">
+        <v>-82.01326205714287</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5019935609388778</v>
+      </c>
+      <c r="T87">
+        <v>6.272379786865393</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.08863055090557551</v>
+      </c>
+      <c r="W87">
+        <v>0.2176350244437486</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.2954351696852516</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.262288804918018</v>
+      </c>
+      <c r="C88">
+        <v>-386.3416908686337</v>
+      </c>
+      <c r="D88">
+        <v>247.4503091313663</v>
+      </c>
+      <c r="E88">
+        <v>637.692</v>
+      </c>
+      <c r="F88">
+        <v>737.192</v>
+      </c>
+      <c r="G88">
+        <v>103.4</v>
+      </c>
+      <c r="H88">
+        <v>757.7</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K88">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L88">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M88">
+        <v>176.0414496</v>
+      </c>
+      <c r="N88">
+        <v>-124.637367967347</v>
+      </c>
+      <c r="O88">
+        <v>-37.39121039020409</v>
+      </c>
+      <c r="P88">
+        <v>-87.24615757714287</v>
+      </c>
+      <c r="Q88">
+        <v>-83.44615757714286</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5350788152916548</v>
+      </c>
+      <c r="T88">
+        <v>6.720406914498636</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.08759996310434788</v>
+      </c>
+      <c r="W88">
+        <v>0.2178811288106817</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2919998770144929</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.264288804918018</v>
+      </c>
+      <c r="C89">
+        <v>-397.108481064283</v>
+      </c>
+      <c r="D89">
+        <v>245.255518935717</v>
+      </c>
+      <c r="E89">
+        <v>646.264</v>
+      </c>
+      <c r="F89">
+        <v>745.764</v>
+      </c>
+      <c r="G89">
+        <v>103.4</v>
+      </c>
+      <c r="H89">
+        <v>757.7</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K89">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L89">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M89">
+        <v>178.0884432</v>
+      </c>
+      <c r="N89">
+        <v>-126.6843615673469</v>
+      </c>
+      <c r="O89">
+        <v>-38.00530847020408</v>
+      </c>
+      <c r="P89">
+        <v>-88.67905309714286</v>
+      </c>
+      <c r="Q89">
+        <v>-84.87905309714284</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5732541087756282</v>
+      </c>
+      <c r="T89">
+        <v>7.237361292536992</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.08659306697671169</v>
+      </c>
+      <c r="W89">
+        <v>0.2181215756059613</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2886435565890391</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2662888049180179</v>
+      </c>
+      <c r="C90">
+        <v>-407.8366796431457</v>
+      </c>
+      <c r="D90">
+        <v>243.0993203568543</v>
+      </c>
+      <c r="E90">
+        <v>654.836</v>
+      </c>
+      <c r="F90">
+        <v>754.336</v>
+      </c>
+      <c r="G90">
+        <v>103.4</v>
+      </c>
+      <c r="H90">
+        <v>757.7</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K90">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L90">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M90">
+        <v>180.1354368</v>
+      </c>
+      <c r="N90">
+        <v>-128.7313551673469</v>
+      </c>
+      <c r="O90">
+        <v>-38.61940655020408</v>
+      </c>
+      <c r="P90">
+        <v>-90.11194861714287</v>
+      </c>
+      <c r="Q90">
+        <v>-86.31194861714286</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6177919511735972</v>
+      </c>
+      <c r="T90">
+        <v>7.840474733581742</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.08560905485197633</v>
+      </c>
+      <c r="W90">
+        <v>0.2183565577013481</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2853635161732545</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.268288804918018</v>
+      </c>
+      <c r="C91">
+        <v>-418.5272955855984</v>
+      </c>
+      <c r="D91">
+        <v>240.9807044144016</v>
+      </c>
+      <c r="E91">
+        <v>663.408</v>
+      </c>
+      <c r="F91">
+        <v>762.908</v>
+      </c>
+      <c r="G91">
+        <v>103.4</v>
+      </c>
+      <c r="H91">
+        <v>757.7</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K91">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L91">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M91">
+        <v>182.1824304</v>
+      </c>
+      <c r="N91">
+        <v>-130.778348767347</v>
+      </c>
+      <c r="O91">
+        <v>-39.23350463020409</v>
+      </c>
+      <c r="P91">
+        <v>-91.54484413714286</v>
+      </c>
+      <c r="Q91">
+        <v>-87.74484413714285</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6704275830984698</v>
+      </c>
+      <c r="T91">
+        <v>8.553245163907356</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.0846471553592575</v>
+      </c>
+      <c r="W91">
+        <v>0.2185862593002093</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2821571845308584</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.270288804918018</v>
+      </c>
+      <c r="C92">
+        <v>-429.1813030027583</v>
+      </c>
+      <c r="D92">
+        <v>238.8986969972417</v>
+      </c>
+      <c r="E92">
+        <v>671.98</v>
+      </c>
+      <c r="F92">
+        <v>771.48</v>
+      </c>
+      <c r="G92">
+        <v>103.4</v>
+      </c>
+      <c r="H92">
+        <v>757.7</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K92">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L92">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M92">
+        <v>184.229424</v>
+      </c>
+      <c r="N92">
+        <v>-132.825342367347</v>
+      </c>
+      <c r="O92">
+        <v>-39.84760271020409</v>
+      </c>
+      <c r="P92">
+        <v>-92.97773965714288</v>
+      </c>
+      <c r="Q92">
+        <v>-89.17773965714287</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7335903414083169</v>
+      </c>
+      <c r="T92">
+        <v>9.408569680298092</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.08370663141082131</v>
+      </c>
+      <c r="W92">
+        <v>0.2188108564190959</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2790221047027377</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.272288804918018</v>
+      </c>
+      <c r="C93">
+        <v>-439.7996426298862</v>
+      </c>
+      <c r="D93">
+        <v>236.8523573701138</v>
+      </c>
+      <c r="E93">
+        <v>680.552</v>
+      </c>
+      <c r="F93">
+        <v>780.052</v>
+      </c>
+      <c r="G93">
+        <v>103.4</v>
+      </c>
+      <c r="H93">
+        <v>757.7</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K93">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L93">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M93">
+        <v>186.2764176</v>
+      </c>
+      <c r="N93">
+        <v>-134.8723359673469</v>
+      </c>
+      <c r="O93">
+        <v>-40.46170079020408</v>
+      </c>
+      <c r="P93">
+        <v>-94.41063517714286</v>
+      </c>
+      <c r="Q93">
+        <v>-90.61063517714285</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8107892682314632</v>
+      </c>
+      <c r="T93">
+        <v>10.45396631144233</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.08278677831839469</v>
+      </c>
+      <c r="W93">
+        <v>0.2190305173375674</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2759559277279824</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.274288804918018</v>
+      </c>
+      <c r="C94">
+        <v>-450.3832232436872</v>
+      </c>
+      <c r="D94">
+        <v>234.8407767563129</v>
+      </c>
+      <c r="E94">
+        <v>689.124</v>
+      </c>
+      <c r="F94">
+        <v>788.624</v>
+      </c>
+      <c r="G94">
+        <v>103.4</v>
+      </c>
+      <c r="H94">
+        <v>757.7</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K94">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L94">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M94">
+        <v>188.3234112</v>
+      </c>
+      <c r="N94">
+        <v>-136.9193295673469</v>
+      </c>
+      <c r="O94">
+        <v>-41.07579887020408</v>
+      </c>
+      <c r="P94">
+        <v>-95.84353069714287</v>
+      </c>
+      <c r="Q94">
+        <v>-92.04353069714287</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.9072879267603964</v>
+      </c>
+      <c r="T94">
+        <v>11.76071210037262</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.08188692203232519</v>
+      </c>
+      <c r="W94">
+        <v>0.2192454030186808</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2729564067744173</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.276288804918018</v>
+      </c>
+      <c r="C95">
+        <v>-460.9329230079973</v>
+      </c>
+      <c r="D95">
+        <v>232.8630769920029</v>
+      </c>
+      <c r="E95">
+        <v>697.6960000000001</v>
+      </c>
+      <c r="F95">
+        <v>797.1960000000001</v>
+      </c>
+      <c r="G95">
+        <v>103.4</v>
+      </c>
+      <c r="H95">
+        <v>757.7</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K95">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L95">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M95">
+        <v>190.3704048</v>
+      </c>
+      <c r="N95">
+        <v>-138.966323167347</v>
+      </c>
+      <c r="O95">
+        <v>-41.68989695020409</v>
+      </c>
+      <c r="P95">
+        <v>-97.2764262171429</v>
+      </c>
+      <c r="Q95">
+        <v>-93.47642621714289</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.03135763058331</v>
+      </c>
+      <c r="T95">
+        <v>13.44081382899728</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.08100641749434319</v>
+      </c>
+      <c r="W95">
+        <v>0.2194556675023508</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2700213916478106</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.278288804918018</v>
+      </c>
+      <c r="C96">
+        <v>-471.4495907520425</v>
+      </c>
+      <c r="D96">
+        <v>230.9184092479576</v>
+      </c>
+      <c r="E96">
+        <v>706.2680000000001</v>
+      </c>
+      <c r="F96">
+        <v>805.7680000000001</v>
+      </c>
+      <c r="G96">
+        <v>103.4</v>
+      </c>
+      <c r="H96">
+        <v>757.7</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K96">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L96">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M96">
+        <v>192.4173984000001</v>
+      </c>
+      <c r="N96">
+        <v>-141.013316767347</v>
+      </c>
+      <c r="O96">
+        <v>-42.3039950302041</v>
+      </c>
+      <c r="P96">
+        <v>-98.70932173714289</v>
+      </c>
+      <c r="Q96">
+        <v>-94.90932173714288</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.196783902347196</v>
+      </c>
+      <c r="T96">
+        <v>15.6809494671635</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.08014464709546719</v>
+      </c>
+      <c r="W96">
+        <v>0.2196614582736025</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2671488236515573</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.280288804918018</v>
+      </c>
+      <c r="C97">
+        <v>-481.934047185179</v>
+      </c>
+      <c r="D97">
+        <v>229.0059528148211</v>
+      </c>
+      <c r="E97">
+        <v>714.8400000000001</v>
+      </c>
+      <c r="F97">
+        <v>814.3400000000001</v>
+      </c>
+      <c r="G97">
+        <v>103.4</v>
+      </c>
+      <c r="H97">
+        <v>757.7</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K97">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L97">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M97">
+        <v>194.464392</v>
+      </c>
+      <c r="N97">
+        <v>-143.060310367347</v>
+      </c>
+      <c r="O97">
+        <v>-42.91809311020409</v>
+      </c>
+      <c r="P97">
+        <v>-100.1422172571429</v>
+      </c>
+      <c r="Q97">
+        <v>-96.34221725714286</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.428380682816635</v>
+      </c>
+      <c r="T97">
+        <v>18.8171393605962</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.07930101923130438</v>
+      </c>
+      <c r="W97">
+        <v>0.2198629166075645</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2643367307710146</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2822888049180179</v>
+      </c>
+      <c r="C98">
+        <v>-492.387086051766</v>
+      </c>
+      <c r="D98">
+        <v>227.1249139482341</v>
+      </c>
+      <c r="E98">
+        <v>723.412</v>
+      </c>
+      <c r="F98">
+        <v>822.912</v>
+      </c>
+      <c r="G98">
+        <v>103.4</v>
+      </c>
+      <c r="H98">
+        <v>757.7</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K98">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L98">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M98">
+        <v>196.5113856</v>
+      </c>
+      <c r="N98">
+        <v>-145.107303967347</v>
+      </c>
+      <c r="O98">
+        <v>-43.53219119020408</v>
+      </c>
+      <c r="P98">
+        <v>-101.5751127771429</v>
+      </c>
+      <c r="Q98">
+        <v>-97.77511277714285</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.77577585352079</v>
+      </c>
+      <c r="T98">
+        <v>23.5214242007452</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.07847496694764498</v>
+      </c>
+      <c r="W98">
+        <v>0.2200601778929024</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2615832231588165</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.284288804918018</v>
+      </c>
+      <c r="C99">
+        <v>-502.8094752295868</v>
+      </c>
+      <c r="D99">
+        <v>225.2745247704132</v>
+      </c>
+      <c r="E99">
+        <v>731.984</v>
+      </c>
+      <c r="F99">
+        <v>831.484</v>
+      </c>
+      <c r="G99">
+        <v>103.4</v>
+      </c>
+      <c r="H99">
+        <v>757.7</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K99">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L99">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M99">
+        <v>198.5583792</v>
+      </c>
+      <c r="N99">
+        <v>-147.154297567347</v>
+      </c>
+      <c r="O99">
+        <v>-44.14628927020409</v>
+      </c>
+      <c r="P99">
+        <v>-103.0080082971429</v>
+      </c>
+      <c r="Q99">
+        <v>-99.20800829714287</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.354767804694387</v>
+      </c>
+      <c r="T99">
+        <v>31.36189893432694</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.07766594666983419</v>
+      </c>
+      <c r="W99">
+        <v>0.2202533719352436</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2588864888994473</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2862888049180179</v>
+      </c>
+      <c r="C100">
+        <v>-513.2019577750098</v>
+      </c>
+      <c r="D100">
+        <v>223.4540422249903</v>
+      </c>
+      <c r="E100">
+        <v>740.556</v>
+      </c>
+      <c r="F100">
+        <v>840.056</v>
+      </c>
+      <c r="G100">
+        <v>103.4</v>
+      </c>
+      <c r="H100">
+        <v>757.7</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K100">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L100">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M100">
+        <v>200.6053728</v>
+      </c>
+      <c r="N100">
+        <v>-149.201291167347</v>
+      </c>
+      <c r="O100">
+        <v>-44.76038735020409</v>
+      </c>
+      <c r="P100">
+        <v>-104.4409038171429</v>
+      </c>
+      <c r="Q100">
+        <v>-100.6409038171429</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.512751707041581</v>
+      </c>
+      <c r="T100">
+        <v>47.0428484014904</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.07687343700993793</v>
+      </c>
+      <c r="W100">
+        <v>0.2204426232420268</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2562447900331264</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.288288804918018</v>
+      </c>
+      <c r="C101">
+        <v>-523.5652529178793</v>
+      </c>
+      <c r="D101">
+        <v>221.6627470821207</v>
+      </c>
+      <c r="E101">
+        <v>749.128</v>
+      </c>
+      <c r="F101">
+        <v>848.628</v>
+      </c>
+      <c r="G101">
+        <v>103.4</v>
+      </c>
+      <c r="H101">
+        <v>757.7</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>55.20408163265306</v>
+      </c>
+      <c r="K101">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="L101">
+        <v>51.40408163265306</v>
+      </c>
+      <c r="M101">
+        <v>202.6523664</v>
+      </c>
+      <c r="N101">
+        <v>-151.248284767347</v>
+      </c>
+      <c r="O101">
+        <v>-45.37448543020409</v>
+      </c>
+      <c r="P101">
+        <v>-105.8737993371429</v>
+      </c>
+      <c r="Q101">
+        <v>-102.0737993371429</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.986703414083162</v>
+      </c>
+      <c r="T101">
+        <v>94.08569680298082</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.07609693764620118</v>
+      </c>
+      <c r="W101">
+        <v>0.2206280512900872</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2536564588206706</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/mexico/mexico_entertainment.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_entertainment.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1157262567099268</v>
+        <v>0.115410577939797</v>
       </c>
       <c r="C2">
-        <v>745.6779590088539</v>
+        <v>741.1238439542645</v>
       </c>
       <c r="D2">
-        <v>643.7779590088539</v>
+        <v>646.6974439542646</v>
       </c>
       <c r="E2">
-        <v>-9.16</v>
+        <v>-1.6864</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>7.4736</v>
       </c>
       <c r="G2">
         <v>101.9</v>
@@ -1439,28 +1439,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.37592208</v>
       </c>
       <c r="N2">
-        <v>50.64999999999999</v>
+        <v>50.27407791999999</v>
       </c>
       <c r="O2">
-        <v>15.195</v>
+        <v>15.082223376</v>
       </c>
       <c r="P2">
-        <v>35.455</v>
+        <v>35.19185454399999</v>
       </c>
       <c r="Q2">
-        <v>39.055</v>
+        <v>38.791854544</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1157262567099268</v>
+        <v>0.1162206847876738</v>
       </c>
       <c r="T2">
-        <v>1.017512237681883</v>
+        <v>1.024706768655391</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>134.735368563613</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.115410577939797</v>
+        <v>0.1150948991696673</v>
       </c>
       <c r="C3">
-        <v>741.1238439542645</v>
+        <v>736.5963288205361</v>
       </c>
       <c r="D3">
-        <v>646.6974439542646</v>
+        <v>649.6435288205361</v>
       </c>
       <c r="E3">
-        <v>-1.6864</v>
+        <v>5.7872</v>
       </c>
       <c r="F3">
-        <v>7.4736</v>
+        <v>14.9472</v>
       </c>
       <c r="G3">
         <v>101.9</v>
@@ -1521,28 +1521,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M3">
-        <v>0.37592208</v>
+        <v>0.75184416</v>
       </c>
       <c r="N3">
-        <v>50.27407791999999</v>
+        <v>49.89815583999999</v>
       </c>
       <c r="O3">
-        <v>15.082223376</v>
+        <v>14.969446752</v>
       </c>
       <c r="P3">
-        <v>35.19185454399999</v>
+        <v>34.928709088</v>
       </c>
       <c r="Q3">
-        <v>38.791854544</v>
+        <v>38.528709088</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1162206847876738</v>
+        <v>0.1167252032343543</v>
       </c>
       <c r="T3">
-        <v>1.024706768655391</v>
+        <v>1.032048126791624</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>134.735368563613</v>
+        <v>67.36768428180648</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1150948991696673</v>
+        <v>0.1147792203995375</v>
       </c>
       <c r="C4">
-        <v>736.5963288205361</v>
+        <v>732.0957788059229</v>
       </c>
       <c r="D4">
-        <v>649.6435288205361</v>
+        <v>652.6165788059229</v>
       </c>
       <c r="E4">
-        <v>5.7872</v>
+        <v>13.2608</v>
       </c>
       <c r="F4">
-        <v>14.9472</v>
+        <v>22.4208</v>
       </c>
       <c r="G4">
         <v>101.9</v>
@@ -1603,28 +1603,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M4">
-        <v>0.75184416</v>
+        <v>1.12776624</v>
       </c>
       <c r="N4">
-        <v>49.89815583999999</v>
+        <v>49.52223375999999</v>
       </c>
       <c r="O4">
-        <v>14.969446752</v>
+        <v>14.856670128</v>
       </c>
       <c r="P4">
-        <v>34.928709088</v>
+        <v>34.66556363199999</v>
       </c>
       <c r="Q4">
-        <v>38.528709088</v>
+        <v>38.265563632</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1167252032343543</v>
+        <v>0.1172401241232345</v>
       </c>
       <c r="T4">
-        <v>1.032048126791624</v>
+        <v>1.039540853136851</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>67.36768428180648</v>
+        <v>44.91178952120432</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1147792203995375</v>
+        <v>0.1144635416294077</v>
       </c>
       <c r="C5">
-        <v>732.0957788059229</v>
+        <v>727.6225658246361</v>
       </c>
       <c r="D5">
-        <v>652.6165788059229</v>
+        <v>655.6169658246362</v>
       </c>
       <c r="E5">
-        <v>13.2608</v>
+        <v>20.7344</v>
       </c>
       <c r="F5">
-        <v>22.4208</v>
+        <v>29.8944</v>
       </c>
       <c r="G5">
         <v>101.9</v>
@@ -1685,28 +1685,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M5">
-        <v>1.12776624</v>
+        <v>1.50368832</v>
       </c>
       <c r="N5">
-        <v>49.52223375999999</v>
+        <v>49.14631167999999</v>
       </c>
       <c r="O5">
-        <v>14.856670128</v>
+        <v>14.743893504</v>
       </c>
       <c r="P5">
-        <v>34.66556363199999</v>
+        <v>34.402418176</v>
       </c>
       <c r="Q5">
-        <v>38.265563632</v>
+        <v>38.002418176</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1172401241232345</v>
+        <v>0.117765772530633</v>
       </c>
       <c r="T5">
-        <v>1.039540853136851</v>
+        <v>1.047189677947604</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>44.91178952120432</v>
+        <v>33.68384214090324</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1144635416294077</v>
+        <v>0.1141478628592779</v>
       </c>
       <c r="C6">
-        <v>727.6225658246361</v>
+        <v>723.1770686619384</v>
       </c>
       <c r="D6">
-        <v>655.6169658246362</v>
+        <v>658.6450686619385</v>
       </c>
       <c r="E6">
-        <v>20.7344</v>
+        <v>28.208</v>
       </c>
       <c r="F6">
-        <v>29.8944</v>
+        <v>37.368</v>
       </c>
       <c r="G6">
         <v>101.9</v>
@@ -1767,28 +1767,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M6">
-        <v>1.50368832</v>
+        <v>1.8796104</v>
       </c>
       <c r="N6">
-        <v>49.14631167999999</v>
+        <v>48.77038959999999</v>
       </c>
       <c r="O6">
-        <v>14.743893504</v>
+        <v>14.63111688</v>
       </c>
       <c r="P6">
-        <v>34.402418176</v>
+        <v>34.13927271999999</v>
       </c>
       <c r="Q6">
-        <v>38.002418176</v>
+        <v>37.73927272</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.117765772530633</v>
+        <v>0.1183024872202925</v>
       </c>
       <c r="T6">
-        <v>1.047189677947604</v>
+        <v>1.05499953064911</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>33.68384214090324</v>
+        <v>26.94707371272259</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1141478628592779</v>
+        <v>0.1138321840891481</v>
       </c>
       <c r="C7">
-        <v>723.1770686619384</v>
+        <v>718.7596731335575</v>
       </c>
       <c r="D7">
-        <v>658.6450686619385</v>
+        <v>661.7012731335575</v>
       </c>
       <c r="E7">
-        <v>28.208</v>
+        <v>35.6816</v>
       </c>
       <c r="F7">
-        <v>37.368</v>
+        <v>44.84160000000001</v>
       </c>
       <c r="G7">
         <v>101.9</v>
@@ -1849,28 +1849,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M7">
-        <v>1.8796104</v>
+        <v>2.25553248</v>
       </c>
       <c r="N7">
-        <v>48.77038959999999</v>
+        <v>48.39446751999999</v>
       </c>
       <c r="O7">
-        <v>14.63111688</v>
+        <v>14.518340256</v>
       </c>
       <c r="P7">
-        <v>34.13927271999999</v>
+        <v>33.876127264</v>
       </c>
       <c r="Q7">
-        <v>37.73927272</v>
+        <v>37.476127264</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1183024872202925</v>
+        <v>0.1188506213714342</v>
       </c>
       <c r="T7">
-        <v>1.05499953064911</v>
+        <v>1.062975550429371</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>26.94707371272259</v>
+        <v>22.45589476060216</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1138321840891481</v>
+        <v>0.1135165053190184</v>
       </c>
       <c r="C8">
-        <v>718.7596731335575</v>
+        <v>714.3707722495561</v>
       </c>
       <c r="D8">
-        <v>661.7012731335575</v>
+        <v>664.7859722495562</v>
       </c>
       <c r="E8">
-        <v>35.6816</v>
+        <v>43.15519999999999</v>
       </c>
       <c r="F8">
-        <v>44.8416</v>
+        <v>52.3152</v>
       </c>
       <c r="G8">
         <v>101.9</v>
@@ -1931,28 +1931,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M8">
-        <v>2.25553248</v>
+        <v>2.63145456</v>
       </c>
       <c r="N8">
-        <v>48.39446751999999</v>
+        <v>48.01854543999999</v>
       </c>
       <c r="O8">
-        <v>14.518340256</v>
+        <v>14.405563632</v>
       </c>
       <c r="P8">
-        <v>33.876127264</v>
+        <v>33.61298180799999</v>
       </c>
       <c r="Q8">
-        <v>37.476127264</v>
+        <v>37.21298180799999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1188506213714342</v>
+        <v>0.1194105433537832</v>
       </c>
       <c r="T8">
-        <v>1.062975550429371</v>
+        <v>1.071123097516735</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.45589476060216</v>
+        <v>19.24790979480185</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1135165053190183</v>
+        <v>0.1132008265488886</v>
       </c>
       <c r="C9">
-        <v>714.3707722495562</v>
+        <v>710.0107663828128</v>
       </c>
       <c r="D9">
-        <v>664.7859722495563</v>
+        <v>667.8995663828128</v>
       </c>
       <c r="E9">
-        <v>43.15520000000001</v>
+        <v>50.6288</v>
       </c>
       <c r="F9">
-        <v>52.3152</v>
+        <v>59.7888</v>
       </c>
       <c r="G9">
         <v>101.9</v>
@@ -2013,28 +2013,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M9">
-        <v>2.63145456</v>
+        <v>3.00737664</v>
       </c>
       <c r="N9">
-        <v>48.01854543999999</v>
+        <v>47.64262335999999</v>
       </c>
       <c r="O9">
-        <v>14.405563632</v>
+        <v>14.292787008</v>
       </c>
       <c r="P9">
-        <v>33.61298180799999</v>
+        <v>33.349836352</v>
       </c>
       <c r="Q9">
-        <v>37.21298180799999</v>
+        <v>36.949836352</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1194105433537832</v>
+        <v>0.1199826375531398</v>
       </c>
       <c r="T9">
-        <v>1.071123097516735</v>
+        <v>1.079447765192954</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.24790979480185</v>
+        <v>16.84192107045162</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1132008265488886</v>
+        <v>0.1128851477787588</v>
       </c>
       <c r="C10">
-        <v>710.0107663828128</v>
+        <v>705.6800634422526</v>
       </c>
       <c r="D10">
-        <v>667.8995663828128</v>
+        <v>671.0424634422526</v>
       </c>
       <c r="E10">
-        <v>50.6288</v>
+        <v>58.1024</v>
       </c>
       <c r="F10">
-        <v>59.7888</v>
+        <v>67.2624</v>
       </c>
       <c r="G10">
         <v>101.9</v>
@@ -2095,28 +2095,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M10">
-        <v>3.00737664</v>
+        <v>3.38329872</v>
       </c>
       <c r="N10">
-        <v>47.64262335999999</v>
+        <v>47.26670127999999</v>
       </c>
       <c r="O10">
-        <v>14.292787008</v>
+        <v>14.180010384</v>
       </c>
       <c r="P10">
-        <v>33.349836352</v>
+        <v>33.08669089599999</v>
       </c>
       <c r="Q10">
-        <v>36.949836352</v>
+        <v>36.68669089599999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1199826375531398</v>
+        <v>0.1205673052513833</v>
       </c>
       <c r="T10">
-        <v>1.079447765192954</v>
+        <v>1.087955392598321</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.84192107045162</v>
+        <v>14.97059650706811</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1128851477787588</v>
+        <v>0.112569469008629</v>
       </c>
       <c r="C11">
-        <v>705.6800634422526</v>
+        <v>701.3790790509963</v>
       </c>
       <c r="D11">
-        <v>671.0424634422526</v>
+        <v>674.2150790509963</v>
       </c>
       <c r="E11">
-        <v>58.1024</v>
+        <v>65.57599999999999</v>
       </c>
       <c r="F11">
-        <v>67.2624</v>
+        <v>74.73599999999999</v>
       </c>
       <c r="G11">
         <v>101.9</v>
@@ -2177,28 +2177,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M11">
-        <v>3.38329872</v>
+        <v>3.759220799999999</v>
       </c>
       <c r="N11">
-        <v>47.26670127999999</v>
+        <v>46.89077919999999</v>
       </c>
       <c r="O11">
-        <v>14.180010384</v>
+        <v>14.06723376</v>
       </c>
       <c r="P11">
-        <v>33.08669089599999</v>
+        <v>32.82354543999999</v>
       </c>
       <c r="Q11">
-        <v>36.68669089599999</v>
+        <v>36.42354543999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1205673052513833</v>
+        <v>0.1211649655651434</v>
       </c>
       <c r="T11">
-        <v>1.087955392598321</v>
+        <v>1.096652078390473</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.97059650706811</v>
+        <v>13.4735368563613</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.112569469008629</v>
+        <v>0.1123692902384992</v>
       </c>
       <c r="C12">
-        <v>701.3790790509963</v>
+        <v>695.9328935666661</v>
       </c>
       <c r="D12">
-        <v>674.2150790509963</v>
+        <v>676.2424935666661</v>
       </c>
       <c r="E12">
-        <v>65.57600000000001</v>
+        <v>73.04960000000001</v>
       </c>
       <c r="F12">
-        <v>74.736</v>
+        <v>82.20960000000001</v>
       </c>
       <c r="G12">
         <v>101.9</v>
@@ -2259,45 +2259,45 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M12">
-        <v>3.7592208</v>
+        <v>4.25845728</v>
       </c>
       <c r="N12">
-        <v>46.89077919999999</v>
+        <v>46.39154271999999</v>
       </c>
       <c r="O12">
-        <v>14.06723376</v>
+        <v>13.917462816</v>
       </c>
       <c r="P12">
-        <v>32.82354543999999</v>
+        <v>32.47407990399999</v>
       </c>
       <c r="Q12">
-        <v>36.42354543999999</v>
+        <v>36.07407990399999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1211649655651434</v>
+        <v>0.121776056447752</v>
       </c>
       <c r="T12">
-        <v>1.096652078390473</v>
+        <v>1.105544195324023</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.3</v>
       </c>
       <c r="W12">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.47353685636129</v>
+        <v>11.89397865698444</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1123692902384992</v>
+        <v>0.1120641114683695</v>
       </c>
       <c r="C13">
-        <v>695.9328935666661</v>
+        <v>691.5737222962309</v>
       </c>
       <c r="D13">
-        <v>676.2424935666661</v>
+        <v>679.356922296231</v>
       </c>
       <c r="E13">
-        <v>73.04960000000001</v>
+        <v>80.5232</v>
       </c>
       <c r="F13">
-        <v>82.20960000000001</v>
+        <v>89.6832</v>
       </c>
       <c r="G13">
         <v>101.9</v>
@@ -2341,28 +2341,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M13">
-        <v>4.25845728</v>
+        <v>4.64558976</v>
       </c>
       <c r="N13">
-        <v>46.39154271999999</v>
+        <v>46.00441023999999</v>
       </c>
       <c r="O13">
-        <v>13.917462816</v>
+        <v>13.801323072</v>
       </c>
       <c r="P13">
-        <v>32.47407990399999</v>
+        <v>32.203087168</v>
       </c>
       <c r="Q13">
-        <v>36.07407990399999</v>
+        <v>35.803087168</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.121776056447752</v>
+        <v>0.1224010357595108</v>
       </c>
       <c r="T13">
-        <v>1.105544195324023</v>
+        <v>1.114638405824244</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.89397865698444</v>
+        <v>10.9028137689024</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1120641114683695</v>
+        <v>0.1117589326982397</v>
       </c>
       <c r="C14">
-        <v>691.5737222962309</v>
+        <v>687.2433707016295</v>
       </c>
       <c r="D14">
-        <v>679.356922296231</v>
+        <v>682.5001707016295</v>
       </c>
       <c r="E14">
-        <v>80.5232</v>
+        <v>87.99680000000001</v>
       </c>
       <c r="F14">
-        <v>89.6832</v>
+        <v>97.1568</v>
       </c>
       <c r="G14">
         <v>101.9</v>
@@ -2423,28 +2423,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M14">
-        <v>4.64558976</v>
+        <v>5.03272224</v>
       </c>
       <c r="N14">
-        <v>46.00441023999999</v>
+        <v>45.61727775999999</v>
       </c>
       <c r="O14">
-        <v>13.801323072</v>
+        <v>13.685183328</v>
       </c>
       <c r="P14">
-        <v>32.203087168</v>
+        <v>31.932094432</v>
       </c>
       <c r="Q14">
-        <v>35.803087168</v>
+        <v>35.53209443199999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1224010357595108</v>
+        <v>0.1230403824117697</v>
       </c>
       <c r="T14">
-        <v>1.114638405824244</v>
+        <v>1.123941678634815</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.9028137689024</v>
+        <v>10.06413578667914</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1117589326982397</v>
+        <v>0.1116203539281099</v>
       </c>
       <c r="C15">
-        <v>687.2433707016295</v>
+        <v>681.2067127510827</v>
       </c>
       <c r="D15">
-        <v>682.5001707016295</v>
+        <v>683.9371127510827</v>
       </c>
       <c r="E15">
-        <v>87.99680000000001</v>
+        <v>95.47040000000001</v>
       </c>
       <c r="F15">
-        <v>97.1568</v>
+        <v>104.6304</v>
       </c>
       <c r="G15">
         <v>101.9</v>
@@ -2505,45 +2505,45 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M15">
-        <v>5.03272224</v>
+        <v>5.5977264</v>
       </c>
       <c r="N15">
-        <v>45.61727775999999</v>
+        <v>45.05227359999999</v>
       </c>
       <c r="O15">
-        <v>13.685183328</v>
+        <v>13.51568208</v>
       </c>
       <c r="P15">
-        <v>31.932094432</v>
+        <v>31.53659151999999</v>
       </c>
       <c r="Q15">
-        <v>35.53209443199999</v>
+        <v>35.13659152</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1230403824117697</v>
+        <v>0.1236945975908255</v>
       </c>
       <c r="T15">
-        <v>1.123941678634815</v>
+        <v>1.133461306627027</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.3</v>
       </c>
       <c r="W15">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.06413578667914</v>
+        <v>9.04831647363115</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1116203539281099</v>
+        <v>0.1113270751579801</v>
       </c>
       <c r="C16">
-        <v>681.2067127510827</v>
+        <v>676.7942021525269</v>
       </c>
       <c r="D16">
-        <v>683.9371127510827</v>
+        <v>686.9982021525269</v>
       </c>
       <c r="E16">
-        <v>95.47040000000001</v>
+        <v>102.944</v>
       </c>
       <c r="F16">
-        <v>104.6304</v>
+        <v>112.104</v>
       </c>
       <c r="G16">
         <v>101.9</v>
@@ -2587,28 +2587,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M16">
-        <v>5.5977264</v>
+        <v>5.997564000000001</v>
       </c>
       <c r="N16">
-        <v>45.05227359999999</v>
+        <v>44.65243599999999</v>
       </c>
       <c r="O16">
-        <v>13.51568208</v>
+        <v>13.3957308</v>
       </c>
       <c r="P16">
-        <v>31.53659151999999</v>
+        <v>31.2567052</v>
       </c>
       <c r="Q16">
-        <v>35.13659152</v>
+        <v>34.8567052</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1236945975908255</v>
+        <v>0.1243642060682119</v>
       </c>
       <c r="T16">
-        <v>1.133461306627027</v>
+        <v>1.143204925866115</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.04831647363115</v>
+        <v>8.445095375389073</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1113270751579801</v>
+        <v>0.1110337963878503</v>
       </c>
       <c r="C17">
-        <v>676.7942021525269</v>
+        <v>672.4092157081564</v>
       </c>
       <c r="D17">
-        <v>686.9982021525269</v>
+        <v>690.0868157081563</v>
       </c>
       <c r="E17">
-        <v>102.944</v>
+        <v>110.4176</v>
       </c>
       <c r="F17">
-        <v>112.104</v>
+        <v>119.5776</v>
       </c>
       <c r="G17">
         <v>101.9</v>
@@ -2669,28 +2669,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M17">
-        <v>5.997564</v>
+        <v>6.3974016</v>
       </c>
       <c r="N17">
-        <v>44.65243599999999</v>
+        <v>44.25259839999999</v>
       </c>
       <c r="O17">
-        <v>13.3957308</v>
+        <v>13.27577952</v>
       </c>
       <c r="P17">
-        <v>31.2567052</v>
+        <v>30.97681887999999</v>
       </c>
       <c r="Q17">
-        <v>34.8567052</v>
+        <v>34.57681887999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1243642060682119</v>
+        <v>0.1250497576045837</v>
       </c>
       <c r="T17">
-        <v>1.143204925866115</v>
+        <v>1.153180536039467</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.445095375389073</v>
+        <v>7.917276914427256</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1110337963878503</v>
+        <v>0.1108357176177206</v>
       </c>
       <c r="C18">
-        <v>672.4092157081564</v>
+        <v>667.037407657954</v>
       </c>
       <c r="D18">
-        <v>690.0868157081563</v>
+        <v>692.188607657954</v>
       </c>
       <c r="E18">
-        <v>110.4176</v>
+        <v>117.8912</v>
       </c>
       <c r="F18">
-        <v>119.5776</v>
+        <v>127.0512</v>
       </c>
       <c r="G18">
         <v>101.9</v>
@@ -2751,45 +2751,45 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M18">
-        <v>6.3974016</v>
+        <v>6.898880160000001</v>
       </c>
       <c r="N18">
-        <v>44.25259839999999</v>
+        <v>43.75111983999999</v>
       </c>
       <c r="O18">
-        <v>13.27577952</v>
+        <v>13.125335952</v>
       </c>
       <c r="P18">
-        <v>30.97681887999999</v>
+        <v>30.62578388799999</v>
       </c>
       <c r="Q18">
-        <v>34.57681887999999</v>
+        <v>34.225783888</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1250497576045837</v>
+        <v>0.125751828455085</v>
       </c>
       <c r="T18">
-        <v>1.153180536039467</v>
+        <v>1.163396522361574</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.3</v>
       </c>
       <c r="W18">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.917276914427256</v>
+        <v>7.341771247697682</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1108357176177206</v>
+        <v>0.1105480388475907</v>
       </c>
       <c r="C19">
-        <v>667.037407657954</v>
+        <v>662.6392362098152</v>
       </c>
       <c r="D19">
-        <v>692.188607657954</v>
+        <v>695.2640362098152</v>
       </c>
       <c r="E19">
-        <v>117.8912</v>
+        <v>125.3648</v>
       </c>
       <c r="F19">
-        <v>127.0512</v>
+        <v>134.5248</v>
       </c>
       <c r="G19">
         <v>101.9</v>
@@ -2833,28 +2833,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M19">
-        <v>6.898880160000001</v>
+        <v>7.304696640000001</v>
       </c>
       <c r="N19">
-        <v>43.75111983999999</v>
+        <v>43.34530335999999</v>
       </c>
       <c r="O19">
-        <v>13.125335952</v>
+        <v>13.003591008</v>
       </c>
       <c r="P19">
-        <v>30.62578388799999</v>
+        <v>30.34171235199999</v>
       </c>
       <c r="Q19">
-        <v>34.225783888</v>
+        <v>33.941712352</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.125751828455085</v>
+        <v>0.1264710229848668</v>
       </c>
       <c r="T19">
-        <v>1.163396522361574</v>
+        <v>1.173861679081782</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.341771247697682</v>
+        <v>6.933895067270033</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1105480388475908</v>
+        <v>0.110260360077461</v>
       </c>
       <c r="C20">
-        <v>662.6392362098151</v>
+        <v>658.2685152910358</v>
       </c>
       <c r="D20">
-        <v>695.2640362098151</v>
+        <v>698.3669152910359</v>
       </c>
       <c r="E20">
-        <v>125.3648</v>
+        <v>132.8384</v>
       </c>
       <c r="F20">
-        <v>134.5248</v>
+        <v>141.9984</v>
       </c>
       <c r="G20">
         <v>101.9</v>
@@ -2915,28 +2915,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M20">
-        <v>7.30469664</v>
+        <v>7.710513120000001</v>
       </c>
       <c r="N20">
-        <v>43.34530335999999</v>
+        <v>42.93948687999999</v>
       </c>
       <c r="O20">
-        <v>13.003591008</v>
+        <v>12.881846064</v>
       </c>
       <c r="P20">
-        <v>30.34171235199999</v>
+        <v>30.057640816</v>
       </c>
       <c r="Q20">
-        <v>33.941712352</v>
+        <v>33.657640816</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1264710229848668</v>
+        <v>0.1272079754042728</v>
       </c>
       <c r="T20">
-        <v>1.173861679081782</v>
+        <v>1.184585234733352</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.933895067270034</v>
+        <v>6.568953221624242</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.110260360077461</v>
+        <v>0.1099726813073312</v>
       </c>
       <c r="C21">
-        <v>658.2685152910358</v>
+        <v>653.9256140743403</v>
       </c>
       <c r="D21">
-        <v>698.3669152910359</v>
+        <v>701.4976140743403</v>
       </c>
       <c r="E21">
-        <v>132.8384</v>
+        <v>140.312</v>
       </c>
       <c r="F21">
-        <v>141.9984</v>
+        <v>149.472</v>
       </c>
       <c r="G21">
         <v>101.9</v>
@@ -2997,28 +2997,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M21">
-        <v>7.710513120000001</v>
+        <v>8.1163296</v>
       </c>
       <c r="N21">
-        <v>42.93948687999999</v>
+        <v>42.53367039999999</v>
       </c>
       <c r="O21">
-        <v>12.881846064</v>
+        <v>12.76010112</v>
       </c>
       <c r="P21">
-        <v>30.057640816</v>
+        <v>29.77356928</v>
       </c>
       <c r="Q21">
-        <v>33.657640816</v>
+        <v>33.37356928</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1272079754042728</v>
+        <v>0.127963351634164</v>
       </c>
       <c r="T21">
-        <v>1.184585234733352</v>
+        <v>1.195576879276212</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.568953221624242</v>
+        <v>6.24050556054303</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1099726813073312</v>
+        <v>0.1098320025372014</v>
       </c>
       <c r="C22">
-        <v>653.9256140743403</v>
+        <v>647.993209378042</v>
       </c>
       <c r="D22">
-        <v>701.4976140743403</v>
+        <v>703.0388093780421</v>
       </c>
       <c r="E22">
-        <v>140.312</v>
+        <v>147.7856</v>
       </c>
       <c r="F22">
-        <v>149.472</v>
+        <v>156.9456</v>
       </c>
       <c r="G22">
         <v>101.9</v>
@@ -3079,45 +3079,45 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M22">
-        <v>8.1163296</v>
+        <v>8.679091680000001</v>
       </c>
       <c r="N22">
-        <v>42.53367039999999</v>
+        <v>41.97090831999999</v>
       </c>
       <c r="O22">
-        <v>12.76010112</v>
+        <v>12.591272496</v>
       </c>
       <c r="P22">
-        <v>29.77356928</v>
+        <v>29.379635824</v>
       </c>
       <c r="Q22">
-        <v>33.37356928</v>
+        <v>32.979635824</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.127963351634164</v>
+        <v>0.1287378513129132</v>
       </c>
       <c r="T22">
-        <v>1.195576879276212</v>
+        <v>1.20684679330117</v>
       </c>
       <c r="U22">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.3</v>
       </c>
       <c r="W22">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.24050556054303</v>
+        <v>5.835864151166564</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1098320025372014</v>
+        <v>0.1095513237670716</v>
       </c>
       <c r="C23">
-        <v>647.993209378042</v>
+        <v>643.6148873536133</v>
       </c>
       <c r="D23">
-        <v>703.0388093780421</v>
+        <v>706.1340873536134</v>
       </c>
       <c r="E23">
-        <v>147.7856</v>
+        <v>155.2592</v>
       </c>
       <c r="F23">
-        <v>156.9456</v>
+        <v>164.4192</v>
       </c>
       <c r="G23">
         <v>101.9</v>
@@ -3161,28 +3161,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M23">
-        <v>8.679091679999999</v>
+        <v>9.092381760000002</v>
       </c>
       <c r="N23">
-        <v>41.97090831999999</v>
+        <v>41.55761823999999</v>
       </c>
       <c r="O23">
-        <v>12.591272496</v>
+        <v>12.467285472</v>
       </c>
       <c r="P23">
-        <v>29.379635824</v>
+        <v>29.09033276799999</v>
       </c>
       <c r="Q23">
-        <v>32.979635824</v>
+        <v>32.69033276799999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1287378513129132</v>
+        <v>0.1295322099577842</v>
       </c>
       <c r="T23">
-        <v>1.20684679330117</v>
+        <v>1.218405679480613</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.835864151166565</v>
+        <v>5.57059759884081</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1095513237670716</v>
+        <v>0.1092706449969419</v>
       </c>
       <c r="C24">
-        <v>643.6148873536133</v>
+        <v>639.2639410968463</v>
       </c>
       <c r="D24">
-        <v>706.1340873536134</v>
+        <v>709.2567410968464</v>
       </c>
       <c r="E24">
-        <v>155.2592</v>
+        <v>162.7328</v>
       </c>
       <c r="F24">
-        <v>164.4192</v>
+        <v>171.8928</v>
       </c>
       <c r="G24">
         <v>101.9</v>
@@ -3243,28 +3243,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M24">
-        <v>9.092381760000002</v>
+        <v>9.505671840000002</v>
       </c>
       <c r="N24">
-        <v>41.55761823999999</v>
+        <v>41.14432815999999</v>
       </c>
       <c r="O24">
-        <v>12.467285472</v>
+        <v>12.343298448</v>
       </c>
       <c r="P24">
-        <v>29.09033276799999</v>
+        <v>28.80102971199999</v>
       </c>
       <c r="Q24">
-        <v>32.69033276799999</v>
+        <v>32.401029712</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1295322099577842</v>
+        <v>0.1303472012947297</v>
       </c>
       <c r="T24">
-        <v>1.218405679480613</v>
+        <v>1.230264796469912</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.57059759884081</v>
+        <v>5.328397703239036</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1092706449969419</v>
+        <v>0.1089899662268121</v>
       </c>
       <c r="C25">
-        <v>639.2639410968463</v>
+        <v>634.9407354028471</v>
       </c>
       <c r="D25">
-        <v>709.2567410968464</v>
+        <v>712.4071354028471</v>
       </c>
       <c r="E25">
-        <v>162.7328</v>
+        <v>170.2064</v>
       </c>
       <c r="F25">
-        <v>171.8928</v>
+        <v>179.3664</v>
       </c>
       <c r="G25">
         <v>101.9</v>
@@ -3325,28 +3325,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M25">
-        <v>9.505671840000002</v>
+        <v>9.918961920000001</v>
       </c>
       <c r="N25">
-        <v>41.14432815999999</v>
+        <v>40.73103807999999</v>
       </c>
       <c r="O25">
-        <v>12.343298448</v>
+        <v>12.219311424</v>
       </c>
       <c r="P25">
-        <v>28.80102971199999</v>
+        <v>28.51172665599999</v>
       </c>
       <c r="Q25">
-        <v>32.401029712</v>
+        <v>32.11172665599999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1303472012947297</v>
+        <v>0.1311836397721212</v>
       </c>
       <c r="T25">
-        <v>1.230264796469912</v>
+        <v>1.242435995485246</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.328397703239036</v>
+        <v>5.106381132270744</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1089899662268121</v>
+        <v>0.1087092874566823</v>
       </c>
       <c r="C26">
-        <v>634.9407354028471</v>
+        <v>630.6456415770623</v>
       </c>
       <c r="D26">
-        <v>712.4071354028471</v>
+        <v>715.5856415770623</v>
       </c>
       <c r="E26">
-        <v>170.2064</v>
+        <v>177.68</v>
       </c>
       <c r="F26">
-        <v>179.3664</v>
+        <v>186.84</v>
       </c>
       <c r="G26">
         <v>101.9</v>
@@ -3407,28 +3407,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M26">
-        <v>9.918961920000001</v>
+        <v>10.332252</v>
       </c>
       <c r="N26">
-        <v>40.73103807999999</v>
+        <v>40.31774799999999</v>
       </c>
       <c r="O26">
-        <v>12.219311424</v>
+        <v>12.0953244</v>
       </c>
       <c r="P26">
-        <v>28.51172665599999</v>
+        <v>28.2224236</v>
       </c>
       <c r="Q26">
-        <v>32.11172665599999</v>
+        <v>31.8224236</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1311836397721212</v>
+        <v>0.1320423832755764</v>
       </c>
       <c r="T26">
-        <v>1.242435995485246</v>
+        <v>1.254931759807655</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.106381132270744</v>
+        <v>4.902125886979914</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1087092874566823</v>
+        <v>0.1084286086865525</v>
       </c>
       <c r="C27">
-        <v>630.6456415770623</v>
+        <v>626.3790375811668</v>
       </c>
       <c r="D27">
-        <v>715.5856415770623</v>
+        <v>718.7926375811669</v>
       </c>
       <c r="E27">
-        <v>177.68</v>
+        <v>185.1536</v>
       </c>
       <c r="F27">
-        <v>186.84</v>
+        <v>194.3136</v>
       </c>
       <c r="G27">
         <v>101.9</v>
@@ -3489,28 +3489,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M27">
-        <v>10.332252</v>
+        <v>10.74554208</v>
       </c>
       <c r="N27">
-        <v>40.31774799999999</v>
+        <v>39.90445791999999</v>
       </c>
       <c r="O27">
-        <v>12.0953244</v>
+        <v>11.971337376</v>
       </c>
       <c r="P27">
-        <v>28.2224236</v>
+        <v>27.93312054399999</v>
       </c>
       <c r="Q27">
-        <v>31.8224236</v>
+        <v>31.533120544</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1320423832755764</v>
+        <v>0.1329243360629088</v>
       </c>
       <c r="T27">
-        <v>1.254931759807655</v>
+        <v>1.267765247490129</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.902125886979914</v>
+        <v>4.713582583634532</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1084286086865525</v>
+        <v>0.1081479299164227</v>
       </c>
       <c r="C28">
-        <v>626.3790375811668</v>
+        <v>622.1413081828863</v>
       </c>
       <c r="D28">
-        <v>718.7926375811669</v>
+        <v>722.0285081828863</v>
       </c>
       <c r="E28">
-        <v>185.1536</v>
+        <v>192.6272</v>
       </c>
       <c r="F28">
-        <v>194.3136</v>
+        <v>201.7872</v>
       </c>
       <c r="G28">
         <v>101.9</v>
@@ -3571,28 +3571,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M28">
-        <v>10.74554208</v>
+        <v>11.15883216</v>
       </c>
       <c r="N28">
-        <v>39.90445791999999</v>
+        <v>39.49116783999999</v>
       </c>
       <c r="O28">
-        <v>11.971337376</v>
+        <v>11.847350352</v>
       </c>
       <c r="P28">
-        <v>27.93312054399999</v>
+        <v>27.64381748799999</v>
       </c>
       <c r="Q28">
-        <v>31.533120544</v>
+        <v>31.24381748799999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1329243360629088</v>
+        <v>0.1338304519403051</v>
       </c>
       <c r="T28">
-        <v>1.267765247490129</v>
+        <v>1.280950337574863</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.713582583634532</v>
+        <v>4.539005450907327</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1081479299164227</v>
+        <v>0.108357251146293</v>
       </c>
       <c r="C29">
-        <v>622.1413081828863</v>
+        <v>612.2517469223641</v>
       </c>
       <c r="D29">
-        <v>722.0285081828863</v>
+        <v>719.6125469223641</v>
       </c>
       <c r="E29">
-        <v>192.6272</v>
+        <v>200.1008</v>
       </c>
       <c r="F29">
-        <v>201.7872</v>
+        <v>209.2608</v>
       </c>
       <c r="G29">
         <v>101.9</v>
@@ -3653,45 +3653,45 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M29">
-        <v>11.15883216</v>
+        <v>12.09527424</v>
       </c>
       <c r="N29">
-        <v>39.49116783999999</v>
+        <v>38.55472575999999</v>
       </c>
       <c r="O29">
-        <v>11.847350352</v>
+        <v>11.566417728</v>
       </c>
       <c r="P29">
-        <v>27.64381748799999</v>
+        <v>26.98830803199999</v>
       </c>
       <c r="Q29">
-        <v>31.24381748799999</v>
+        <v>30.58830803199999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1338304519403051</v>
+        <v>0.1347617377031847</v>
       </c>
       <c r="T29">
-        <v>1.280950337574863</v>
+        <v>1.29450168016195</v>
       </c>
       <c r="U29">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V29">
         <v>0.3</v>
       </c>
       <c r="W29">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.539005450907327</v>
+        <v>4.18758591123933</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.108357251146293</v>
+        <v>0.1080940723761632</v>
       </c>
       <c r="C30">
-        <v>612.2517469223641</v>
+        <v>607.8183518382565</v>
       </c>
       <c r="D30">
-        <v>719.6125469223641</v>
+        <v>722.6527518382566</v>
       </c>
       <c r="E30">
-        <v>200.1008</v>
+        <v>207.5744</v>
       </c>
       <c r="F30">
-        <v>209.2608</v>
+        <v>216.7344</v>
       </c>
       <c r="G30">
         <v>101.9</v>
@@ -3735,28 +3735,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M30">
-        <v>12.09527424</v>
+        <v>12.52724832</v>
       </c>
       <c r="N30">
-        <v>38.55472575999999</v>
+        <v>38.12275167999999</v>
       </c>
       <c r="O30">
-        <v>11.566417728</v>
+        <v>11.436825504</v>
       </c>
       <c r="P30">
-        <v>26.98830803199999</v>
+        <v>26.685926176</v>
       </c>
       <c r="Q30">
-        <v>30.58830803199999</v>
+        <v>30.285926176</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1347617377031847</v>
+        <v>0.1357192568678355</v>
       </c>
       <c r="T30">
-        <v>1.29450168016195</v>
+        <v>1.308434750709238</v>
       </c>
       <c r="U30">
         <v>0.0578</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.18758591123933</v>
+        <v>4.043186397058663</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1080940723761632</v>
+        <v>0.1085658936060334</v>
       </c>
       <c r="C31">
-        <v>607.8183518382566</v>
+        <v>594.9124558801753</v>
       </c>
       <c r="D31">
-        <v>722.6527518382566</v>
+        <v>717.2204558801753</v>
       </c>
       <c r="E31">
-        <v>207.5744</v>
+        <v>215.048</v>
       </c>
       <c r="F31">
-        <v>216.7344</v>
+        <v>224.208</v>
       </c>
       <c r="G31">
         <v>101.9</v>
@@ -3817,45 +3817,45 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M31">
-        <v>12.52724832</v>
+        <v>13.7439504</v>
       </c>
       <c r="N31">
-        <v>38.12275167999999</v>
+        <v>36.90604959999999</v>
       </c>
       <c r="O31">
-        <v>11.436825504</v>
+        <v>11.07181488</v>
       </c>
       <c r="P31">
-        <v>26.685926176</v>
+        <v>25.83423471999999</v>
       </c>
       <c r="Q31">
-        <v>30.285926176</v>
+        <v>29.43423471999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1357192568678355</v>
+        <v>0.1367041337229049</v>
       </c>
       <c r="T31">
-        <v>1.308434750709238</v>
+        <v>1.322765908986447</v>
       </c>
       <c r="U31">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V31">
         <v>0.3</v>
       </c>
       <c r="W31">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.043186397058664</v>
+        <v>3.685257769847597</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1085658936060334</v>
+        <v>0.1083272148359036</v>
       </c>
       <c r="C32">
-        <v>594.9124558801753</v>
+        <v>590.1766284927995</v>
       </c>
       <c r="D32">
-        <v>717.2204558801753</v>
+        <v>719.9582284927995</v>
       </c>
       <c r="E32">
-        <v>215.048</v>
+        <v>222.5216</v>
       </c>
       <c r="F32">
-        <v>224.208</v>
+        <v>231.6816</v>
       </c>
       <c r="G32">
         <v>101.9</v>
@@ -3899,28 +3899,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M32">
-        <v>13.7439504</v>
+        <v>14.20208208</v>
       </c>
       <c r="N32">
-        <v>36.90604959999999</v>
+        <v>36.44791791999999</v>
       </c>
       <c r="O32">
-        <v>11.07181488</v>
+        <v>10.934375376</v>
       </c>
       <c r="P32">
-        <v>25.83423471999999</v>
+        <v>25.513542544</v>
       </c>
       <c r="Q32">
-        <v>29.43423471999999</v>
+        <v>29.113542544</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1367041337229049</v>
+        <v>0.1377175577331937</v>
       </c>
       <c r="T32">
-        <v>1.322765908986447</v>
+        <v>1.33751246315575</v>
       </c>
       <c r="U32">
         <v>0.0613</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.685257769847597</v>
+        <v>3.566378486949288</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1083272148359036</v>
+        <v>0.1087157360657738</v>
       </c>
       <c r="C33">
-        <v>590.1766284927995</v>
+        <v>578.2570969360776</v>
       </c>
       <c r="D33">
-        <v>719.9582284927995</v>
+        <v>715.5122969360776</v>
       </c>
       <c r="E33">
-        <v>222.5216</v>
+        <v>229.9952</v>
       </c>
       <c r="F33">
-        <v>231.6816</v>
+        <v>239.1552</v>
       </c>
       <c r="G33">
         <v>101.9</v>
@@ -3981,45 +3981,45 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M33">
-        <v>14.20208208</v>
+        <v>15.32984832</v>
       </c>
       <c r="N33">
-        <v>36.44791791999999</v>
+        <v>35.32015167999999</v>
       </c>
       <c r="O33">
-        <v>10.934375376</v>
+        <v>10.596045504</v>
       </c>
       <c r="P33">
-        <v>25.513542544</v>
+        <v>24.72410617599999</v>
       </c>
       <c r="Q33">
-        <v>29.113542544</v>
+        <v>28.32410617599999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1377175577331937</v>
+        <v>0.1387607883320204</v>
       </c>
       <c r="T33">
-        <v>1.33751246315575</v>
+        <v>1.352692739506503</v>
       </c>
       <c r="U33">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V33">
         <v>0.3</v>
       </c>
       <c r="W33">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.566378486949288</v>
+        <v>3.304011816863168</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1087157360657738</v>
+        <v>0.1084966572956441</v>
       </c>
       <c r="C34">
-        <v>578.2570969360776</v>
+        <v>573.2836869109005</v>
       </c>
       <c r="D34">
-        <v>715.5122969360776</v>
+        <v>718.0124869109006</v>
       </c>
       <c r="E34">
-        <v>229.9952</v>
+        <v>237.4688</v>
       </c>
       <c r="F34">
-        <v>239.1552</v>
+        <v>246.6288</v>
       </c>
       <c r="G34">
         <v>101.9</v>
@@ -4063,28 +4063,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M34">
-        <v>15.32984832</v>
+        <v>15.80890608</v>
       </c>
       <c r="N34">
-        <v>35.32015167999999</v>
+        <v>34.84109391999999</v>
       </c>
       <c r="O34">
-        <v>10.596045504</v>
+        <v>10.452328176</v>
       </c>
       <c r="P34">
-        <v>24.72410617599999</v>
+        <v>24.388765744</v>
       </c>
       <c r="Q34">
-        <v>28.32410617599999</v>
+        <v>27.988765744</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1387607883320204</v>
+        <v>0.1398351601427524</v>
       </c>
       <c r="T34">
-        <v>1.352692739506503</v>
+        <v>1.36832615843489</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.304011816863168</v>
+        <v>3.203890246655194</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1084966572956441</v>
+        <v>0.1082775785255143</v>
       </c>
       <c r="C35">
-        <v>573.2836869109005</v>
+        <v>568.3278108093394</v>
       </c>
       <c r="D35">
-        <v>718.0124869109006</v>
+        <v>720.5302108093395</v>
       </c>
       <c r="E35">
-        <v>237.4688</v>
+        <v>244.9424</v>
       </c>
       <c r="F35">
-        <v>246.6288</v>
+        <v>254.1024</v>
       </c>
       <c r="G35">
         <v>101.9</v>
@@ -4145,28 +4145,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M35">
-        <v>15.80890608</v>
+        <v>16.28796384</v>
       </c>
       <c r="N35">
-        <v>34.84109391999999</v>
+        <v>34.36203615999999</v>
       </c>
       <c r="O35">
-        <v>10.452328176</v>
+        <v>10.308610848</v>
       </c>
       <c r="P35">
-        <v>24.388765744</v>
+        <v>24.05342531199999</v>
       </c>
       <c r="Q35">
-        <v>27.988765744</v>
+        <v>27.653425312</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1398351601427524</v>
+        <v>0.1409420886750216</v>
       </c>
       <c r="T35">
-        <v>1.36832615843489</v>
+        <v>1.384433317330804</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.203890246655194</v>
+        <v>3.109658180577099</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1082775785255143</v>
+        <v>0.1080584997553845</v>
       </c>
       <c r="C36">
-        <v>568.3278108093394</v>
+        <v>563.3896537295135</v>
       </c>
       <c r="D36">
-        <v>720.5302108093395</v>
+        <v>723.0656537295135</v>
       </c>
       <c r="E36">
-        <v>244.9424</v>
+        <v>252.416</v>
       </c>
       <c r="F36">
-        <v>254.1024</v>
+        <v>261.576</v>
       </c>
       <c r="G36">
         <v>101.9</v>
@@ -4227,28 +4227,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M36">
-        <v>16.28796384</v>
+        <v>16.7670216</v>
       </c>
       <c r="N36">
-        <v>34.36203615999999</v>
+        <v>33.88297839999998</v>
       </c>
       <c r="O36">
-        <v>10.308610848</v>
+        <v>10.16489351999999</v>
       </c>
       <c r="P36">
-        <v>24.05342531199999</v>
+        <v>23.71808487999999</v>
       </c>
       <c r="Q36">
-        <v>27.653425312</v>
+        <v>27.31808487999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1409420886750216</v>
+        <v>0.1420830765467454</v>
       </c>
       <c r="T36">
-        <v>1.384433317330804</v>
+        <v>1.401036081115823</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.109658180577099</v>
+        <v>3.020810803989182</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1080584997553845</v>
+        <v>0.1098050209852547</v>
       </c>
       <c r="C37">
-        <v>563.3896537295135</v>
+        <v>536.1855779732518</v>
       </c>
       <c r="D37">
-        <v>723.0656537295135</v>
+        <v>703.3351779732519</v>
       </c>
       <c r="E37">
-        <v>252.416</v>
+        <v>259.8896</v>
       </c>
       <c r="F37">
-        <v>261.576</v>
+        <v>269.0496000000001</v>
       </c>
       <c r="G37">
         <v>101.9</v>
@@ -4309,45 +4309,45 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M37">
-        <v>16.7670216</v>
+        <v>19.34466624000001</v>
       </c>
       <c r="N37">
-        <v>33.88297839999998</v>
+        <v>31.30533375999999</v>
       </c>
       <c r="O37">
-        <v>10.16489351999999</v>
+        <v>9.391600127999995</v>
       </c>
       <c r="P37">
-        <v>23.71808487999999</v>
+        <v>21.91373363199999</v>
       </c>
       <c r="Q37">
-        <v>27.31808487999999</v>
+        <v>25.51373363199999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1420830765467454</v>
+        <v>0.1432597202894605</v>
       </c>
       <c r="T37">
-        <v>1.401036081115823</v>
+        <v>1.418157681269124</v>
       </c>
       <c r="U37">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V37">
         <v>0.3</v>
       </c>
       <c r="W37">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.020810803989182</v>
+        <v>2.618292782703496</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1098050209852547</v>
+        <v>0.1096405422151249</v>
       </c>
       <c r="C38">
-        <v>536.1855779732518</v>
+        <v>530.524050694568</v>
       </c>
       <c r="D38">
-        <v>703.3351779732518</v>
+        <v>705.147250694568</v>
       </c>
       <c r="E38">
-        <v>259.8896</v>
+        <v>267.3631999999999</v>
       </c>
       <c r="F38">
-        <v>269.0496</v>
+        <v>276.5232</v>
       </c>
       <c r="G38">
         <v>101.9</v>
@@ -4391,28 +4391,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M38">
-        <v>19.34466624</v>
+        <v>19.88201808</v>
       </c>
       <c r="N38">
-        <v>31.30533375999999</v>
+        <v>30.76798191999999</v>
       </c>
       <c r="O38">
-        <v>9.391600127999997</v>
+        <v>9.230394575999998</v>
       </c>
       <c r="P38">
-        <v>21.91373363199999</v>
+        <v>21.53758734399999</v>
       </c>
       <c r="Q38">
-        <v>25.51373363199999</v>
+        <v>25.137587344</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1432597202894605</v>
+        <v>0.1444737178017856</v>
       </c>
       <c r="T38">
-        <v>1.418157681269124</v>
+        <v>1.435822824284434</v>
       </c>
       <c r="U38">
         <v>0.07190000000000001</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.618292782703497</v>
+        <v>2.5475281129007</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1096405422151249</v>
+        <v>0.1105134634449952</v>
       </c>
       <c r="C39">
-        <v>530.524050694568</v>
+        <v>513.5387050307141</v>
       </c>
       <c r="D39">
-        <v>705.147250694568</v>
+        <v>695.6355050307142</v>
       </c>
       <c r="E39">
-        <v>267.3631999999999</v>
+        <v>274.8368</v>
       </c>
       <c r="F39">
-        <v>276.5232</v>
+        <v>283.9968</v>
       </c>
       <c r="G39">
         <v>101.9</v>
@@ -4473,45 +4473,45 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M39">
-        <v>19.88201808</v>
+        <v>21.52695744</v>
       </c>
       <c r="N39">
-        <v>30.76798191999999</v>
+        <v>29.12304255999999</v>
       </c>
       <c r="O39">
-        <v>9.230394575999998</v>
+        <v>8.736912767999996</v>
       </c>
       <c r="P39">
-        <v>21.53758734399999</v>
+        <v>20.38612979199999</v>
       </c>
       <c r="Q39">
-        <v>25.137587344</v>
+        <v>23.98612979199999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1444737178017856</v>
+        <v>0.1457268765241858</v>
       </c>
       <c r="T39">
-        <v>1.435822824284434</v>
+        <v>1.454057810622819</v>
       </c>
       <c r="U39">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V39">
         <v>0.3</v>
       </c>
       <c r="W39">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.5475281129007</v>
+        <v>2.352863851808683</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1105134634449952</v>
+        <v>0.1103762846748654</v>
       </c>
       <c r="C40">
-        <v>513.5387050307141</v>
+        <v>507.5428367323625</v>
       </c>
       <c r="D40">
-        <v>695.6355050307142</v>
+        <v>697.1132367323626</v>
       </c>
       <c r="E40">
-        <v>274.8368</v>
+        <v>282.3104</v>
       </c>
       <c r="F40">
-        <v>283.9968</v>
+        <v>291.4704</v>
       </c>
       <c r="G40">
         <v>101.9</v>
@@ -4555,28 +4555,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M40">
-        <v>21.52695744</v>
+        <v>22.09345632</v>
       </c>
       <c r="N40">
-        <v>29.12304255999999</v>
+        <v>28.55654367999999</v>
       </c>
       <c r="O40">
-        <v>8.736912767999996</v>
+        <v>8.566963103999996</v>
       </c>
       <c r="P40">
-        <v>20.38612979199999</v>
+        <v>19.98958057599999</v>
       </c>
       <c r="Q40">
-        <v>23.98612979199999</v>
+        <v>23.58958057599999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1457268765241858</v>
+        <v>0.1470211224178121</v>
       </c>
       <c r="T40">
-        <v>1.454057810622819</v>
+        <v>1.472890665365741</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.352863851808683</v>
+        <v>2.292534009454614</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1103762846748654</v>
+        <v>0.1102391059047356</v>
       </c>
       <c r="C41">
-        <v>507.5428367323625</v>
+        <v>501.5532600612632</v>
       </c>
       <c r="D41">
-        <v>697.1132367323626</v>
+        <v>698.5972600612632</v>
       </c>
       <c r="E41">
-        <v>282.3104</v>
+        <v>289.784</v>
       </c>
       <c r="F41">
-        <v>291.4704</v>
+        <v>298.944</v>
       </c>
       <c r="G41">
         <v>101.9</v>
@@ -4637,28 +4637,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M41">
-        <v>22.09345632</v>
+        <v>22.6599552</v>
       </c>
       <c r="N41">
-        <v>28.55654367999999</v>
+        <v>27.99004479999999</v>
       </c>
       <c r="O41">
-        <v>8.566963103999996</v>
+        <v>8.397013439999997</v>
       </c>
       <c r="P41">
-        <v>19.98958057599999</v>
+        <v>19.59303135999999</v>
       </c>
       <c r="Q41">
-        <v>23.58958057599999</v>
+        <v>23.19303135999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1470211224178121</v>
+        <v>0.148358509841226</v>
       </c>
       <c r="T41">
-        <v>1.472890665365741</v>
+        <v>1.492351281933428</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.292534009454614</v>
+        <v>2.235220659218249</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1102391059047356</v>
+        <v>0.1101019271346058</v>
       </c>
       <c r="C42">
-        <v>501.5532600612632</v>
+        <v>495.5700152842198</v>
       </c>
       <c r="D42">
-        <v>698.5972600612632</v>
+        <v>700.0876152842199</v>
       </c>
       <c r="E42">
-        <v>289.784</v>
+        <v>297.2576</v>
       </c>
       <c r="F42">
-        <v>298.944</v>
+        <v>306.4176</v>
       </c>
       <c r="G42">
         <v>101.9</v>
@@ -4719,28 +4719,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M42">
-        <v>22.6599552</v>
+        <v>23.22645408000001</v>
       </c>
       <c r="N42">
-        <v>27.99004479999999</v>
+        <v>27.42354591999998</v>
       </c>
       <c r="O42">
-        <v>8.397013439999997</v>
+        <v>8.227063775999994</v>
       </c>
       <c r="P42">
-        <v>19.59303135999999</v>
+        <v>19.19648214399999</v>
       </c>
       <c r="Q42">
-        <v>23.19303135999999</v>
+        <v>22.79648214399999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.148358509841226</v>
+        <v>0.1497412324315353</v>
       </c>
       <c r="T42">
-        <v>1.492351281933428</v>
+        <v>1.512471580418663</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.235220659218249</v>
+        <v>2.180703082164145</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1101019271346058</v>
+        <v>0.109964748364476</v>
       </c>
       <c r="C43">
-        <v>495.5700152842198</v>
+        <v>489.5931430123838</v>
       </c>
       <c r="D43">
-        <v>700.0876152842199</v>
+        <v>701.5843430123839</v>
       </c>
       <c r="E43">
-        <v>297.2576</v>
+        <v>304.7312</v>
       </c>
       <c r="F43">
-        <v>306.4176</v>
+        <v>313.8912</v>
       </c>
       <c r="G43">
         <v>101.9</v>
@@ -4801,28 +4801,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M43">
-        <v>23.22645408000001</v>
+        <v>23.79295296</v>
       </c>
       <c r="N43">
-        <v>27.42354591999998</v>
+        <v>26.85704703999999</v>
       </c>
       <c r="O43">
-        <v>8.227063775999994</v>
+        <v>8.057114111999995</v>
       </c>
       <c r="P43">
-        <v>19.19648214399999</v>
+        <v>18.79993292799999</v>
       </c>
       <c r="Q43">
-        <v>22.79648214399999</v>
+        <v>22.39993292799999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1497412324315353</v>
+        <v>0.1511716351111656</v>
       </c>
       <c r="T43">
-        <v>1.512471580418663</v>
+        <v>1.53328568229994</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.180703082164145</v>
+        <v>2.128781580207856</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.109964748364476</v>
+        <v>0.1098275695943463</v>
       </c>
       <c r="C44">
-        <v>489.5931430123839</v>
+        <v>483.6226842049436</v>
       </c>
       <c r="D44">
-        <v>701.5843430123839</v>
+        <v>703.0874842049436</v>
       </c>
       <c r="E44">
-        <v>304.7311999999999</v>
+        <v>312.2048</v>
       </c>
       <c r="F44">
-        <v>313.8912</v>
+        <v>321.3648</v>
       </c>
       <c r="G44">
         <v>101.9</v>
@@ -4883,28 +4883,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M44">
-        <v>23.79295296</v>
+        <v>24.35945184</v>
       </c>
       <c r="N44">
-        <v>26.85704703999999</v>
+        <v>26.29054815999999</v>
       </c>
       <c r="O44">
-        <v>8.057114111999997</v>
+        <v>7.887164447999996</v>
       </c>
       <c r="P44">
-        <v>18.79993292799999</v>
+        <v>18.40338371199999</v>
       </c>
       <c r="Q44">
-        <v>22.39993292799999</v>
+        <v>22.00338371199999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1511716351111656</v>
+        <v>0.1526522273585022</v>
       </c>
       <c r="T44">
-        <v>1.53328568229994</v>
+        <v>1.554830103545473</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.128781580207856</v>
+        <v>2.079275031830929</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1098275695943463</v>
+        <v>0.1096903908242165</v>
       </c>
       <c r="C45">
-        <v>483.6226842049436</v>
+        <v>477.6586801728604</v>
       </c>
       <c r="D45">
-        <v>703.0874842049436</v>
+        <v>704.5970801728605</v>
       </c>
       <c r="E45">
-        <v>312.2048</v>
+        <v>319.6784</v>
       </c>
       <c r="F45">
-        <v>321.3648</v>
+        <v>328.8384</v>
       </c>
       <c r="G45">
         <v>101.9</v>
@@ -4965,28 +4965,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M45">
-        <v>24.35945184</v>
+        <v>24.92595072</v>
       </c>
       <c r="N45">
-        <v>26.29054815999999</v>
+        <v>25.72404927999999</v>
       </c>
       <c r="O45">
-        <v>7.887164447999996</v>
+        <v>7.717214783999996</v>
       </c>
       <c r="P45">
-        <v>18.40338371199999</v>
+        <v>18.00683449599999</v>
       </c>
       <c r="Q45">
-        <v>22.00338371199999</v>
+        <v>21.60683449599999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1526522273585022</v>
+        <v>0.1541856979003866</v>
       </c>
       <c r="T45">
-        <v>1.554830103545473</v>
+        <v>1.577143968406918</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.079275031830929</v>
+        <v>2.032018781107499</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1096903908242165</v>
+        <v>0.1140262120540867</v>
       </c>
       <c r="C46">
-        <v>477.6586801728604</v>
+        <v>425.407466309494</v>
       </c>
       <c r="D46">
-        <v>704.5970801728605</v>
+        <v>659.819466309494</v>
       </c>
       <c r="E46">
-        <v>319.6784</v>
+        <v>327.152</v>
       </c>
       <c r="F46">
-        <v>328.8384</v>
+        <v>336.312</v>
       </c>
       <c r="G46">
         <v>101.9</v>
@@ -5047,45 +5047,45 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M46">
-        <v>24.92595072</v>
+        <v>30.26808</v>
       </c>
       <c r="N46">
-        <v>25.72404927999999</v>
+        <v>20.38191999999999</v>
       </c>
       <c r="O46">
-        <v>7.717214783999996</v>
+        <v>6.114575999999997</v>
       </c>
       <c r="P46">
-        <v>18.00683449599999</v>
+        <v>14.26734399999999</v>
       </c>
       <c r="Q46">
-        <v>21.60683449599999</v>
+        <v>17.867344</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1541856979003866</v>
+        <v>0.1557749310074304</v>
       </c>
       <c r="T46">
-        <v>1.577143968406918</v>
+        <v>1.600269246536052</v>
       </c>
       <c r="U46">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V46">
         <v>0.3</v>
       </c>
       <c r="W46">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.032018781107499</v>
+        <v>1.673380009567835</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1140262120540867</v>
+        <v>0.1139884332839569</v>
       </c>
       <c r="C47">
-        <v>425.407466309494</v>
+        <v>418.2994293052158</v>
       </c>
       <c r="D47">
-        <v>659.819466309494</v>
+        <v>660.1850293052158</v>
       </c>
       <c r="E47">
-        <v>327.152</v>
+        <v>334.6256</v>
       </c>
       <c r="F47">
-        <v>336.312</v>
+        <v>343.7856</v>
       </c>
       <c r="G47">
         <v>101.9</v>
@@ -5129,28 +5129,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M47">
-        <v>30.26808</v>
+        <v>30.940704</v>
       </c>
       <c r="N47">
-        <v>20.38191999999999</v>
+        <v>19.70929599999999</v>
       </c>
       <c r="O47">
-        <v>6.114575999999997</v>
+        <v>5.912788799999996</v>
       </c>
       <c r="P47">
-        <v>14.26734399999999</v>
+        <v>13.79650719999999</v>
       </c>
       <c r="Q47">
-        <v>17.867344</v>
+        <v>17.39650719999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1557749310074304</v>
+        <v>0.1574230245999202</v>
       </c>
       <c r="T47">
-        <v>1.600269246536052</v>
+        <v>1.624251016447746</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.673380009567835</v>
+        <v>1.637002183272882</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1139884332839569</v>
+        <v>0.1139506545138271</v>
       </c>
       <c r="C48">
-        <v>418.2994293052158</v>
+        <v>411.191797594782</v>
       </c>
       <c r="D48">
-        <v>660.1850293052158</v>
+        <v>660.5509975947821</v>
       </c>
       <c r="E48">
-        <v>334.6256</v>
+        <v>342.0992</v>
       </c>
       <c r="F48">
-        <v>343.7856</v>
+        <v>351.2592</v>
       </c>
       <c r="G48">
         <v>101.9</v>
@@ -5211,28 +5211,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M48">
-        <v>30.940704</v>
+        <v>31.613328</v>
       </c>
       <c r="N48">
-        <v>19.70929599999999</v>
+        <v>19.03667199999999</v>
       </c>
       <c r="O48">
-        <v>5.912788799999996</v>
+        <v>5.711001599999998</v>
       </c>
       <c r="P48">
-        <v>13.79650719999999</v>
+        <v>13.32567039999999</v>
       </c>
       <c r="Q48">
-        <v>17.39650719999999</v>
+        <v>16.92567039999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1574230245999202</v>
+        <v>0.1591333104034474</v>
       </c>
       <c r="T48">
-        <v>1.624251016447746</v>
+        <v>1.649137758808938</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.637002183272882</v>
+        <v>1.602172349586225</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1139506545138271</v>
+        <v>0.1139128757436974</v>
       </c>
       <c r="C49">
-        <v>411.191797594782</v>
+        <v>404.0845718525807</v>
       </c>
       <c r="D49">
-        <v>660.5509975947821</v>
+        <v>660.9173718525808</v>
       </c>
       <c r="E49">
-        <v>342.0992</v>
+        <v>349.5728</v>
       </c>
       <c r="F49">
-        <v>351.2592</v>
+        <v>358.7328000000001</v>
       </c>
       <c r="G49">
         <v>101.9</v>
@@ -5293,28 +5293,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M49">
-        <v>31.613328</v>
+        <v>32.285952</v>
       </c>
       <c r="N49">
-        <v>19.03667199999999</v>
+        <v>18.36404799999999</v>
       </c>
       <c r="O49">
-        <v>5.711001599999998</v>
+        <v>5.509214399999997</v>
       </c>
       <c r="P49">
-        <v>13.32567039999999</v>
+        <v>12.85483359999999</v>
       </c>
       <c r="Q49">
-        <v>16.92567039999999</v>
+        <v>16.45483359999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1591333104034474</v>
+        <v>0.1609093764301872</v>
       </c>
       <c r="T49">
-        <v>1.649137758808938</v>
+        <v>1.674981683568638</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.602172349586225</v>
+        <v>1.568793758969845</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1139128757436974</v>
+        <v>0.1138750969735676</v>
       </c>
       <c r="C50">
-        <v>404.0845718525808</v>
+        <v>396.9777527544971</v>
       </c>
       <c r="D50">
-        <v>660.9173718525808</v>
+        <v>661.2841527544971</v>
       </c>
       <c r="E50">
-        <v>349.5728</v>
+        <v>357.0463999999999</v>
       </c>
       <c r="F50">
-        <v>358.7328</v>
+        <v>366.2064</v>
       </c>
       <c r="G50">
         <v>101.9</v>
@@ -5375,28 +5375,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M50">
-        <v>32.285952</v>
+        <v>32.95857599999999</v>
       </c>
       <c r="N50">
-        <v>18.36404799999999</v>
+        <v>17.691424</v>
       </c>
       <c r="O50">
-        <v>5.509214399999997</v>
+        <v>5.307427199999999</v>
       </c>
       <c r="P50">
-        <v>12.85483359999999</v>
+        <v>12.3839968</v>
       </c>
       <c r="Q50">
-        <v>16.45483359999999</v>
+        <v>15.9839968</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1609093764301872</v>
+        <v>0.1627550921050344</v>
       </c>
       <c r="T50">
-        <v>1.674981683568638</v>
+        <v>1.701839095573815</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.568793758969845</v>
+        <v>1.536777559807196</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1138750969735676</v>
+        <v>0.1138373182034378</v>
       </c>
       <c r="C51">
-        <v>396.9777527544971</v>
+        <v>389.871340977917</v>
       </c>
       <c r="D51">
-        <v>661.2841527544971</v>
+        <v>661.651340977917</v>
       </c>
       <c r="E51">
-        <v>357.0463999999999</v>
+        <v>364.52</v>
       </c>
       <c r="F51">
-        <v>366.2064</v>
+        <v>373.68</v>
       </c>
       <c r="G51">
         <v>101.9</v>
@@ -5457,28 +5457,28 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M51">
-        <v>32.95857599999999</v>
+        <v>33.6312</v>
       </c>
       <c r="N51">
-        <v>17.691424</v>
+        <v>17.01879999999999</v>
       </c>
       <c r="O51">
-        <v>5.307427199999999</v>
+        <v>5.105639999999998</v>
       </c>
       <c r="P51">
-        <v>12.3839968</v>
+        <v>11.91315999999999</v>
       </c>
       <c r="Q51">
-        <v>15.9839968</v>
+        <v>15.51316</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1627550921050344</v>
+        <v>0.1646746364068756</v>
       </c>
       <c r="T51">
-        <v>1.701839095573815</v>
+        <v>1.7297708040592</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.536777559807196</v>
+        <v>1.506042008611051</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1138373182034378</v>
+        <v>0.1372200139704764</v>
       </c>
       <c r="C52">
-        <v>389.871340977917</v>
+        <v>213.165738727993</v>
       </c>
       <c r="D52">
-        <v>661.651340977917</v>
+        <v>492.419338727993</v>
       </c>
       <c r="E52">
-        <v>364.52</v>
+        <v>371.9936</v>
       </c>
       <c r="F52">
-        <v>373.68</v>
+        <v>381.1536</v>
       </c>
       <c r="G52">
         <v>101.9</v>
@@ -5539,45 +5539,45 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M52">
-        <v>33.6312</v>
+        <v>55.95334848000001</v>
       </c>
       <c r="N52">
-        <v>17.01879999999999</v>
+        <v>-5.303348480000018</v>
       </c>
       <c r="O52">
-        <v>5.105639999999998</v>
+        <v>-1.591004544000005</v>
       </c>
       <c r="P52">
-        <v>11.91315999999999</v>
+        <v>-3.712343936000013</v>
       </c>
       <c r="Q52">
-        <v>15.51316</v>
+        <v>-0.1123439360000114</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1646746364068756</v>
+        <v>0.1687420022178072</v>
       </c>
       <c r="T52">
-        <v>1.7297708040592</v>
+        <v>1.788955932542766</v>
       </c>
       <c r="U52">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.3</v>
+        <v>0.2715655168596622</v>
       </c>
       <c r="W52">
-        <v>0.063</v>
+        <v>0.1069341821250016</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y52">
-        <v>1.506042008611051</v>
+        <v>0.9052183895322073</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1372200139704764</v>
+        <v>0.1382300139704764</v>
       </c>
       <c r="C53">
-        <v>213.165738727993</v>
+        <v>200.3113807820499</v>
       </c>
       <c r="D53">
-        <v>492.419338727993</v>
+        <v>487.0385807820499</v>
       </c>
       <c r="E53">
-        <v>371.9936</v>
+        <v>379.4672</v>
       </c>
       <c r="F53">
-        <v>381.1536</v>
+        <v>388.6272</v>
       </c>
       <c r="G53">
         <v>101.9</v>
@@ -5621,37 +5621,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M53">
-        <v>55.95334848000001</v>
+        <v>57.05047296000001</v>
       </c>
       <c r="N53">
-        <v>-5.303348480000018</v>
+        <v>-6.400472960000016</v>
       </c>
       <c r="O53">
-        <v>-1.591004544000005</v>
+        <v>-1.920141888000005</v>
       </c>
       <c r="P53">
-        <v>-3.712343936000013</v>
+        <v>-4.480331072000011</v>
       </c>
       <c r="Q53">
-        <v>-0.1123439360000114</v>
+        <v>-0.8803310720000095</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1687420022178072</v>
+        <v>0.1713032939306782</v>
       </c>
       <c r="T53">
-        <v>1.788955932542766</v>
+        <v>1.826225847804074</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.2715655168596622</v>
+        <v>0.2663431030738995</v>
       </c>
       <c r="W53">
-        <v>0.1069341821250016</v>
+        <v>0.1077008324687516</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.9052183895322073</v>
+        <v>0.8878103435796649</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1382300139704764</v>
+        <v>0.1392400139704764</v>
       </c>
       <c r="C54">
-        <v>200.3113807820499</v>
+        <v>187.5733448547898</v>
       </c>
       <c r="D54">
-        <v>487.0385807820499</v>
+        <v>481.7741448547898</v>
       </c>
       <c r="E54">
-        <v>379.4672</v>
+        <v>386.9408</v>
       </c>
       <c r="F54">
-        <v>388.6272</v>
+        <v>396.1008</v>
       </c>
       <c r="G54">
         <v>101.9</v>
@@ -5703,37 +5703,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M54">
-        <v>57.05047296000001</v>
+        <v>58.14759744000001</v>
       </c>
       <c r="N54">
-        <v>-6.400472960000016</v>
+        <v>-7.497597440000021</v>
       </c>
       <c r="O54">
-        <v>-1.920141888000005</v>
+        <v>-2.249279232000006</v>
       </c>
       <c r="P54">
-        <v>-4.480331072000011</v>
+        <v>-5.248318208000015</v>
       </c>
       <c r="Q54">
-        <v>-0.8803310720000095</v>
+        <v>-1.648318208000013</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1713032939306782</v>
+        <v>0.1739735767802671</v>
       </c>
       <c r="T54">
-        <v>1.826225847804074</v>
+        <v>1.865081716906288</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.2663431030738995</v>
+        <v>0.2613177615064674</v>
       </c>
       <c r="W54">
-        <v>0.1077008324687516</v>
+        <v>0.1084385526108506</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8878103435796649</v>
+        <v>0.871059205021558</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1392400139704764</v>
+        <v>0.1402500139704764</v>
       </c>
       <c r="C55">
-        <v>187.5733448547898</v>
+        <v>174.9478992822159</v>
       </c>
       <c r="D55">
-        <v>481.7741448547898</v>
+        <v>476.6222992822159</v>
       </c>
       <c r="E55">
-        <v>386.9408</v>
+        <v>394.4144</v>
       </c>
       <c r="F55">
-        <v>396.1008</v>
+        <v>403.5744</v>
       </c>
       <c r="G55">
         <v>101.9</v>
@@ -5785,37 +5785,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M55">
-        <v>58.14759744000001</v>
+        <v>59.24472192000001</v>
       </c>
       <c r="N55">
-        <v>-7.497597440000021</v>
+        <v>-8.594721920000019</v>
       </c>
       <c r="O55">
-        <v>-2.249279232000006</v>
+        <v>-2.578416576000006</v>
       </c>
       <c r="P55">
-        <v>-5.248318208000015</v>
+        <v>-6.016305344000013</v>
       </c>
       <c r="Q55">
-        <v>-1.648318208000013</v>
+        <v>-2.416305344000012</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1739735767802671</v>
+        <v>0.176759958884186</v>
       </c>
       <c r="T55">
-        <v>1.865081716906288</v>
+        <v>1.905626971621643</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.2613177615064674</v>
+        <v>0.256478543700792</v>
       </c>
       <c r="W55">
-        <v>0.1084385526108506</v>
+        <v>0.1091489497847237</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.871059205021558</v>
+        <v>0.8549284790026402</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1402500139704764</v>
+        <v>0.1412600139704764</v>
       </c>
       <c r="C56">
-        <v>174.9478992822159</v>
+        <v>162.4314703295202</v>
       </c>
       <c r="D56">
-        <v>476.6222992822159</v>
+        <v>471.5794703295203</v>
       </c>
       <c r="E56">
-        <v>394.4144</v>
+        <v>401.888</v>
       </c>
       <c r="F56">
-        <v>403.5744</v>
+        <v>411.0480000000001</v>
       </c>
       <c r="G56">
         <v>101.9</v>
@@ -5867,37 +5867,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M56">
-        <v>59.24472192000001</v>
+        <v>60.34184640000002</v>
       </c>
       <c r="N56">
-        <v>-8.594721920000019</v>
+        <v>-9.691846400000024</v>
       </c>
       <c r="O56">
-        <v>-2.578416576000006</v>
+        <v>-2.907553920000007</v>
       </c>
       <c r="P56">
-        <v>-6.016305344000013</v>
+        <v>-6.784292480000017</v>
       </c>
       <c r="Q56">
-        <v>-2.416305344000012</v>
+        <v>-3.184292480000016</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.176759958884186</v>
+        <v>0.1796701801927235</v>
       </c>
       <c r="T56">
-        <v>1.905626971621643</v>
+        <v>1.947974237657679</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.256478543700792</v>
+        <v>0.2518152974516867</v>
       </c>
       <c r="W56">
-        <v>0.1091489497847237</v>
+        <v>0.1098335143340924</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8549284790026402</v>
+        <v>0.8393843248389559</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1412600139704764</v>
+        <v>0.1422700139704764</v>
       </c>
       <c r="C57">
-        <v>162.4314703295202</v>
+        <v>150.0206339238267</v>
       </c>
       <c r="D57">
-        <v>471.5794703295203</v>
+        <v>466.6422339238267</v>
       </c>
       <c r="E57">
-        <v>401.888</v>
+        <v>409.3616</v>
       </c>
       <c r="F57">
-        <v>411.0480000000001</v>
+        <v>418.5216</v>
       </c>
       <c r="G57">
         <v>101.9</v>
@@ -5949,37 +5949,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M57">
-        <v>60.34184640000002</v>
+        <v>61.43897088000001</v>
       </c>
       <c r="N57">
-        <v>-9.691846400000024</v>
+        <v>-10.78897088000002</v>
       </c>
       <c r="O57">
-        <v>-2.907553920000007</v>
+        <v>-3.236691264000007</v>
       </c>
       <c r="P57">
-        <v>-6.784292480000017</v>
+        <v>-7.552279616000016</v>
       </c>
       <c r="Q57">
-        <v>-3.184292480000016</v>
+        <v>-3.952279616000014</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1796701801927235</v>
+        <v>0.1827126842880126</v>
       </c>
       <c r="T57">
-        <v>1.947974237657679</v>
+        <v>1.992246379422626</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2518152974516867</v>
+        <v>0.2473185957114781</v>
       </c>
       <c r="W57">
-        <v>0.1098335143340924</v>
+        <v>0.110493630149555</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8393843248389559</v>
+        <v>0.8243953190382602</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1422700139704764</v>
+        <v>0.1432800139704763</v>
       </c>
       <c r="C58">
-        <v>150.0206339238267</v>
+        <v>137.71210790088</v>
       </c>
       <c r="D58">
-        <v>466.6422339238267</v>
+        <v>461.8073079008801</v>
       </c>
       <c r="E58">
-        <v>409.3616</v>
+        <v>416.8352</v>
       </c>
       <c r="F58">
-        <v>418.5216</v>
+        <v>425.9952000000001</v>
       </c>
       <c r="G58">
         <v>101.9</v>
@@ -6031,37 +6031,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M58">
-        <v>61.43897088000001</v>
+        <v>62.53609536000002</v>
       </c>
       <c r="N58">
-        <v>-10.78897088000002</v>
+        <v>-11.88609536000003</v>
       </c>
       <c r="O58">
-        <v>-3.236691264000007</v>
+        <v>-3.565828608000008</v>
       </c>
       <c r="P58">
-        <v>-7.552279616000016</v>
+        <v>-8.32026675200002</v>
       </c>
       <c r="Q58">
-        <v>-3.952279616000014</v>
+        <v>-4.720266752000018</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1827126842880126</v>
+        <v>0.1858967002016873</v>
       </c>
       <c r="T58">
-        <v>1.992246379422626</v>
+        <v>2.03857769057199</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2473185957114781</v>
+        <v>0.2429796729796977</v>
       </c>
       <c r="W58">
-        <v>0.110493630149555</v>
+        <v>0.1111305840065804</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8243953190382602</v>
+        <v>0.8099322432656592</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1432800139704763</v>
+        <v>0.1782144586101819</v>
       </c>
       <c r="C59">
-        <v>137.71210790088</v>
+        <v>8.401497038123523</v>
       </c>
       <c r="D59">
-        <v>461.8073079008801</v>
+        <v>339.9702970381235</v>
       </c>
       <c r="E59">
-        <v>416.8352</v>
+        <v>424.3088</v>
       </c>
       <c r="F59">
-        <v>425.9952000000001</v>
+        <v>433.4688</v>
       </c>
       <c r="G59">
         <v>101.9</v>
@@ -6113,45 +6113,45 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M59">
-        <v>62.53609536000002</v>
+        <v>87.04053504000001</v>
       </c>
       <c r="N59">
-        <v>-11.88609536000003</v>
+        <v>-36.39053504000002</v>
       </c>
       <c r="O59">
-        <v>-3.565828608000008</v>
+        <v>-10.917160512</v>
       </c>
       <c r="P59">
-        <v>-8.32026675200002</v>
+        <v>-25.47337452800002</v>
       </c>
       <c r="Q59">
-        <v>-4.720266752000018</v>
+        <v>-21.87337452800001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1858967002016873</v>
+        <v>0.1954333945867407</v>
       </c>
       <c r="T59">
-        <v>2.03857769057199</v>
+        <v>2.17734821398321</v>
       </c>
       <c r="U59">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.2429796729796977</v>
+        <v>0.1745738349726026</v>
       </c>
       <c r="W59">
-        <v>0.1111305840065804</v>
+        <v>0.1657455739375014</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.8099322432656592</v>
+        <v>0.5819127832420088</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1782144586101819</v>
+        <v>0.1797644586101819</v>
       </c>
       <c r="C60">
-        <v>8.401497038123694</v>
+        <v>-3.005638512096027</v>
       </c>
       <c r="D60">
-        <v>339.9702970381236</v>
+        <v>336.0367614879039</v>
       </c>
       <c r="E60">
-        <v>424.3088</v>
+        <v>431.7823999999999</v>
       </c>
       <c r="F60">
-        <v>433.4688</v>
+        <v>440.9424</v>
       </c>
       <c r="G60">
         <v>101.9</v>
@@ -6195,37 +6195,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M60">
-        <v>87.04053503999999</v>
+        <v>88.54123392</v>
       </c>
       <c r="N60">
-        <v>-36.39053504</v>
+        <v>-37.89123392</v>
       </c>
       <c r="O60">
-        <v>-10.917160512</v>
+        <v>-11.367370176</v>
       </c>
       <c r="P60">
-        <v>-25.473374528</v>
+        <v>-26.523863744</v>
       </c>
       <c r="Q60">
-        <v>-21.873374528</v>
+        <v>-22.923863744</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1954333945867406</v>
+        <v>0.1990829895766611</v>
       </c>
       <c r="T60">
-        <v>2.177348213983209</v>
+        <v>2.230454267982799</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1745738349726026</v>
+        <v>0.171614956413745</v>
       </c>
       <c r="W60">
-        <v>0.1657455739375014</v>
+        <v>0.16633971675212</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5819127832420088</v>
+        <v>0.5720498547124833</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1797644586101819</v>
+        <v>0.1813144586101819</v>
       </c>
       <c r="C61">
-        <v>-3.005638512096027</v>
+        <v>-14.32279133773619</v>
       </c>
       <c r="D61">
-        <v>336.0367614879039</v>
+        <v>332.1932086622638</v>
       </c>
       <c r="E61">
-        <v>431.7823999999999</v>
+        <v>439.256</v>
       </c>
       <c r="F61">
-        <v>440.9424</v>
+        <v>448.416</v>
       </c>
       <c r="G61">
         <v>101.9</v>
@@ -6277,37 +6277,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M61">
-        <v>88.54123392</v>
+        <v>90.0419328</v>
       </c>
       <c r="N61">
-        <v>-37.89123392</v>
+        <v>-39.39193280000001</v>
       </c>
       <c r="O61">
-        <v>-11.367370176</v>
+        <v>-11.81757984</v>
       </c>
       <c r="P61">
-        <v>-26.523863744</v>
+        <v>-27.57435296000001</v>
       </c>
       <c r="Q61">
-        <v>-22.923863744</v>
+        <v>-23.97435296</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1990829895766611</v>
+        <v>0.2029150643160776</v>
       </c>
       <c r="T61">
-        <v>2.230454267982799</v>
+        <v>2.286215624682369</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.171614956413745</v>
+        <v>0.1687547071401826</v>
       </c>
       <c r="W61">
-        <v>0.16633971675212</v>
+        <v>0.1669140548062513</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5720498547124833</v>
+        <v>0.5625156904672752</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1813144586101819</v>
+        <v>0.1828644586101819</v>
       </c>
       <c r="C62">
-        <v>-14.32279133773619</v>
+        <v>-25.55301416065868</v>
       </c>
       <c r="D62">
-        <v>332.1932086622638</v>
+        <v>328.4365858393413</v>
       </c>
       <c r="E62">
-        <v>439.256</v>
+        <v>446.7295999999999</v>
       </c>
       <c r="F62">
-        <v>448.416</v>
+        <v>455.8896</v>
       </c>
       <c r="G62">
         <v>101.9</v>
@@ -6359,37 +6359,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M62">
-        <v>90.0419328</v>
+        <v>91.54263168</v>
       </c>
       <c r="N62">
-        <v>-39.39193280000001</v>
+        <v>-40.89263168000001</v>
       </c>
       <c r="O62">
-        <v>-11.81757984</v>
+        <v>-12.267789504</v>
       </c>
       <c r="P62">
-        <v>-27.57435296000001</v>
+        <v>-28.62484217600001</v>
       </c>
       <c r="Q62">
-        <v>-23.97435296</v>
+        <v>-25.02484217600001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2029150643160776</v>
+        <v>0.2069436557087976</v>
       </c>
       <c r="T62">
-        <v>2.286215624682369</v>
+        <v>2.344836538135764</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1687547071401826</v>
+        <v>0.1659882365313271</v>
       </c>
       <c r="W62">
-        <v>0.1669140548062513</v>
+        <v>0.1674695621045095</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5625156904672752</v>
+        <v>0.5532941217710903</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1828644586101819</v>
+        <v>0.1844144586101819</v>
       </c>
       <c r="C63">
-        <v>-25.55301416065868</v>
+        <v>-36.69922315942574</v>
       </c>
       <c r="D63">
-        <v>328.4365858393413</v>
+        <v>324.7639768405743</v>
       </c>
       <c r="E63">
-        <v>446.7295999999999</v>
+        <v>454.2032</v>
       </c>
       <c r="F63">
-        <v>455.8896</v>
+        <v>463.3632</v>
       </c>
       <c r="G63">
         <v>101.9</v>
@@ -6441,37 +6441,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M63">
-        <v>91.54263168</v>
+        <v>93.04333056</v>
       </c>
       <c r="N63">
-        <v>-40.89263168000001</v>
+        <v>-42.39333056000001</v>
       </c>
       <c r="O63">
-        <v>-12.267789504</v>
+        <v>-12.717999168</v>
       </c>
       <c r="P63">
-        <v>-28.62484217600001</v>
+        <v>-29.67533139200001</v>
       </c>
       <c r="Q63">
-        <v>-25.02484217600001</v>
+        <v>-26.07533139200001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2069436557087976</v>
+        <v>0.2111842782274502</v>
       </c>
       <c r="T63">
-        <v>2.344836538135764</v>
+        <v>2.406542762823547</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1659882365313271</v>
+        <v>0.1633110069098541</v>
       </c>
       <c r="W63">
-        <v>0.1674695621045095</v>
+        <v>0.1680071498125013</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5532941217710903</v>
+        <v>0.544370023032847</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1844144586101819</v>
+        <v>0.1859644586101819</v>
       </c>
       <c r="C64">
-        <v>-36.69922315942574</v>
+        <v>-47.76420551907847</v>
       </c>
       <c r="D64">
-        <v>324.7639768405743</v>
+        <v>321.1725944809215</v>
       </c>
       <c r="E64">
-        <v>454.2032</v>
+        <v>461.6768</v>
       </c>
       <c r="F64">
-        <v>463.3632</v>
+        <v>470.8368</v>
       </c>
       <c r="G64">
         <v>101.9</v>
@@ -6523,37 +6523,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M64">
-        <v>93.04333056</v>
+        <v>94.54402944000002</v>
       </c>
       <c r="N64">
-        <v>-42.39333056000001</v>
+        <v>-43.89402944000003</v>
       </c>
       <c r="O64">
-        <v>-12.717999168</v>
+        <v>-13.16820883200001</v>
       </c>
       <c r="P64">
-        <v>-29.67533139200001</v>
+        <v>-30.72582060800002</v>
       </c>
       <c r="Q64">
-        <v>-26.07533139200001</v>
+        <v>-27.12582060800002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2111842782274502</v>
+        <v>0.2156541235849488</v>
       </c>
       <c r="T64">
-        <v>2.406542762823547</v>
+        <v>2.471584459116075</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1633110069098541</v>
+        <v>0.1607187687049357</v>
       </c>
       <c r="W64">
-        <v>0.1680071498125013</v>
+        <v>0.1685276712440489</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.544370023032847</v>
+        <v>0.5357292290164524</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1859644586101819</v>
+        <v>0.1875144586101819</v>
       </c>
       <c r="C65">
-        <v>-47.76420551907847</v>
+        <v>-58.75062648546128</v>
       </c>
       <c r="D65">
-        <v>321.1725944809215</v>
+        <v>317.6597735145387</v>
       </c>
       <c r="E65">
-        <v>461.6768</v>
+        <v>469.1504</v>
       </c>
       <c r="F65">
-        <v>470.8368</v>
+        <v>478.3104</v>
       </c>
       <c r="G65">
         <v>101.9</v>
@@ -6605,37 +6605,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M65">
-        <v>94.54402944000002</v>
+        <v>96.04472832</v>
       </c>
       <c r="N65">
-        <v>-43.89402944000003</v>
+        <v>-45.39472832000001</v>
       </c>
       <c r="O65">
-        <v>-13.16820883200001</v>
+        <v>-13.618418496</v>
       </c>
       <c r="P65">
-        <v>-30.72582060800002</v>
+        <v>-31.77630982400001</v>
       </c>
       <c r="Q65">
-        <v>-27.12582060800002</v>
+        <v>-28.17630982400001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2156541235849488</v>
+        <v>0.2203722936845308</v>
       </c>
       <c r="T65">
-        <v>2.471584459116075</v>
+        <v>2.540239582980411</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1607187687049357</v>
+        <v>0.1582075379439211</v>
       </c>
       <c r="W65">
-        <v>0.1685276712440489</v>
+        <v>0.1690319263808606</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5357292290164524</v>
+        <v>0.5273584598130705</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1875144586101819</v>
+        <v>0.1890644586101819</v>
       </c>
       <c r="C66">
-        <v>-58.75062648546128</v>
+        <v>-69.66103596161514</v>
       </c>
       <c r="D66">
-        <v>317.6597735145387</v>
+        <v>314.2229640383849</v>
       </c>
       <c r="E66">
-        <v>469.1504</v>
+        <v>476.624</v>
       </c>
       <c r="F66">
-        <v>478.3104</v>
+        <v>485.784</v>
       </c>
       <c r="G66">
         <v>101.9</v>
@@ -6687,37 +6687,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M66">
-        <v>96.04472832</v>
+        <v>97.54542720000001</v>
       </c>
       <c r="N66">
-        <v>-45.39472832000001</v>
+        <v>-46.89542720000001</v>
       </c>
       <c r="O66">
-        <v>-13.618418496</v>
+        <v>-14.06862816</v>
       </c>
       <c r="P66">
-        <v>-31.77630982400001</v>
+        <v>-32.82679904000001</v>
       </c>
       <c r="Q66">
-        <v>-28.17630982400001</v>
+        <v>-29.22679904000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2203722936845308</v>
+        <v>0.2253600735040888</v>
       </c>
       <c r="T66">
-        <v>2.540239582980411</v>
+        <v>2.612817856779852</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1582075379439211</v>
+        <v>0.1557735758217069</v>
       </c>
       <c r="W66">
-        <v>0.1690319263808606</v>
+        <v>0.1695206659750013</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5273584598130705</v>
+        <v>0.5192452527390232</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1890644586101819</v>
+        <v>0.1906144586101819</v>
       </c>
       <c r="C67">
-        <v>-69.66103596161514</v>
+        <v>-80.49787468055104</v>
       </c>
       <c r="D67">
-        <v>314.2229640383849</v>
+        <v>310.859725319449</v>
       </c>
       <c r="E67">
-        <v>476.624</v>
+        <v>484.0976</v>
       </c>
       <c r="F67">
-        <v>485.784</v>
+        <v>493.2576</v>
       </c>
       <c r="G67">
         <v>101.9</v>
@@ -6769,37 +6769,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M67">
-        <v>97.54542720000001</v>
+        <v>99.04612608000001</v>
       </c>
       <c r="N67">
-        <v>-46.89542720000001</v>
+        <v>-48.39612608000002</v>
       </c>
       <c r="O67">
-        <v>-14.06862816</v>
+        <v>-14.518837824</v>
       </c>
       <c r="P67">
-        <v>-32.82679904000001</v>
+        <v>-33.87728825600001</v>
       </c>
       <c r="Q67">
-        <v>-29.22679904000001</v>
+        <v>-30.27728825600001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2253600735040888</v>
+        <v>0.230641252136562</v>
       </c>
       <c r="T67">
-        <v>2.612817856779852</v>
+        <v>2.689665440802788</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1557735758217069</v>
+        <v>0.1534133701274387</v>
       </c>
       <c r="W67">
-        <v>0.1695206659750013</v>
+        <v>0.1699945952784103</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5192452527390232</v>
+        <v>0.5113779004247956</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1906144586101819</v>
+        <v>0.1921644586101819</v>
       </c>
       <c r="C68">
-        <v>-80.49787468055104</v>
+        <v>-91.26347998580366</v>
       </c>
       <c r="D68">
-        <v>310.859725319449</v>
+        <v>307.5677200141964</v>
       </c>
       <c r="E68">
-        <v>484.0976</v>
+        <v>491.5712</v>
       </c>
       <c r="F68">
-        <v>493.2576</v>
+        <v>500.7312000000001</v>
       </c>
       <c r="G68">
         <v>101.9</v>
@@ -6851,37 +6851,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M68">
-        <v>99.04612608000001</v>
+        <v>100.54682496</v>
       </c>
       <c r="N68">
-        <v>-48.39612608000002</v>
+        <v>-49.89682496000002</v>
       </c>
       <c r="O68">
-        <v>-14.518837824</v>
+        <v>-14.969047488</v>
       </c>
       <c r="P68">
-        <v>-33.87728825600001</v>
+        <v>-34.92777747200002</v>
       </c>
       <c r="Q68">
-        <v>-30.27728825600001</v>
+        <v>-31.32777747200002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.230641252136562</v>
+        <v>0.2362425022013063</v>
       </c>
       <c r="T68">
-        <v>2.689665440802788</v>
+        <v>2.771170454160448</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1534133701274387</v>
+        <v>0.1511236183344918</v>
       </c>
       <c r="W68">
-        <v>0.1699945952784103</v>
+        <v>0.1704543774384341</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5113779004247956</v>
+        <v>0.5037453944483061</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1921644586101819</v>
+        <v>0.2185653834805057</v>
       </c>
       <c r="C69">
-        <v>-91.26347998580366</v>
+        <v>-145.7376544356489</v>
       </c>
       <c r="D69">
-        <v>307.5677200141964</v>
+        <v>260.5671455643511</v>
       </c>
       <c r="E69">
-        <v>491.5712</v>
+        <v>499.0448</v>
       </c>
       <c r="F69">
-        <v>500.7312000000001</v>
+        <v>508.2048</v>
       </c>
       <c r="G69">
         <v>101.9</v>
@@ -6933,45 +6933,45 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M69">
-        <v>100.54682496</v>
+        <v>119.83469184</v>
       </c>
       <c r="N69">
-        <v>-49.89682496000002</v>
+        <v>-69.18469184000003</v>
       </c>
       <c r="O69">
-        <v>-14.969047488</v>
+        <v>-20.75540755200001</v>
       </c>
       <c r="P69">
-        <v>-34.92777747200002</v>
+        <v>-48.42928428800002</v>
       </c>
       <c r="Q69">
-        <v>-31.32777747200002</v>
+        <v>-44.82928428800002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2362425022013063</v>
+        <v>0.245477970614859</v>
       </c>
       <c r="T69">
-        <v>2.771170454160448</v>
+        <v>2.905557772653651</v>
       </c>
       <c r="U69">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1511236183344918</v>
+        <v>0.1267996751749313</v>
       </c>
       <c r="W69">
-        <v>0.1704543774384341</v>
+        <v>0.2059006365937512</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.5037453944483061</v>
+        <v>0.4226655839164378</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2185653834805057</v>
+        <v>0.2204653834805057</v>
       </c>
       <c r="C70">
-        <v>-145.7376544356489</v>
+        <v>-156.0456888651106</v>
       </c>
       <c r="D70">
-        <v>260.5671455643511</v>
+        <v>257.7327111348894</v>
       </c>
       <c r="E70">
-        <v>499.0448</v>
+        <v>506.5184</v>
       </c>
       <c r="F70">
-        <v>508.2048</v>
+        <v>515.6784</v>
       </c>
       <c r="G70">
         <v>101.9</v>
@@ -7015,37 +7015,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M70">
-        <v>119.83469184</v>
+        <v>121.59696672</v>
       </c>
       <c r="N70">
-        <v>-69.18469184000003</v>
+        <v>-70.94696672000002</v>
       </c>
       <c r="O70">
-        <v>-20.75540755200001</v>
+        <v>-21.284090016</v>
       </c>
       <c r="P70">
-        <v>-48.42928428800002</v>
+        <v>-49.66287670400001</v>
       </c>
       <c r="Q70">
-        <v>-44.82928428800002</v>
+        <v>-46.06287670400001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.245477970614859</v>
+        <v>0.2519191954734028</v>
       </c>
       <c r="T70">
-        <v>2.905557772653651</v>
+        <v>2.999285442739252</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1267996751749313</v>
+        <v>0.1249619987231207</v>
       </c>
       <c r="W70">
-        <v>0.2059006365937512</v>
+        <v>0.2063339607010881</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4226655839164378</v>
+        <v>0.4165399957437358</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2204653834805057</v>
+        <v>0.2223653834805057</v>
       </c>
       <c r="C71">
-        <v>-156.0456888651106</v>
+        <v>-166.2927212418502</v>
       </c>
       <c r="D71">
-        <v>257.7327111348894</v>
+        <v>254.9592787581498</v>
       </c>
       <c r="E71">
-        <v>506.5184</v>
+        <v>513.9920000000001</v>
       </c>
       <c r="F71">
-        <v>515.6784</v>
+        <v>523.152</v>
       </c>
       <c r="G71">
         <v>101.9</v>
@@ -7097,37 +7097,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M71">
-        <v>121.59696672</v>
+        <v>123.3592416</v>
       </c>
       <c r="N71">
-        <v>-70.94696672000002</v>
+        <v>-72.70924160000003</v>
       </c>
       <c r="O71">
-        <v>-21.284090016</v>
+        <v>-21.81277248000001</v>
       </c>
       <c r="P71">
-        <v>-49.66287670400001</v>
+        <v>-50.89646912000002</v>
       </c>
       <c r="Q71">
-        <v>-46.06287670400001</v>
+        <v>-47.29646912000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2519191954734028</v>
+        <v>0.2587898353225162</v>
       </c>
       <c r="T71">
-        <v>2.999285442739252</v>
+        <v>3.099261624163894</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1249619987231207</v>
+        <v>0.1231768273127904</v>
       </c>
       <c r="W71">
-        <v>0.2063339607010881</v>
+        <v>0.206754904119644</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4165399957437358</v>
+        <v>0.4105894243759681</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2223653834805057</v>
+        <v>0.2242653834805057</v>
       </c>
       <c r="C72">
-        <v>-166.2927212418502</v>
+        <v>-176.480699908419</v>
       </c>
       <c r="D72">
-        <v>254.9592787581498</v>
+        <v>252.2449000915811</v>
       </c>
       <c r="E72">
-        <v>513.9920000000001</v>
+        <v>521.4656000000001</v>
       </c>
       <c r="F72">
-        <v>523.152</v>
+        <v>530.6256000000001</v>
       </c>
       <c r="G72">
         <v>101.9</v>
@@ -7179,37 +7179,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M72">
-        <v>123.3592416</v>
+        <v>125.12151648</v>
       </c>
       <c r="N72">
-        <v>-72.70924160000003</v>
+        <v>-74.47151648000003</v>
       </c>
       <c r="O72">
-        <v>-21.81277248000001</v>
+        <v>-22.34145494400001</v>
       </c>
       <c r="P72">
-        <v>-50.89646912000002</v>
+        <v>-52.13006153600003</v>
       </c>
       <c r="Q72">
-        <v>-47.29646912000002</v>
+        <v>-48.53006153600003</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2587898353225162</v>
+        <v>0.266134312402603</v>
       </c>
       <c r="T72">
-        <v>3.099261624163894</v>
+        <v>3.206132714652305</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1231768273127904</v>
+        <v>0.121441942421061</v>
       </c>
       <c r="W72">
-        <v>0.206754904119644</v>
+        <v>0.2071639899771138</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4105894243759681</v>
+        <v>0.40480647473687</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2242653834805057</v>
+        <v>0.2261653834805057</v>
       </c>
       <c r="C73">
-        <v>-176.4806999084189</v>
+        <v>-186.6114911106642</v>
       </c>
       <c r="D73">
-        <v>252.2449000915811</v>
+        <v>249.5877088893357</v>
       </c>
       <c r="E73">
-        <v>521.4656</v>
+        <v>528.9392</v>
       </c>
       <c r="F73">
-        <v>530.6256</v>
+        <v>538.0992</v>
       </c>
       <c r="G73">
         <v>101.9</v>
@@ -7261,37 +7261,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M73">
-        <v>125.12151648</v>
+        <v>126.88379136</v>
       </c>
       <c r="N73">
-        <v>-74.47151648000001</v>
+        <v>-76.23379136000001</v>
       </c>
       <c r="O73">
-        <v>-22.341454944</v>
+        <v>-22.870137408</v>
       </c>
       <c r="P73">
-        <v>-52.130061536</v>
+        <v>-53.36365395200001</v>
       </c>
       <c r="Q73">
-        <v>-48.530061536</v>
+        <v>-49.76365395200001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2661343124026029</v>
+        <v>0.2740033949884102</v>
       </c>
       <c r="T73">
-        <v>3.206132714652303</v>
+        <v>3.320637454461314</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.121441942421061</v>
+        <v>0.1197552487763241</v>
       </c>
       <c r="W73">
-        <v>0.2071639899771138</v>
+        <v>0.2075617123385428</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.40480647473687</v>
+        <v>0.3991841625877468</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2261653834805057</v>
+        <v>0.2280653834805057</v>
       </c>
       <c r="C74">
-        <v>-186.6114911106642</v>
+        <v>-196.6868832767585</v>
       </c>
       <c r="D74">
-        <v>249.5877088893357</v>
+        <v>246.9859167232415</v>
       </c>
       <c r="E74">
-        <v>528.9392</v>
+        <v>536.4128000000001</v>
       </c>
       <c r="F74">
-        <v>538.0992</v>
+        <v>545.5728</v>
       </c>
       <c r="G74">
         <v>101.9</v>
@@ -7343,37 +7343,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M74">
-        <v>126.88379136</v>
+        <v>128.64606624</v>
       </c>
       <c r="N74">
-        <v>-76.23379136000001</v>
+        <v>-77.99606624000002</v>
       </c>
       <c r="O74">
-        <v>-22.870137408</v>
+        <v>-23.398819872</v>
       </c>
       <c r="P74">
-        <v>-53.36365395200001</v>
+        <v>-54.59724636800001</v>
       </c>
       <c r="Q74">
-        <v>-49.76365395200001</v>
+        <v>-50.99724636800001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2740033949884102</v>
+        <v>0.2824553725805735</v>
       </c>
       <c r="T74">
-        <v>3.320637454461314</v>
+        <v>3.44362402684877</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1197552487763241</v>
+        <v>0.1181147659163744</v>
       </c>
       <c r="W74">
-        <v>0.2075617123385428</v>
+        <v>0.2079485381969189</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3991841625877468</v>
+        <v>0.3937158863879147</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2280653834805057</v>
+        <v>0.2299653834805057</v>
       </c>
       <c r="C75">
-        <v>-196.6868832767585</v>
+        <v>-206.7085910313508</v>
       </c>
       <c r="D75">
-        <v>246.9859167232415</v>
+        <v>244.4378089686491</v>
       </c>
       <c r="E75">
-        <v>536.4128000000001</v>
+        <v>543.8864</v>
       </c>
       <c r="F75">
-        <v>545.5728</v>
+        <v>553.0463999999999</v>
       </c>
       <c r="G75">
         <v>101.9</v>
@@ -7425,37 +7425,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M75">
-        <v>128.64606624</v>
+        <v>130.40834112</v>
       </c>
       <c r="N75">
-        <v>-77.99606624000002</v>
+        <v>-79.75834112</v>
       </c>
       <c r="O75">
-        <v>-23.398819872</v>
+        <v>-23.927502336</v>
       </c>
       <c r="P75">
-        <v>-54.59724636800001</v>
+        <v>-55.83083878399999</v>
       </c>
       <c r="Q75">
-        <v>-50.99724636800001</v>
+        <v>-52.23083878399999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2824553725805735</v>
+        <v>0.291557502295211</v>
       </c>
       <c r="T75">
-        <v>3.44362402684877</v>
+        <v>3.576071104804492</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1181147659163744</v>
+        <v>0.116518620431018</v>
       </c>
       <c r="W75">
-        <v>0.2079485381969189</v>
+        <v>0.208324909302366</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3937158863879147</v>
+        <v>0.3883954014367267</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2299653834805057</v>
+        <v>0.2318653834805057</v>
       </c>
       <c r="C76">
-        <v>-206.7085910313508</v>
+        <v>-216.6782589637779</v>
       </c>
       <c r="D76">
-        <v>244.4378089686491</v>
+        <v>241.9417410362221</v>
       </c>
       <c r="E76">
-        <v>543.8864</v>
+        <v>551.36</v>
       </c>
       <c r="F76">
-        <v>553.0463999999999</v>
+        <v>560.52</v>
       </c>
       <c r="G76">
         <v>101.9</v>
@@ -7507,37 +7507,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M76">
-        <v>130.40834112</v>
+        <v>132.170616</v>
       </c>
       <c r="N76">
-        <v>-79.75834112</v>
+        <v>-81.520616</v>
       </c>
       <c r="O76">
-        <v>-23.927502336</v>
+        <v>-24.4561848</v>
       </c>
       <c r="P76">
-        <v>-55.83083878399999</v>
+        <v>-57.0644312</v>
       </c>
       <c r="Q76">
-        <v>-52.23083878399999</v>
+        <v>-53.4644312</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.291557502295211</v>
+        <v>0.3013878023870195</v>
       </c>
       <c r="T76">
-        <v>3.576071104804492</v>
+        <v>3.719113948996672</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.116518620431018</v>
+        <v>0.1149650388252711</v>
       </c>
       <c r="W76">
-        <v>0.208324909302366</v>
+        <v>0.2086912438450011</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3883954014367267</v>
+        <v>0.383216796084237</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2318653834805057</v>
+        <v>0.2337653834805057</v>
       </c>
       <c r="C77">
-        <v>-216.6782589637779</v>
+        <v>-226.5974651677336</v>
       </c>
       <c r="D77">
-        <v>241.9417410362221</v>
+        <v>239.4961348322664</v>
       </c>
       <c r="E77">
-        <v>551.36</v>
+        <v>558.8336</v>
       </c>
       <c r="F77">
-        <v>560.52</v>
+        <v>567.9936</v>
       </c>
       <c r="G77">
         <v>101.9</v>
@@ -7589,37 +7589,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M77">
-        <v>132.170616</v>
+        <v>133.93289088</v>
       </c>
       <c r="N77">
-        <v>-81.520616</v>
+        <v>-83.28289088000001</v>
       </c>
       <c r="O77">
-        <v>-24.4561848</v>
+        <v>-24.984867264</v>
       </c>
       <c r="P77">
-        <v>-57.0644312</v>
+        <v>-58.29802361600001</v>
       </c>
       <c r="Q77">
-        <v>-53.4644312</v>
+        <v>-54.69802361600001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3013878023870195</v>
+        <v>0.3120372941531453</v>
       </c>
       <c r="T77">
-        <v>3.719113948996672</v>
+        <v>3.874077030204867</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1149650388252711</v>
+        <v>0.1134523409459912</v>
       </c>
       <c r="W77">
-        <v>0.2086912438450011</v>
+        <v>0.2090479380049353</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.383216796084237</v>
+        <v>0.3781744698199707</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2337653834805057</v>
+        <v>0.2356653834805057</v>
       </c>
       <c r="C78">
-        <v>-226.5974651677336</v>
+        <v>-236.4677245684085</v>
       </c>
       <c r="D78">
-        <v>239.4961348322664</v>
+        <v>237.0994754315915</v>
       </c>
       <c r="E78">
-        <v>558.8336</v>
+        <v>566.3072000000001</v>
       </c>
       <c r="F78">
-        <v>567.9936</v>
+        <v>575.4672</v>
       </c>
       <c r="G78">
         <v>101.9</v>
@@ -7671,37 +7671,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M78">
-        <v>133.93289088</v>
+        <v>135.69516576</v>
       </c>
       <c r="N78">
-        <v>-83.28289088000001</v>
+        <v>-85.04516576000002</v>
       </c>
       <c r="O78">
-        <v>-24.984867264</v>
+        <v>-25.513549728</v>
       </c>
       <c r="P78">
-        <v>-58.29802361600001</v>
+        <v>-59.53161603200002</v>
       </c>
       <c r="Q78">
-        <v>-54.69802361600001</v>
+        <v>-55.93161603200002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3120372941531453</v>
+        <v>0.323612828681543</v>
       </c>
       <c r="T78">
-        <v>3.874077030204867</v>
+        <v>4.042515161952905</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1134523409459912</v>
+        <v>0.1119789339207186</v>
       </c>
       <c r="W78">
-        <v>0.2090479380049353</v>
+        <v>0.2093953673814946</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3781744698199707</v>
+        <v>0.373263113069062</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2356653834805057</v>
+        <v>0.2375653834805057</v>
       </c>
       <c r="C79">
-        <v>-236.4677245684085</v>
+        <v>-246.2904920518392</v>
       </c>
       <c r="D79">
-        <v>237.0994754315915</v>
+        <v>234.7503079481609</v>
       </c>
       <c r="E79">
-        <v>566.3072000000001</v>
+        <v>573.7808000000001</v>
       </c>
       <c r="F79">
-        <v>575.4672</v>
+        <v>582.9408000000001</v>
       </c>
       <c r="G79">
         <v>101.9</v>
@@ -7753,37 +7753,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M79">
-        <v>135.69516576</v>
+        <v>137.45744064</v>
       </c>
       <c r="N79">
-        <v>-85.04516576000002</v>
+        <v>-86.80744064000002</v>
       </c>
       <c r="O79">
-        <v>-25.513549728</v>
+        <v>-26.04223219200001</v>
       </c>
       <c r="P79">
-        <v>-59.53161603200002</v>
+        <v>-60.76520844800002</v>
       </c>
       <c r="Q79">
-        <v>-55.93161603200002</v>
+        <v>-57.16520844800002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.323612828681543</v>
+        <v>0.3362406845307039</v>
       </c>
       <c r="T79">
-        <v>4.042515161952905</v>
+        <v>4.226265851132582</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1119789339207186</v>
+        <v>0.1105433065627607</v>
       </c>
       <c r="W79">
-        <v>0.2093953673814946</v>
+        <v>0.209733888312501</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.373263113069062</v>
+        <v>0.3684776885425355</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2375653834805057</v>
+        <v>0.2394653834805057</v>
       </c>
       <c r="C80">
-        <v>-246.2904920518392</v>
+        <v>-256.0671654100494</v>
       </c>
       <c r="D80">
-        <v>234.7503079481609</v>
+        <v>232.4472345899507</v>
       </c>
       <c r="E80">
-        <v>573.7808000000001</v>
+        <v>581.2544</v>
       </c>
       <c r="F80">
-        <v>582.9408000000001</v>
+        <v>590.4144</v>
       </c>
       <c r="G80">
         <v>101.9</v>
@@ -7835,37 +7835,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M80">
-        <v>137.45744064</v>
+        <v>139.21971552</v>
       </c>
       <c r="N80">
-        <v>-86.80744064000002</v>
+        <v>-88.56971552</v>
       </c>
       <c r="O80">
-        <v>-26.04223219200001</v>
+        <v>-26.570914656</v>
       </c>
       <c r="P80">
-        <v>-60.76520844800002</v>
+        <v>-61.998800864</v>
       </c>
       <c r="Q80">
-        <v>-57.16520844800002</v>
+        <v>-58.398800864</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3362406845307039</v>
+        <v>0.3500711933178803</v>
       </c>
       <c r="T80">
-        <v>4.226265851132582</v>
+        <v>4.427516605948419</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1105433065627607</v>
+        <v>0.1091440242012068</v>
       </c>
       <c r="W80">
-        <v>0.209733888312501</v>
+        <v>0.2100638390933555</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3684776885425355</v>
+        <v>0.3638134140040225</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2394653834805057</v>
+        <v>0.2413653834805057</v>
       </c>
       <c r="C81">
-        <v>-256.0671654100494</v>
+        <v>-265.7990881145117</v>
       </c>
       <c r="D81">
-        <v>232.4472345899507</v>
+        <v>230.1889118854884</v>
       </c>
       <c r="E81">
-        <v>581.2544</v>
+        <v>588.7280000000001</v>
       </c>
       <c r="F81">
-        <v>590.4144</v>
+        <v>597.888</v>
       </c>
       <c r="G81">
         <v>101.9</v>
@@ -7917,37 +7917,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M81">
-        <v>139.21971552</v>
+        <v>140.9819904</v>
       </c>
       <c r="N81">
-        <v>-88.56971552</v>
+        <v>-90.33199040000001</v>
       </c>
       <c r="O81">
-        <v>-26.570914656</v>
+        <v>-27.09959712</v>
       </c>
       <c r="P81">
-        <v>-61.998800864</v>
+        <v>-63.23239328000001</v>
       </c>
       <c r="Q81">
-        <v>-58.398800864</v>
+        <v>-59.63239328000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3500711933178803</v>
+        <v>0.3652847529837743</v>
       </c>
       <c r="T81">
-        <v>4.427516605948419</v>
+        <v>4.64889243624584</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1091440242012068</v>
+        <v>0.1077797238986917</v>
       </c>
       <c r="W81">
-        <v>0.2100638390933555</v>
+        <v>0.2103855411046885</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3638134140040225</v>
+        <v>0.3592657463289722</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2413653834805057</v>
+        <v>0.2432653834805057</v>
       </c>
       <c r="C82">
-        <v>-265.7990881145117</v>
+        <v>-275.4875519294933</v>
       </c>
       <c r="D82">
-        <v>230.1889118854884</v>
+        <v>227.9740480705068</v>
       </c>
       <c r="E82">
-        <v>588.7280000000001</v>
+        <v>596.2016000000001</v>
       </c>
       <c r="F82">
-        <v>597.888</v>
+        <v>605.3616000000001</v>
       </c>
       <c r="G82">
         <v>101.9</v>
@@ -7999,37 +7999,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M82">
-        <v>140.9819904</v>
+        <v>142.74426528</v>
       </c>
       <c r="N82">
-        <v>-90.33199040000001</v>
+        <v>-92.09426528000002</v>
       </c>
       <c r="O82">
-        <v>-27.09959712</v>
+        <v>-27.628279584</v>
       </c>
       <c r="P82">
-        <v>-63.23239328000001</v>
+        <v>-64.46598569600002</v>
       </c>
       <c r="Q82">
-        <v>-59.63239328000001</v>
+        <v>-60.86598569600002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3652847529837743</v>
+        <v>0.3820997399829204</v>
       </c>
       <c r="T82">
-        <v>4.64889243624584</v>
+        <v>4.893570985521937</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1077797238986917</v>
+        <v>0.1064491100233991</v>
       </c>
       <c r="W82">
-        <v>0.2103855411046885</v>
+        <v>0.2106992998564825</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3592657463289722</v>
+        <v>0.3548303667446638</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2432653834805057</v>
+        <v>0.2451653834805057</v>
       </c>
       <c r="C83">
-        <v>-275.4875519294933</v>
+        <v>-285.133799375966</v>
       </c>
       <c r="D83">
-        <v>227.9740480705068</v>
+        <v>225.8014006240341</v>
       </c>
       <c r="E83">
-        <v>596.2016000000001</v>
+        <v>603.6752000000001</v>
       </c>
       <c r="F83">
-        <v>605.3616000000001</v>
+        <v>612.8352000000001</v>
       </c>
       <c r="G83">
         <v>101.9</v>
@@ -8081,37 +8081,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M83">
-        <v>142.74426528</v>
+        <v>144.50654016</v>
       </c>
       <c r="N83">
-        <v>-92.09426528000002</v>
+        <v>-93.85654016000005</v>
       </c>
       <c r="O83">
-        <v>-27.628279584</v>
+        <v>-28.15696204800001</v>
       </c>
       <c r="P83">
-        <v>-64.46598569600002</v>
+        <v>-65.69957811200004</v>
       </c>
       <c r="Q83">
-        <v>-60.86598569600002</v>
+        <v>-62.09957811200004</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3820997399829204</v>
+        <v>0.4007830588708605</v>
       </c>
       <c r="T83">
-        <v>4.893570985521937</v>
+        <v>5.165436040273157</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1064491100233991</v>
+        <v>0.105150950145065</v>
       </c>
       <c r="W83">
-        <v>0.2106992998564825</v>
+        <v>0.2110054059557937</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3548303667446638</v>
+        <v>0.3505031671502167</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2451653834805057</v>
+        <v>0.2470653834805057</v>
       </c>
       <c r="C84">
-        <v>-285.133799375966</v>
+        <v>-294.739026055957</v>
       </c>
       <c r="D84">
-        <v>225.8014006240341</v>
+        <v>223.6697739440431</v>
       </c>
       <c r="E84">
-        <v>603.6752000000001</v>
+        <v>611.1488000000001</v>
       </c>
       <c r="F84">
-        <v>612.8352000000001</v>
+        <v>620.3088</v>
       </c>
       <c r="G84">
         <v>101.9</v>
@@ -8163,37 +8163,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M84">
-        <v>144.50654016</v>
+        <v>146.26881504</v>
       </c>
       <c r="N84">
-        <v>-93.85654016000005</v>
+        <v>-95.61881504000003</v>
       </c>
       <c r="O84">
-        <v>-28.15696204800001</v>
+        <v>-28.68564451200001</v>
       </c>
       <c r="P84">
-        <v>-65.69957811200004</v>
+        <v>-66.93317052800002</v>
       </c>
       <c r="Q84">
-        <v>-62.09957811200004</v>
+        <v>-63.33317052800002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4007830588708605</v>
+        <v>0.4216644152750287</v>
       </c>
       <c r="T84">
-        <v>5.165436040273157</v>
+        <v>5.469285219112755</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.105150950145065</v>
+        <v>0.1038840712276546</v>
       </c>
       <c r="W84">
-        <v>0.2110054059557937</v>
+        <v>0.2113041360045191</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3505031671502167</v>
+        <v>0.3462802374255153</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2470653834805057</v>
+        <v>0.2489653834805057</v>
       </c>
       <c r="C85">
-        <v>-294.739026055957</v>
+        <v>-304.3043828464756</v>
       </c>
       <c r="D85">
-        <v>223.6697739440431</v>
+        <v>221.5780171535244</v>
       </c>
       <c r="E85">
-        <v>611.1488000000001</v>
+        <v>618.6224000000001</v>
       </c>
       <c r="F85">
-        <v>620.3088</v>
+        <v>627.7824000000001</v>
       </c>
       <c r="G85">
         <v>101.9</v>
@@ -8245,37 +8245,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M85">
-        <v>146.26881504</v>
+        <v>148.03108992</v>
       </c>
       <c r="N85">
-        <v>-95.61881504000003</v>
+        <v>-97.38108992000004</v>
       </c>
       <c r="O85">
-        <v>-28.68564451200001</v>
+        <v>-29.21432697600001</v>
       </c>
       <c r="P85">
-        <v>-66.93317052800002</v>
+        <v>-68.16676294400003</v>
       </c>
       <c r="Q85">
-        <v>-63.33317052800002</v>
+        <v>-64.56676294400003</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4216644152750287</v>
+        <v>0.4451559412297182</v>
       </c>
       <c r="T85">
-        <v>5.469285219112755</v>
+        <v>5.811115545307304</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1038840712276546</v>
+        <v>0.102647356093992</v>
       </c>
       <c r="W85">
-        <v>0.2113041360045191</v>
+        <v>0.2115957534330367</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3462802374255153</v>
+        <v>0.3421578536466401</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2489653834805057</v>
+        <v>0.2508653834805057</v>
       </c>
       <c r="C86">
-        <v>-304.3043828464755</v>
+        <v>-313.8309779714754</v>
       </c>
       <c r="D86">
-        <v>221.5780171535245</v>
+        <v>219.5250220285246</v>
       </c>
       <c r="E86">
-        <v>618.6224</v>
+        <v>626.096</v>
       </c>
       <c r="F86">
-        <v>627.7823999999999</v>
+        <v>635.256</v>
       </c>
       <c r="G86">
         <v>101.9</v>
@@ -8327,37 +8327,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M86">
-        <v>148.03108992</v>
+        <v>149.7933648</v>
       </c>
       <c r="N86">
-        <v>-97.38108992000001</v>
+        <v>-99.14336480000001</v>
       </c>
       <c r="O86">
-        <v>-29.214326976</v>
+        <v>-29.74300944</v>
       </c>
       <c r="P86">
-        <v>-68.166762944</v>
+        <v>-69.40035536000002</v>
       </c>
       <c r="Q86">
-        <v>-64.566762944</v>
+        <v>-65.80035536000003</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4451559412297179</v>
+        <v>0.4717796706450323</v>
       </c>
       <c r="T86">
-        <v>5.8111155453073</v>
+        <v>6.198523248327786</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1026473560939921</v>
+        <v>0.1014397401399451</v>
       </c>
       <c r="W86">
-        <v>0.2115957534330367</v>
+        <v>0.211880509275001</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3421578536466402</v>
+        <v>0.3381324671331503</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2508653834805057</v>
+        <v>0.2527653834805057</v>
       </c>
       <c r="C87">
-        <v>-313.8309779714754</v>
+        <v>-323.3198789596887</v>
       </c>
       <c r="D87">
-        <v>219.5250220285246</v>
+        <v>217.5097210403113</v>
       </c>
       <c r="E87">
-        <v>626.096</v>
+        <v>633.5696</v>
       </c>
       <c r="F87">
-        <v>635.256</v>
+        <v>642.7296</v>
       </c>
       <c r="G87">
         <v>101.9</v>
@@ -8409,37 +8409,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M87">
-        <v>149.7933648</v>
+        <v>151.55563968</v>
       </c>
       <c r="N87">
-        <v>-99.14336480000001</v>
+        <v>-100.90563968</v>
       </c>
       <c r="O87">
-        <v>-29.74300944</v>
+        <v>-30.271691904</v>
       </c>
       <c r="P87">
-        <v>-69.40035536000002</v>
+        <v>-70.63394777600001</v>
       </c>
       <c r="Q87">
-        <v>-65.80035536000003</v>
+        <v>-67.03394777600002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4717796706450323</v>
+        <v>0.5022067899768204</v>
       </c>
       <c r="T87">
-        <v>6.198523248327786</v>
+        <v>6.641274908922629</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1014397401399451</v>
+        <v>0.1002602082778527</v>
       </c>
       <c r="W87">
-        <v>0.211880509275001</v>
+        <v>0.2121586428880824</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3381324671331503</v>
+        <v>0.3342006942595089</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2527653834805057</v>
+        <v>0.2546653834805057</v>
       </c>
       <c r="C88">
-        <v>-323.3198789596887</v>
+        <v>-332.7721144956015</v>
       </c>
       <c r="D88">
-        <v>217.5097210403113</v>
+        <v>215.5310855043985</v>
       </c>
       <c r="E88">
-        <v>633.5696</v>
+        <v>641.0432000000001</v>
       </c>
       <c r="F88">
-        <v>642.7296</v>
+        <v>650.2032</v>
       </c>
       <c r="G88">
         <v>101.9</v>
@@ -8491,37 +8491,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M88">
-        <v>151.55563968</v>
+        <v>153.31791456</v>
       </c>
       <c r="N88">
-        <v>-100.90563968</v>
+        <v>-102.66791456</v>
       </c>
       <c r="O88">
-        <v>-30.271691904</v>
+        <v>-30.80037436800001</v>
       </c>
       <c r="P88">
-        <v>-70.63394777600001</v>
+        <v>-71.86754019200002</v>
       </c>
       <c r="Q88">
-        <v>-67.03394777600002</v>
+        <v>-68.26754019200001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5022067899768204</v>
+        <v>0.5373150045904219</v>
       </c>
       <c r="T88">
-        <v>6.641274908922629</v>
+        <v>7.152142209608984</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1002602082778527</v>
+        <v>0.09910779209075092</v>
       </c>
       <c r="W88">
-        <v>0.2121586428880824</v>
+        <v>0.2124303826250009</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3342006942595089</v>
+        <v>0.3303593069691698</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2546653834805057</v>
+        <v>0.2565653834805057</v>
       </c>
       <c r="C89">
-        <v>-332.7721144956015</v>
+        <v>-342.1886761703124</v>
       </c>
       <c r="D89">
-        <v>215.5310855043985</v>
+        <v>213.5881238296877</v>
       </c>
       <c r="E89">
-        <v>641.0432000000001</v>
+        <v>648.5168000000001</v>
       </c>
       <c r="F89">
-        <v>650.2032</v>
+        <v>657.6768000000001</v>
       </c>
       <c r="G89">
         <v>101.9</v>
@@ -8573,37 +8573,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M89">
-        <v>153.31791456</v>
+        <v>155.08018944</v>
       </c>
       <c r="N89">
-        <v>-102.66791456</v>
+        <v>-104.43018944</v>
       </c>
       <c r="O89">
-        <v>-30.80037436800001</v>
+        <v>-31.32905683200001</v>
       </c>
       <c r="P89">
-        <v>-71.86754019200002</v>
+        <v>-73.10113260800003</v>
       </c>
       <c r="Q89">
-        <v>-68.26754019200001</v>
+        <v>-69.50113260800003</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5373150045904219</v>
+        <v>0.5782745883062905</v>
       </c>
       <c r="T89">
-        <v>7.152142209608984</v>
+        <v>7.748154060409735</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.09910779209075092</v>
+        <v>0.09798156718062875</v>
       </c>
       <c r="W89">
-        <v>0.2124303826250009</v>
+        <v>0.2126959464588077</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3303593069691698</v>
+        <v>0.3266052239354292</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2565653834805057</v>
+        <v>0.2584653834805057</v>
       </c>
       <c r="C90">
-        <v>-342.1886761703124</v>
+        <v>-351.5705201385348</v>
       </c>
       <c r="D90">
-        <v>213.5881238296877</v>
+        <v>211.6798798614652</v>
       </c>
       <c r="E90">
-        <v>648.5168000000001</v>
+        <v>655.9904</v>
       </c>
       <c r="F90">
-        <v>657.6768000000001</v>
+        <v>665.1504</v>
       </c>
       <c r="G90">
         <v>101.9</v>
@@ -8655,37 +8655,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M90">
-        <v>155.08018944</v>
+        <v>156.84246432</v>
       </c>
       <c r="N90">
-        <v>-104.43018944</v>
+        <v>-106.19246432</v>
       </c>
       <c r="O90">
-        <v>-31.32905683200001</v>
+        <v>-31.857739296</v>
       </c>
       <c r="P90">
-        <v>-73.10113260800003</v>
+        <v>-74.33472502400001</v>
       </c>
       <c r="Q90">
-        <v>-69.50113260800003</v>
+        <v>-70.734725024</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5782745883062905</v>
+        <v>0.6266813690614078</v>
       </c>
       <c r="T90">
-        <v>7.748154060409735</v>
+        <v>8.452531702265164</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.09798156718062875</v>
+        <v>0.09688065069545317</v>
       </c>
       <c r="W90">
-        <v>0.2126959464588077</v>
+        <v>0.2129555425660122</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3266052239354292</v>
+        <v>0.3229355023181772</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2584653834805057</v>
+        <v>0.2603653834805057</v>
       </c>
       <c r="C91">
-        <v>-351.5705201385348</v>
+        <v>-360.9185686875634</v>
       </c>
       <c r="D91">
-        <v>211.6798798614652</v>
+        <v>209.8054313124366</v>
       </c>
       <c r="E91">
-        <v>655.9904</v>
+        <v>663.4640000000001</v>
       </c>
       <c r="F91">
-        <v>665.1504</v>
+        <v>672.624</v>
       </c>
       <c r="G91">
         <v>101.9</v>
@@ -8737,37 +8737,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M91">
-        <v>156.84246432</v>
+        <v>158.6047392</v>
       </c>
       <c r="N91">
-        <v>-106.19246432</v>
+        <v>-107.9547392</v>
       </c>
       <c r="O91">
-        <v>-31.857739296</v>
+        <v>-32.38642176</v>
       </c>
       <c r="P91">
-        <v>-74.33472502400001</v>
+        <v>-75.56831744000002</v>
       </c>
       <c r="Q91">
-        <v>-70.734725024</v>
+        <v>-71.96831744000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6266813690614078</v>
+        <v>0.6847695059675487</v>
       </c>
       <c r="T91">
-        <v>8.452531702265164</v>
+        <v>9.297784872491683</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.09688065069545317</v>
+        <v>0.09580419902105924</v>
       </c>
       <c r="W91">
-        <v>0.2129555425660122</v>
+        <v>0.2132093698708342</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3229355023181772</v>
+        <v>0.3193473300701974</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2603653834805057</v>
+        <v>0.2622653834805057</v>
       </c>
       <c r="C92">
-        <v>-360.9185686875634</v>
+        <v>-370.2337117236098</v>
       </c>
       <c r="D92">
-        <v>209.8054313124366</v>
+        <v>207.9638882763903</v>
       </c>
       <c r="E92">
-        <v>663.4640000000001</v>
+        <v>670.9376000000001</v>
       </c>
       <c r="F92">
-        <v>672.624</v>
+        <v>680.0976000000001</v>
       </c>
       <c r="G92">
         <v>101.9</v>
@@ -8819,37 +8819,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M92">
-        <v>158.6047392</v>
+        <v>160.36701408</v>
       </c>
       <c r="N92">
-        <v>-107.9547392</v>
+        <v>-109.71701408</v>
       </c>
       <c r="O92">
-        <v>-32.38642176</v>
+        <v>-32.915104224</v>
       </c>
       <c r="P92">
-        <v>-75.56831744000002</v>
+        <v>-76.80190985600002</v>
       </c>
       <c r="Q92">
-        <v>-71.96831744000002</v>
+        <v>-73.20190985600001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6847695059675487</v>
+        <v>0.7557661177417209</v>
       </c>
       <c r="T92">
-        <v>9.297784872491683</v>
+        <v>10.33087208054631</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.09580419902105924</v>
+        <v>0.09475140562522343</v>
       </c>
       <c r="W92">
-        <v>0.2132093698708342</v>
+        <v>0.2134576185535723</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3193473300701974</v>
+        <v>0.3158380187507447</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2622653834805057</v>
+        <v>0.2641653834805057</v>
       </c>
       <c r="C93">
-        <v>-370.2337117236098</v>
+        <v>-379.5168081805445</v>
       </c>
       <c r="D93">
-        <v>207.9638882763903</v>
+        <v>206.1543918194556</v>
       </c>
       <c r="E93">
-        <v>670.9376000000001</v>
+        <v>678.4112000000001</v>
       </c>
       <c r="F93">
-        <v>680.0976000000001</v>
+        <v>687.5712000000001</v>
       </c>
       <c r="G93">
         <v>101.9</v>
@@ -8901,37 +8901,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M93">
-        <v>160.36701408</v>
+        <v>162.12928896</v>
       </c>
       <c r="N93">
-        <v>-109.71701408</v>
+        <v>-111.47928896</v>
       </c>
       <c r="O93">
-        <v>-32.915104224</v>
+        <v>-33.44378668800001</v>
       </c>
       <c r="P93">
-        <v>-76.80190985600002</v>
+        <v>-78.03550227200003</v>
       </c>
       <c r="Q93">
-        <v>-73.20190985600001</v>
+        <v>-74.43550227200004</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7557661177417209</v>
+        <v>0.8445118824594363</v>
       </c>
       <c r="T93">
-        <v>10.33087208054631</v>
+        <v>11.62223109061461</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.09475140562522343</v>
+        <v>0.09372149904234056</v>
       </c>
       <c r="W93">
-        <v>0.2134576185535723</v>
+        <v>0.2137004705258161</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3158380187507447</v>
+        <v>0.3124049968078019</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2641653834805057</v>
+        <v>0.2660653834805057</v>
       </c>
       <c r="C94">
-        <v>-379.5168081805445</v>
+        <v>-388.7686873557268</v>
       </c>
       <c r="D94">
-        <v>206.1543918194556</v>
+        <v>204.3761126442732</v>
       </c>
       <c r="E94">
-        <v>678.4112000000001</v>
+        <v>685.8848</v>
       </c>
       <c r="F94">
-        <v>687.5712000000001</v>
+        <v>695.0448</v>
       </c>
       <c r="G94">
         <v>101.9</v>
@@ -8983,37 +8983,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M94">
-        <v>162.12928896</v>
+        <v>163.89156384</v>
       </c>
       <c r="N94">
-        <v>-111.47928896</v>
+        <v>-113.24156384</v>
       </c>
       <c r="O94">
-        <v>-33.44378668800001</v>
+        <v>-33.972469152</v>
       </c>
       <c r="P94">
-        <v>-78.03550227200003</v>
+        <v>-79.26909468800001</v>
       </c>
       <c r="Q94">
-        <v>-74.43550227200004</v>
+        <v>-75.669094688</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8445118824594363</v>
+        <v>0.9586135799536415</v>
       </c>
       <c r="T94">
-        <v>11.62223109061461</v>
+        <v>13.28254981784527</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09372149904234056</v>
+        <v>0.09271374098812184</v>
       </c>
       <c r="W94">
-        <v>0.2137004705258161</v>
+        <v>0.2139380998750009</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3124049968078019</v>
+        <v>0.3090458032937395</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2660653834805057</v>
+        <v>0.2679653834805057</v>
       </c>
       <c r="C95">
-        <v>-388.7686873557268</v>
+        <v>-397.990150177291</v>
       </c>
       <c r="D95">
-        <v>204.3761126442732</v>
+        <v>202.6282498227091</v>
       </c>
       <c r="E95">
-        <v>685.8848</v>
+        <v>693.3584000000001</v>
       </c>
       <c r="F95">
-        <v>695.0448</v>
+        <v>702.5184</v>
       </c>
       <c r="G95">
         <v>101.9</v>
@@ -9065,37 +9065,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M95">
-        <v>163.89156384</v>
+        <v>165.65383872</v>
       </c>
       <c r="N95">
-        <v>-113.24156384</v>
+        <v>-115.00383872</v>
       </c>
       <c r="O95">
-        <v>-33.972469152</v>
+        <v>-34.501151616</v>
       </c>
       <c r="P95">
-        <v>-79.26909468800001</v>
+        <v>-80.50268710400002</v>
       </c>
       <c r="Q95">
-        <v>-75.669094688</v>
+        <v>-76.90268710400002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9586135799536415</v>
+        <v>1.110749176612582</v>
       </c>
       <c r="T95">
-        <v>13.28254981784527</v>
+        <v>15.49630812081948</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09271374098812184</v>
+        <v>0.09172742459463119</v>
       </c>
       <c r="W95">
-        <v>0.2139380998750009</v>
+        <v>0.214170673280586</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3090458032937395</v>
+        <v>0.305758081982104</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2679653834805057</v>
+        <v>0.2698653834805057</v>
       </c>
       <c r="C96">
-        <v>-397.990150177291</v>
+        <v>-407.1819704069529</v>
       </c>
       <c r="D96">
-        <v>202.6282498227091</v>
+        <v>200.9100295930471</v>
       </c>
       <c r="E96">
-        <v>693.3584000000001</v>
+        <v>700.8320000000001</v>
       </c>
       <c r="F96">
-        <v>702.5184</v>
+        <v>709.9920000000001</v>
       </c>
       <c r="G96">
         <v>101.9</v>
@@ -9147,37 +9147,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M96">
-        <v>165.65383872</v>
+        <v>167.4161136</v>
       </c>
       <c r="N96">
-        <v>-115.00383872</v>
+        <v>-116.7661136</v>
       </c>
       <c r="O96">
-        <v>-34.501151616</v>
+        <v>-35.02983408000001</v>
       </c>
       <c r="P96">
-        <v>-80.50268710400002</v>
+        <v>-81.73627952000001</v>
       </c>
       <c r="Q96">
-        <v>-76.90268710400002</v>
+        <v>-78.13627952000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.110749176612582</v>
+        <v>1.323739011935099</v>
       </c>
       <c r="T96">
-        <v>15.49630812081948</v>
+        <v>18.59556974498339</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09172742459463119</v>
+        <v>0.09076187275679296</v>
       </c>
       <c r="W96">
-        <v>0.214170673280586</v>
+        <v>0.2143983504039482</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.305758081982104</v>
+        <v>0.3025395758559766</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2698653834805057</v>
+        <v>0.2717653834805057</v>
       </c>
       <c r="C97">
-        <v>-407.1819704069529</v>
+        <v>-416.3448957821369</v>
       </c>
       <c r="D97">
-        <v>200.9100295930471</v>
+        <v>199.2207042178632</v>
       </c>
       <c r="E97">
-        <v>700.8320000000001</v>
+        <v>708.3056000000001</v>
       </c>
       <c r="F97">
-        <v>709.9920000000001</v>
+        <v>717.4656000000001</v>
       </c>
       <c r="G97">
         <v>101.9</v>
@@ -9229,37 +9229,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M97">
-        <v>167.4161136</v>
+        <v>169.17838848</v>
       </c>
       <c r="N97">
-        <v>-116.7661136</v>
+        <v>-118.52838848</v>
       </c>
       <c r="O97">
-        <v>-35.02983408000001</v>
+        <v>-35.55851654400001</v>
       </c>
       <c r="P97">
-        <v>-81.73627952000001</v>
+        <v>-82.96987193600003</v>
       </c>
       <c r="Q97">
-        <v>-78.13627952000002</v>
+        <v>-79.36987193600004</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.323739011935099</v>
+        <v>1.643223764918875</v>
       </c>
       <c r="T97">
-        <v>18.59556974498339</v>
+        <v>23.24446218122925</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09076187275679296</v>
+        <v>0.08981643658224303</v>
       </c>
       <c r="W97">
-        <v>0.2143983504039482</v>
+        <v>0.2146212842539071</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3025395758559766</v>
+        <v>0.2993881219408101</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2717653834805057</v>
+        <v>0.2736653834805057</v>
       </c>
       <c r="C98">
-        <v>-416.3448957821367</v>
+        <v>-425.4796491009616</v>
       </c>
       <c r="D98">
-        <v>199.2207042178632</v>
+        <v>197.5595508990384</v>
       </c>
       <c r="E98">
-        <v>708.3056</v>
+        <v>715.7792000000001</v>
       </c>
       <c r="F98">
-        <v>717.4656</v>
+        <v>724.9392</v>
       </c>
       <c r="G98">
         <v>101.9</v>
@@ -9311,37 +9311,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M98">
-        <v>169.17838848</v>
+        <v>170.94066336</v>
       </c>
       <c r="N98">
-        <v>-118.52838848</v>
+        <v>-120.29066336</v>
       </c>
       <c r="O98">
-        <v>-35.558516544</v>
+        <v>-36.087199008</v>
       </c>
       <c r="P98">
-        <v>-82.969871936</v>
+        <v>-84.20346435200001</v>
       </c>
       <c r="Q98">
-        <v>-79.36987193600001</v>
+        <v>-80.603464352</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.64322376491887</v>
+        <v>2.17569835322516</v>
       </c>
       <c r="T98">
-        <v>23.24446218122918</v>
+        <v>30.99261624163891</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08981643658224304</v>
+        <v>0.08889049393706529</v>
       </c>
       <c r="W98">
-        <v>0.2146212842539071</v>
+        <v>0.21483962152964</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2993881219408102</v>
+        <v>0.2963016464568843</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2736653834805057</v>
+        <v>0.2755653834805057</v>
       </c>
       <c r="C99">
-        <v>-425.4796491009616</v>
+        <v>-434.5869292533941</v>
       </c>
       <c r="D99">
-        <v>197.5595508990384</v>
+        <v>195.9258707466058</v>
       </c>
       <c r="E99">
-        <v>715.7792000000001</v>
+        <v>723.2528</v>
       </c>
       <c r="F99">
-        <v>724.9392</v>
+        <v>732.4127999999999</v>
       </c>
       <c r="G99">
         <v>101.9</v>
@@ -9393,37 +9393,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M99">
-        <v>170.94066336</v>
+        <v>172.70293824</v>
       </c>
       <c r="N99">
-        <v>-120.29066336</v>
+        <v>-122.05293824</v>
       </c>
       <c r="O99">
-        <v>-36.087199008</v>
+        <v>-36.61588147200001</v>
       </c>
       <c r="P99">
-        <v>-84.20346435200001</v>
+        <v>-85.43705676800002</v>
       </c>
       <c r="Q99">
-        <v>-80.603464352</v>
+        <v>-81.83705676800002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.17569835322516</v>
+        <v>3.24064752983774</v>
       </c>
       <c r="T99">
-        <v>30.99261624163891</v>
+        <v>46.48892436245836</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08889049393706529</v>
+        <v>0.0879834480805646</v>
       </c>
       <c r="W99">
-        <v>0.21483962152964</v>
+        <v>0.2150535029426029</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2963016464568843</v>
+        <v>0.2932781602685487</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2755653834805057</v>
+        <v>0.2774653834805056</v>
       </c>
       <c r="C100">
-        <v>-434.5869292533941</v>
+        <v>-443.6674122016611</v>
       </c>
       <c r="D100">
-        <v>195.9258707466058</v>
+        <v>194.3189877983388</v>
       </c>
       <c r="E100">
-        <v>723.2528</v>
+        <v>730.7264</v>
       </c>
       <c r="F100">
-        <v>732.4127999999999</v>
+        <v>739.8864</v>
       </c>
       <c r="G100">
         <v>101.9</v>
@@ -9475,37 +9475,37 @@
         <v>50.64999999999999</v>
       </c>
       <c r="M100">
-        <v>172.70293824</v>
+        <v>174.46521312</v>
       </c>
       <c r="N100">
-        <v>-122.05293824</v>
+        <v>-123.81521312</v>
       </c>
       <c r="O100">
-        <v>-36.61588147200001</v>
+        <v>-37.144563936</v>
       </c>
       <c r="P100">
-        <v>-85.43705676800002</v>
+        <v>-86.67064918400001</v>
       </c>
       <c r="Q100">
-        <v>-81.83705676800002</v>
+        <v>-83.07064918400002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.24064752983774</v>
+        <v>6.435495059675481</v>
       </c>
       <c r="T100">
-        <v>46.48892436245836</v>
+        <v>92.97784872491673</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0879834480805646</v>
+        <v>0.08709472638278114</v>
       </c>
       <c r="W100">
-        <v>0.2150535029426029</v>
+        <v>0.2152630635189402</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2932781602685487</v>
+        <v>0.2903157546092704</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2774653834805056</v>
-      </c>
-      <c r="C101">
-        <v>-443.6674122016611</v>
-      </c>
-      <c r="D101">
-        <v>194.3189877983388</v>
-      </c>
-      <c r="E101">
-        <v>730.7264</v>
-      </c>
-      <c r="F101">
-        <v>739.8864</v>
-      </c>
-      <c r="G101">
-        <v>101.9</v>
-      </c>
-      <c r="H101">
-        <v>738.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>54.24999999999999</v>
-      </c>
-      <c r="K101">
-        <v>3.600000000000001</v>
-      </c>
-      <c r="L101">
-        <v>50.64999999999999</v>
-      </c>
-      <c r="M101">
-        <v>174.46521312</v>
-      </c>
-      <c r="N101">
-        <v>-123.81521312</v>
-      </c>
-      <c r="O101">
-        <v>-37.144563936</v>
-      </c>
-      <c r="P101">
-        <v>-86.67064918400001</v>
-      </c>
-      <c r="Q101">
-        <v>-83.07064918400002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.435495059675481</v>
-      </c>
-      <c r="T101">
-        <v>92.97784872491673</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08709472638278114</v>
-      </c>
-      <c r="W101">
-        <v>0.2152630635189402</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2903157546092704</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
